--- a/docs/MUSCLE_EXPERIENCE_FINAL_2026-07-25.xlsx
+++ b/docs/MUSCLE_EXPERIENCE_FINAL_2026-07-25.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F199"/>
+  <dimension ref="A1:F200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -511,64 +511,43 @@
       <c r="F4" s="1" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>CHANGE LOG — Sam 2026-07-27: MetCon row DELETED (the conditioning ruling retiring the name wins); Single-Arm Pulldown row ADDED (Lats / Upper back, Midline / everyone); 3 casing typos corrected as authorised edits (Suitcase Carry + Skull Crushers 'Everyone' -&gt; 'everyone', Chin-Up Negative (Slow) secondary 'midline' -&gt; 'Midline').</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Pool</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Exercise</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Primary Muscle Group(s)</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Secondary Muscle Group(s)</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Experience Level</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Lower squat</t>
-        </is>
-      </c>
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>Back Squat</t>
-        </is>
-      </c>
-      <c r="C6" s="1" t="inlineStr">
-        <is>
-          <t>Quads, Glutes</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="inlineStr">
-        <is>
-          <t>Hips, Midline, Low back</t>
-        </is>
-      </c>
-      <c r="E6" s="1" t="inlineStr">
-        <is>
-          <t>2+ years</t>
-        </is>
-      </c>
-      <c r="F6" s="1" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -578,7 +557,7 @@
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>Front Squat</t>
+          <t>Back Squat</t>
         </is>
       </c>
       <c r="C7" s="1" t="inlineStr">
@@ -588,7 +567,7 @@
       </c>
       <c r="D7" s="1" t="inlineStr">
         <is>
-          <t>Midline, Upper back</t>
+          <t>Hips, Midline, Low back</t>
         </is>
       </c>
       <c r="E7" s="1" t="inlineStr">
@@ -596,11 +575,7 @@
           <t>2+ years</t>
         </is>
       </c>
-      <c r="F7" s="1" t="inlineStr">
-        <is>
-          <t>⚑ rack-position mobility/technique demand is higher than back squat, but could reasonably be 1+ years.</t>
-        </is>
-      </c>
+      <c r="F7" s="1" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -610,7 +585,7 @@
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>Box Squat</t>
+          <t>Front Squat</t>
         </is>
       </c>
       <c r="C8" s="1" t="inlineStr">
@@ -620,15 +595,19 @@
       </c>
       <c r="D8" s="1" t="inlineStr">
         <is>
-          <t>Hips</t>
+          <t>Midline, Upper back</t>
         </is>
       </c>
       <c r="E8" s="1" t="inlineStr">
         <is>
-          <t>1+ years</t>
-        </is>
-      </c>
-      <c r="F8" s="1" t="inlineStr"/>
+          <t>2+ years</t>
+        </is>
+      </c>
+      <c r="F8" s="1" t="inlineStr">
+        <is>
+          <t>⚑ rack-position mobility/technique demand is higher than back squat, but could reasonably be 1+ years.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -638,7 +617,7 @@
       </c>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>High Box Squat</t>
+          <t>Box Squat</t>
         </is>
       </c>
       <c r="C9" s="1" t="inlineStr">
@@ -666,7 +645,7 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>Walking Lunges</t>
+          <t>High Box Squat</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
@@ -676,7 +655,7 @@
       </c>
       <c r="D10" s="1" t="inlineStr">
         <is>
-          <t>Hamstrings, Hips</t>
+          <t>Hips</t>
         </is>
       </c>
       <c r="E10" s="1" t="inlineStr">
@@ -694,7 +673,7 @@
       </c>
       <c r="B11" s="1" t="inlineStr">
         <is>
-          <t>Bulgarian Split Squats</t>
+          <t>Walking Lunges</t>
         </is>
       </c>
       <c r="C11" s="1" t="inlineStr">
@@ -709,7 +688,7 @@
       </c>
       <c r="E11" s="1" t="inlineStr">
         <is>
-          <t>2+ years</t>
+          <t>1+ years</t>
         </is>
       </c>
       <c r="F11" s="1" t="inlineStr"/>
@@ -722,7 +701,7 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>Reverse Lunges</t>
+          <t>Bulgarian Split Squats</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
@@ -737,7 +716,7 @@
       </c>
       <c r="E12" s="1" t="inlineStr">
         <is>
-          <t>everyone</t>
+          <t>2+ years</t>
         </is>
       </c>
       <c r="F12" s="1" t="inlineStr"/>
@@ -750,7 +729,7 @@
       </c>
       <c r="B13" s="1" t="inlineStr">
         <is>
-          <t>Step Ups</t>
+          <t>Reverse Lunges</t>
         </is>
       </c>
       <c r="C13" s="1" t="inlineStr">
@@ -760,7 +739,7 @@
       </c>
       <c r="D13" s="1" t="inlineStr">
         <is>
-          <t>Hips</t>
+          <t>Hamstrings, Hips</t>
         </is>
       </c>
       <c r="E13" s="1" t="inlineStr">
@@ -778,7 +757,7 @@
       </c>
       <c r="B14" s="1" t="inlineStr">
         <is>
-          <t>Goblet Squat</t>
+          <t>Step Ups</t>
         </is>
       </c>
       <c r="C14" s="1" t="inlineStr">
@@ -788,12 +767,12 @@
       </c>
       <c r="D14" s="1" t="inlineStr">
         <is>
-          <t>Midline</t>
+          <t>Hips</t>
         </is>
       </c>
       <c r="E14" s="1" t="inlineStr">
         <is>
-          <t>everyone (regression)</t>
+          <t>everyone</t>
         </is>
       </c>
       <c r="F14" s="1" t="inlineStr"/>
@@ -806,7 +785,7 @@
       </c>
       <c r="B15" s="1" t="inlineStr">
         <is>
-          <t>Leg Press</t>
+          <t>Goblet Squat</t>
         </is>
       </c>
       <c r="C15" s="1" t="inlineStr">
@@ -816,12 +795,12 @@
       </c>
       <c r="D15" s="1" t="inlineStr">
         <is>
-          <t>Hamstrings</t>
+          <t>Midline</t>
         </is>
       </c>
       <c r="E15" s="1" t="inlineStr">
         <is>
-          <t>everyone</t>
+          <t>everyone (regression)</t>
         </is>
       </c>
       <c r="F15" s="1" t="inlineStr"/>
@@ -834,7 +813,7 @@
       </c>
       <c r="B16" s="1" t="inlineStr">
         <is>
-          <t>Single-Leg Leg Press</t>
+          <t>Leg Press</t>
         </is>
       </c>
       <c r="C16" s="1" t="inlineStr">
@@ -844,7 +823,7 @@
       </c>
       <c r="D16" s="1" t="inlineStr">
         <is>
-          <t>Hamstrings, Hips</t>
+          <t>Hamstrings</t>
         </is>
       </c>
       <c r="E16" s="1" t="inlineStr">
@@ -862,7 +841,7 @@
       </c>
       <c r="B17" s="1" t="inlineStr">
         <is>
-          <t>Single-Leg Squat (to Box)</t>
+          <t>Single-Leg Leg Press</t>
         </is>
       </c>
       <c r="C17" s="1" t="inlineStr">
@@ -872,12 +851,12 @@
       </c>
       <c r="D17" s="1" t="inlineStr">
         <is>
-          <t>Hips</t>
+          <t>Hamstrings, Hips</t>
         </is>
       </c>
       <c r="E17" s="1" t="inlineStr">
         <is>
-          <t>1+ years</t>
+          <t>everyone</t>
         </is>
       </c>
       <c r="F17" s="1" t="inlineStr"/>
@@ -890,7 +869,7 @@
       </c>
       <c r="B18" s="1" t="inlineStr">
         <is>
-          <t>Bodyweight Squat</t>
+          <t>Single-Leg Squat (to Box)</t>
         </is>
       </c>
       <c r="C18" s="1" t="inlineStr">
@@ -898,10 +877,14 @@
           <t>Quads, Glutes</t>
         </is>
       </c>
-      <c r="D18" s="1" t="inlineStr"/>
+      <c r="D18" s="1" t="inlineStr">
+        <is>
+          <t>Hips</t>
+        </is>
+      </c>
       <c r="E18" s="1" t="inlineStr">
         <is>
-          <t>everyone (regression)</t>
+          <t>1+ years</t>
         </is>
       </c>
       <c r="F18" s="1" t="inlineStr"/>
@@ -909,34 +892,26 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>Lower hinge</t>
+          <t>Lower squat</t>
         </is>
       </c>
       <c r="B19" s="1" t="inlineStr">
         <is>
-          <t>Deadlift</t>
+          <t>Bodyweight Squat</t>
         </is>
       </c>
       <c r="C19" s="1" t="inlineStr">
         <is>
-          <t>Hamstrings, Glutes, Low back</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="inlineStr">
-        <is>
-          <t>Upper back, Midline</t>
-        </is>
-      </c>
+          <t>Quads, Glutes</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="inlineStr"/>
       <c r="E19" s="1" t="inlineStr">
         <is>
-          <t>2+ years</t>
-        </is>
-      </c>
-      <c r="F19" s="1" t="inlineStr">
-        <is>
-          <t>⚑ straight-bar technical demand; app's own beginner curriculum substitutes Trap Bar instead, but 1+ years is defensible too.</t>
-        </is>
-      </c>
+          <t>everyone (regression)</t>
+        </is>
+      </c>
+      <c r="F19" s="1" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
@@ -946,7 +921,7 @@
       </c>
       <c r="B20" s="1" t="inlineStr">
         <is>
-          <t>Trap Bar Deadlift</t>
+          <t>Deadlift</t>
         </is>
       </c>
       <c r="C20" s="1" t="inlineStr">
@@ -956,15 +931,19 @@
       </c>
       <c r="D20" s="1" t="inlineStr">
         <is>
-          <t>Quads, Upper back</t>
+          <t>Upper back, Midline</t>
         </is>
       </c>
       <c r="E20" s="1" t="inlineStr">
         <is>
-          <t>everyone</t>
-        </is>
-      </c>
-      <c r="F20" s="1" t="inlineStr"/>
+          <t>2+ years</t>
+        </is>
+      </c>
+      <c r="F20" s="1" t="inlineStr">
+        <is>
+          <t>⚑ straight-bar technical demand; app's own beginner curriculum substitutes Trap Bar instead, but 1+ years is defensible too.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
@@ -974,29 +953,25 @@
       </c>
       <c r="B21" s="1" t="inlineStr">
         <is>
-          <t>RDLs</t>
+          <t>Trap Bar Deadlift</t>
         </is>
       </c>
       <c r="C21" s="1" t="inlineStr">
         <is>
-          <t>Hamstrings, Glutes</t>
+          <t>Hamstrings, Glutes, Low back</t>
         </is>
       </c>
       <c r="D21" s="1" t="inlineStr">
         <is>
-          <t>Upper back, Midline</t>
+          <t>Quads, Upper back</t>
         </is>
       </c>
       <c r="E21" s="1" t="inlineStr">
         <is>
-          <t>1+ years</t>
-        </is>
-      </c>
-      <c r="F21" s="1" t="inlineStr">
-        <is>
-          <t>⚑ hamstring tagged 'avoid' (highest injury rating) + high eccentric demand, but could arguably be 1+ years.</t>
-        </is>
-      </c>
+          <t>everyone</t>
+        </is>
+      </c>
+      <c r="F21" s="1" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -1006,7 +981,7 @@
       </c>
       <c r="B22" s="1" t="inlineStr">
         <is>
-          <t>Single-Leg RDL</t>
+          <t>RDLs</t>
         </is>
       </c>
       <c r="C22" s="1" t="inlineStr">
@@ -1016,15 +991,19 @@
       </c>
       <c r="D22" s="1" t="inlineStr">
         <is>
-          <t>Hips, Midline</t>
+          <t>Upper back, Midline</t>
         </is>
       </c>
       <c r="E22" s="1" t="inlineStr">
         <is>
-          <t>everyone</t>
-        </is>
-      </c>
-      <c r="F22" s="1" t="inlineStr"/>
+          <t>1+ years</t>
+        </is>
+      </c>
+      <c r="F22" s="1" t="inlineStr">
+        <is>
+          <t>⚑ hamstring tagged 'avoid' (highest injury rating) + high eccentric demand, but could arguably be 1+ years.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
@@ -1034,17 +1013,17 @@
       </c>
       <c r="B23" s="1" t="inlineStr">
         <is>
-          <t>Hip Thrusts</t>
+          <t>Single-Leg RDL</t>
         </is>
       </c>
       <c r="C23" s="1" t="inlineStr">
         <is>
-          <t>Glutes</t>
+          <t>Hamstrings, Glutes</t>
         </is>
       </c>
       <c r="D23" s="1" t="inlineStr">
         <is>
-          <t>Hamstrings, Low back</t>
+          <t>Hips, Midline</t>
         </is>
       </c>
       <c r="E23" s="1" t="inlineStr">
@@ -1062,22 +1041,22 @@
       </c>
       <c r="B24" s="1" t="inlineStr">
         <is>
-          <t>Kettlebell Swings</t>
+          <t>Hip Thrusts</t>
         </is>
       </c>
       <c r="C24" s="1" t="inlineStr">
         <is>
-          <t>Glutes, Hamstrings</t>
+          <t>Glutes</t>
         </is>
       </c>
       <c r="D24" s="1" t="inlineStr">
         <is>
-          <t>Midline, Low back</t>
+          <t>Hamstrings, Low back</t>
         </is>
       </c>
       <c r="E24" s="1" t="inlineStr">
         <is>
-          <t>1+ years</t>
+          <t>everyone</t>
         </is>
       </c>
       <c r="F24" s="1" t="inlineStr"/>
@@ -1090,22 +1069,22 @@
       </c>
       <c r="B25" s="1" t="inlineStr">
         <is>
-          <t>Glute Bridge</t>
+          <t>Kettlebell Swings</t>
         </is>
       </c>
       <c r="C25" s="1" t="inlineStr">
         <is>
-          <t>Glutes</t>
+          <t>Glutes, Hamstrings</t>
         </is>
       </c>
       <c r="D25" s="1" t="inlineStr">
         <is>
-          <t>Hamstrings</t>
+          <t>Midline, Low back</t>
         </is>
       </c>
       <c r="E25" s="1" t="inlineStr">
         <is>
-          <t>everyone (regression)</t>
+          <t>1+ years</t>
         </is>
       </c>
       <c r="F25" s="1" t="inlineStr"/>
@@ -1113,27 +1092,27 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>Upper push horizontal</t>
+          <t>Lower hinge</t>
         </is>
       </c>
       <c r="B26" s="1" t="inlineStr">
         <is>
-          <t>Bench Press</t>
+          <t>Glute Bridge</t>
         </is>
       </c>
       <c r="C26" s="1" t="inlineStr">
         <is>
-          <t>Chest</t>
+          <t>Glutes</t>
         </is>
       </c>
       <c r="D26" s="1" t="inlineStr">
         <is>
-          <t>Triceps, Shoulders</t>
+          <t>Hamstrings</t>
         </is>
       </c>
       <c r="E26" s="1" t="inlineStr">
         <is>
-          <t>1+ years</t>
+          <t>everyone (regression)</t>
         </is>
       </c>
       <c r="F26" s="1" t="inlineStr"/>
@@ -1146,17 +1125,17 @@
       </c>
       <c r="B27" s="1" t="inlineStr">
         <is>
-          <t>Incline Bench</t>
+          <t>Bench Press</t>
         </is>
       </c>
       <c r="C27" s="1" t="inlineStr">
         <is>
-          <t>Chest, Shoulders</t>
+          <t>Chest</t>
         </is>
       </c>
       <c r="D27" s="1" t="inlineStr">
         <is>
-          <t>Triceps</t>
+          <t>Triceps, Shoulders</t>
         </is>
       </c>
       <c r="E27" s="1" t="inlineStr">
@@ -1174,17 +1153,17 @@
       </c>
       <c r="B28" s="1" t="inlineStr">
         <is>
-          <t>Close Grip Bench</t>
+          <t>Incline Bench</t>
         </is>
       </c>
       <c r="C28" s="1" t="inlineStr">
         <is>
-          <t>Triceps, Chest</t>
+          <t>Chest, Shoulders</t>
         </is>
       </c>
       <c r="D28" s="1" t="inlineStr">
         <is>
-          <t>Shoulders</t>
+          <t>Triceps</t>
         </is>
       </c>
       <c r="E28" s="1" t="inlineStr">
@@ -1202,22 +1181,22 @@
       </c>
       <c r="B29" s="1" t="inlineStr">
         <is>
-          <t>DB Bench Press</t>
+          <t>Close Grip Bench</t>
         </is>
       </c>
       <c r="C29" s="1" t="inlineStr">
         <is>
-          <t>Chest</t>
+          <t>Triceps, Chest</t>
         </is>
       </c>
       <c r="D29" s="1" t="inlineStr">
         <is>
-          <t>Triceps, Shoulders</t>
+          <t>Shoulders</t>
         </is>
       </c>
       <c r="E29" s="1" t="inlineStr">
         <is>
-          <t>everyone</t>
+          <t>1+ years</t>
         </is>
       </c>
       <c r="F29" s="1" t="inlineStr"/>
@@ -1230,17 +1209,17 @@
       </c>
       <c r="B30" s="1" t="inlineStr">
         <is>
-          <t>Incline DB Bench</t>
+          <t>DB Bench Press</t>
         </is>
       </c>
       <c r="C30" s="1" t="inlineStr">
         <is>
-          <t>Chest, Shoulders</t>
+          <t>Chest</t>
         </is>
       </c>
       <c r="D30" s="1" t="inlineStr">
         <is>
-          <t>Triceps</t>
+          <t>Triceps, Shoulders</t>
         </is>
       </c>
       <c r="E30" s="1" t="inlineStr">
@@ -1258,22 +1237,22 @@
       </c>
       <c r="B31" s="1" t="inlineStr">
         <is>
-          <t>Push-ups</t>
+          <t>Incline DB Bench</t>
         </is>
       </c>
       <c r="C31" s="1" t="inlineStr">
         <is>
-          <t>Chest</t>
+          <t>Chest, Shoulders</t>
         </is>
       </c>
       <c r="D31" s="1" t="inlineStr">
         <is>
-          <t>Triceps, Shoulders, Midline</t>
+          <t>Triceps</t>
         </is>
       </c>
       <c r="E31" s="1" t="inlineStr">
         <is>
-          <t>everyone (regression)</t>
+          <t>everyone</t>
         </is>
       </c>
       <c r="F31" s="1" t="inlineStr"/>
@@ -1286,22 +1265,22 @@
       </c>
       <c r="B32" s="1" t="inlineStr">
         <is>
-          <t>Dips</t>
+          <t>Push-ups</t>
         </is>
       </c>
       <c r="C32" s="1" t="inlineStr">
         <is>
-          <t>Chest, Triceps</t>
+          <t>Chest</t>
         </is>
       </c>
       <c r="D32" s="1" t="inlineStr">
         <is>
-          <t>Shoulders</t>
+          <t>Triceps, Shoulders, Midline</t>
         </is>
       </c>
       <c r="E32" s="1" t="inlineStr">
         <is>
-          <t>1+ years</t>
+          <t>everyone (regression)</t>
         </is>
       </c>
       <c r="F32" s="1" t="inlineStr"/>
@@ -1314,29 +1293,25 @@
       </c>
       <c r="B33" s="1" t="inlineStr">
         <is>
-          <t>Single-Arm DB Bench Press</t>
+          <t>Dips</t>
         </is>
       </c>
       <c r="C33" s="1" t="inlineStr">
         <is>
-          <t>Chest</t>
+          <t>Chest, Triceps</t>
         </is>
       </c>
       <c r="D33" s="1" t="inlineStr">
         <is>
-          <t>Triceps, Midline</t>
+          <t>Shoulders</t>
         </is>
       </c>
       <c r="E33" s="1" t="inlineStr">
         <is>
-          <t>2+ years</t>
-        </is>
-      </c>
-      <c r="F33" s="1" t="inlineStr">
-        <is>
-          <t>anti-rotation control under unilateral load; low stability + caution lateWeek in the source tags.</t>
-        </is>
-      </c>
+          <t>1+ years</t>
+        </is>
+      </c>
+      <c r="F33" s="1" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
@@ -1346,49 +1321,49 @@
       </c>
       <c r="B34" s="1" t="inlineStr">
         <is>
-          <t>Single-Arm DB Floor Press</t>
+          <t>Single-Arm DB Bench Press</t>
         </is>
       </c>
       <c r="C34" s="1" t="inlineStr">
         <is>
-          <t>Chest, Triceps</t>
+          <t>Chest</t>
         </is>
       </c>
       <c r="D34" s="1" t="inlineStr">
         <is>
-          <t>Midline</t>
+          <t>Triceps, Midline</t>
         </is>
       </c>
       <c r="E34" s="1" t="inlineStr">
         <is>
-          <t>1+ years</t>
+          <t>2+ years</t>
         </is>
       </c>
       <c r="F34" s="1" t="inlineStr">
         <is>
-          <t>⚑ shorter ROM protects the shoulder vs. the bench variant, so this may be gentler than the sibling above — could be 'everyone'.</t>
+          <t>anti-rotation control under unilateral load; low stability + caution lateWeek in the source tags.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>Upper push vertical</t>
+          <t>Upper push horizontal</t>
         </is>
       </c>
       <c r="B35" s="1" t="inlineStr">
         <is>
-          <t>Overhead Press</t>
+          <t>Single-Arm DB Floor Press</t>
         </is>
       </c>
       <c r="C35" s="1" t="inlineStr">
         <is>
-          <t>Shoulders</t>
+          <t>Chest, Triceps</t>
         </is>
       </c>
       <c r="D35" s="1" t="inlineStr">
         <is>
-          <t>Triceps, Midline, Traps</t>
+          <t>Midline</t>
         </is>
       </c>
       <c r="E35" s="1" t="inlineStr">
@@ -1396,7 +1371,11 @@
           <t>1+ years</t>
         </is>
       </c>
-      <c r="F35" s="1" t="inlineStr"/>
+      <c r="F35" s="1" t="inlineStr">
+        <is>
+          <t>⚑ shorter ROM protects the shoulder vs. the bench variant, so this may be gentler than the sibling above — could be 'everyone'.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
@@ -1406,17 +1385,17 @@
       </c>
       <c r="B36" s="1" t="inlineStr">
         <is>
-          <t>Landmine Press</t>
+          <t>Overhead Press</t>
         </is>
       </c>
       <c r="C36" s="1" t="inlineStr">
         <is>
-          <t>Shoulders, Chest</t>
+          <t>Shoulders</t>
         </is>
       </c>
       <c r="D36" s="1" t="inlineStr">
         <is>
-          <t>Triceps</t>
+          <t>Triceps, Midline, Traps</t>
         </is>
       </c>
       <c r="E36" s="1" t="inlineStr">
@@ -1424,11 +1403,7 @@
           <t>1+ years</t>
         </is>
       </c>
-      <c r="F36" s="1" t="inlineStr">
-        <is>
-          <t>⚑ SAFE injury profile suggests this could reasonably be 'everyone'; not in the app's own beginner curriculum, so left at 1+ years.</t>
-        </is>
-      </c>
+      <c r="F36" s="1" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
@@ -1438,12 +1413,12 @@
       </c>
       <c r="B37" s="1" t="inlineStr">
         <is>
-          <t>DB Shoulder Press</t>
+          <t>Landmine Press</t>
         </is>
       </c>
       <c r="C37" s="1" t="inlineStr">
         <is>
-          <t>Shoulders</t>
+          <t>Shoulders, Chest</t>
         </is>
       </c>
       <c r="D37" s="1" t="inlineStr">
@@ -1456,7 +1431,11 @@
           <t>1+ years</t>
         </is>
       </c>
-      <c r="F37" s="1" t="inlineStr"/>
+      <c r="F37" s="1" t="inlineStr">
+        <is>
+          <t>⚑ SAFE injury profile suggests this could reasonably be 'everyone'; not in the app's own beginner curriculum, so left at 1+ years.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
@@ -1466,7 +1445,7 @@
       </c>
       <c r="B38" s="1" t="inlineStr">
         <is>
-          <t>Seated DB Press</t>
+          <t>DB Shoulder Press</t>
         </is>
       </c>
       <c r="C38" s="1" t="inlineStr">
@@ -1481,7 +1460,7 @@
       </c>
       <c r="E38" s="1" t="inlineStr">
         <is>
-          <t>everyone</t>
+          <t>1+ years</t>
         </is>
       </c>
       <c r="F38" s="1" t="inlineStr"/>
@@ -1494,7 +1473,7 @@
       </c>
       <c r="B39" s="1" t="inlineStr">
         <is>
-          <t>Half-Kneeling Single-Arm Overhead Press</t>
+          <t>Seated DB Press</t>
         </is>
       </c>
       <c r="C39" s="1" t="inlineStr">
@@ -1504,7 +1483,7 @@
       </c>
       <c r="D39" s="1" t="inlineStr">
         <is>
-          <t>Triceps, Midline</t>
+          <t>Triceps</t>
         </is>
       </c>
       <c r="E39" s="1" t="inlineStr">
@@ -1522,22 +1501,22 @@
       </c>
       <c r="B40" s="1" t="inlineStr">
         <is>
-          <t>Explosive Landmine Press</t>
+          <t>Half-Kneeling Single-Arm Overhead Press</t>
         </is>
       </c>
       <c r="C40" s="1" t="inlineStr">
         <is>
-          <t>Shoulders, Chest</t>
+          <t>Shoulders</t>
         </is>
       </c>
       <c r="D40" s="1" t="inlineStr">
         <is>
-          <t>Triceps</t>
+          <t>Triceps, Midline</t>
         </is>
       </c>
       <c r="E40" s="1" t="inlineStr">
         <is>
-          <t>1+ years</t>
+          <t>everyone</t>
         </is>
       </c>
       <c r="F40" s="1" t="inlineStr"/>
@@ -1550,57 +1529,57 @@
       </c>
       <c r="B41" s="1" t="inlineStr">
         <is>
-          <t>Z-Press</t>
+          <t>Explosive Landmine Press</t>
         </is>
       </c>
       <c r="C41" s="1" t="inlineStr">
         <is>
-          <t>Shoulders</t>
+          <t>Shoulders, Chest</t>
         </is>
       </c>
       <c r="D41" s="1" t="inlineStr">
         <is>
-          <t>Triceps, Midline</t>
+          <t>Triceps</t>
         </is>
       </c>
       <c r="E41" s="1" t="inlineStr">
         <is>
-          <t>2+ years</t>
-        </is>
-      </c>
-      <c r="F41" s="1" t="inlineStr">
-        <is>
-          <t>⚑ no leg drive raises the midline/shoulder stability demand, but could be 1+ years.</t>
-        </is>
-      </c>
+          <t>1+ years</t>
+        </is>
+      </c>
+      <c r="F41" s="1" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>Upper pull horizontal</t>
+          <t>Upper push vertical</t>
         </is>
       </c>
       <c r="B42" s="1" t="inlineStr">
         <is>
-          <t>Barbell Row</t>
+          <t>Z-Press</t>
         </is>
       </c>
       <c r="C42" s="1" t="inlineStr">
         <is>
-          <t>Upper back, Lats</t>
+          <t>Shoulders</t>
         </is>
       </c>
       <c r="D42" s="1" t="inlineStr">
         <is>
-          <t>Biceps, Midline</t>
+          <t>Triceps, Midline</t>
         </is>
       </c>
       <c r="E42" s="1" t="inlineStr">
         <is>
-          <t>1+ years</t>
-        </is>
-      </c>
-      <c r="F42" s="1" t="inlineStr"/>
+          <t>2+ years</t>
+        </is>
+      </c>
+      <c r="F42" s="1" t="inlineStr">
+        <is>
+          <t>⚑ no leg drive raises the midline/shoulder stability demand, but could be 1+ years.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
@@ -1610,7 +1589,7 @@
       </c>
       <c r="B43" s="1" t="inlineStr">
         <is>
-          <t>Chest Supported Row</t>
+          <t>Barbell Row</t>
         </is>
       </c>
       <c r="C43" s="1" t="inlineStr">
@@ -1620,19 +1599,15 @@
       </c>
       <c r="D43" s="1" t="inlineStr">
         <is>
-          <t>Biceps</t>
+          <t>Biceps, Midline</t>
         </is>
       </c>
       <c r="E43" s="1" t="inlineStr">
         <is>
-          <t>everyone</t>
-        </is>
-      </c>
-      <c r="F43" s="1" t="inlineStr">
-        <is>
-          <t>⚑ not in the app's literal beginner list (Single-Arm DB Row is), but SAFE injury profile reads as beginner-friendly — could be 1+ years instead.</t>
-        </is>
-      </c>
+          <t>1+ years</t>
+        </is>
+      </c>
+      <c r="F43" s="1" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
@@ -1642,7 +1617,7 @@
       </c>
       <c r="B44" s="1" t="inlineStr">
         <is>
-          <t>Single-Arm DB Row</t>
+          <t>Chest Supported Row</t>
         </is>
       </c>
       <c r="C44" s="1" t="inlineStr">
@@ -1652,7 +1627,7 @@
       </c>
       <c r="D44" s="1" t="inlineStr">
         <is>
-          <t>Biceps, Midline</t>
+          <t>Biceps</t>
         </is>
       </c>
       <c r="E44" s="1" t="inlineStr">
@@ -1660,7 +1635,11 @@
           <t>everyone</t>
         </is>
       </c>
-      <c r="F44" s="1" t="inlineStr"/>
+      <c r="F44" s="1" t="inlineStr">
+        <is>
+          <t>⚑ not in the app's literal beginner list (Single-Arm DB Row is), but SAFE injury profile reads as beginner-friendly — could be 1+ years instead.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
@@ -1670,7 +1649,7 @@
       </c>
       <c r="B45" s="1" t="inlineStr">
         <is>
-          <t>Seated Cable Row</t>
+          <t>Single-Arm DB Row</t>
         </is>
       </c>
       <c r="C45" s="1" t="inlineStr">
@@ -1680,7 +1659,7 @@
       </c>
       <c r="D45" s="1" t="inlineStr">
         <is>
-          <t>Biceps</t>
+          <t>Biceps, Midline</t>
         </is>
       </c>
       <c r="E45" s="1" t="inlineStr">
@@ -1698,17 +1677,17 @@
       </c>
       <c r="B46" s="1" t="inlineStr">
         <is>
-          <t>Face Pull</t>
+          <t>Seated Cable Row</t>
         </is>
       </c>
       <c r="C46" s="1" t="inlineStr">
         <is>
-          <t>Shoulders, Upper back</t>
+          <t>Upper back, Lats</t>
         </is>
       </c>
       <c r="D46" s="1" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Biceps</t>
         </is>
       </c>
       <c r="E46" s="1" t="inlineStr">
@@ -1726,7 +1705,7 @@
       </c>
       <c r="B47" s="1" t="inlineStr">
         <is>
-          <t>Rear Delt Fly</t>
+          <t>Face Pull</t>
         </is>
       </c>
       <c r="C47" s="1" t="inlineStr">
@@ -1754,12 +1733,12 @@
       </c>
       <c r="B48" s="1" t="inlineStr">
         <is>
-          <t>Band Pull-Apart</t>
+          <t>Rear Delt Fly</t>
         </is>
       </c>
       <c r="C48" s="1" t="inlineStr">
         <is>
-          <t>Upper back, Shoulders</t>
+          <t>Shoulders, Upper back</t>
         </is>
       </c>
       <c r="D48" s="1" t="inlineStr">
@@ -1777,27 +1756,27 @@
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>Upper pull vertical</t>
+          <t>Upper pull horizontal</t>
         </is>
       </c>
       <c r="B49" s="1" t="inlineStr">
         <is>
-          <t>Pull-Ups</t>
+          <t>Band Pull-Apart</t>
         </is>
       </c>
       <c r="C49" s="1" t="inlineStr">
         <is>
-          <t>Lats, Upper back</t>
+          <t>Upper back, Shoulders</t>
         </is>
       </c>
       <c r="D49" s="1" t="inlineStr">
         <is>
-          <t>Biceps</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E49" s="1" t="inlineStr">
         <is>
-          <t>1+ years</t>
+          <t>everyone</t>
         </is>
       </c>
       <c r="F49" s="1" t="inlineStr"/>
@@ -1810,17 +1789,17 @@
       </c>
       <c r="B50" s="1" t="inlineStr">
         <is>
-          <t>Chin-Ups</t>
+          <t>Pull-Ups</t>
         </is>
       </c>
       <c r="C50" s="1" t="inlineStr">
         <is>
-          <t>Lats, Biceps</t>
+          <t>Lats, Upper back</t>
         </is>
       </c>
       <c r="D50" s="1" t="inlineStr">
         <is>
-          <t>Upper back</t>
+          <t>Biceps</t>
         </is>
       </c>
       <c r="E50" s="1" t="inlineStr">
@@ -1838,22 +1817,22 @@
       </c>
       <c r="B51" s="1" t="inlineStr">
         <is>
-          <t>Lat Pulldown</t>
+          <t>Chin-Ups</t>
         </is>
       </c>
       <c r="C51" s="1" t="inlineStr">
         <is>
-          <t>Lats, Upper back</t>
+          <t>Lats, Biceps</t>
         </is>
       </c>
       <c r="D51" s="1" t="inlineStr">
         <is>
-          <t>Biceps</t>
+          <t>Upper back</t>
         </is>
       </c>
       <c r="E51" s="1" t="inlineStr">
         <is>
-          <t>everyone</t>
+          <t>1+ years</t>
         </is>
       </c>
       <c r="F51" s="1" t="inlineStr"/>
@@ -1866,7 +1845,7 @@
       </c>
       <c r="B52" s="1" t="inlineStr">
         <is>
-          <t>Neutral-Grip Pulldown</t>
+          <t>Lat Pulldown</t>
         </is>
       </c>
       <c r="C52" s="1" t="inlineStr">
@@ -1894,17 +1873,17 @@
       </c>
       <c r="B53" s="1" t="inlineStr">
         <is>
-          <t>Single-Arm Lat Pulldown</t>
+          <t>Neutral-Grip Pulldown</t>
         </is>
       </c>
       <c r="C53" s="1" t="inlineStr">
         <is>
-          <t>Lats</t>
+          <t>Lats, Upper back</t>
         </is>
       </c>
       <c r="D53" s="1" t="inlineStr">
         <is>
-          <t>Biceps, Upper back, Midline</t>
+          <t>Biceps</t>
         </is>
       </c>
       <c r="E53" s="1" t="inlineStr">
@@ -1912,31 +1891,27 @@
           <t>everyone</t>
         </is>
       </c>
-      <c r="F53" s="1" t="inlineStr">
-        <is>
-          <t>MERGED per Sam: absorbs Single-Arm Pulldown (alias). Keeping this name + cue — say the word to flip the name.</t>
-        </is>
-      </c>
+      <c r="F53" s="1" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>Lower plyometric</t>
+          <t>Upper pull vertical</t>
         </is>
       </c>
       <c r="B54" s="1" t="inlineStr">
         <is>
-          <t>Box Jumps</t>
+          <t>Single-Arm Lat Pulldown</t>
         </is>
       </c>
       <c r="C54" s="1" t="inlineStr">
         <is>
-          <t>Quads, Glutes</t>
+          <t>Lats</t>
         </is>
       </c>
       <c r="D54" s="1" t="inlineStr">
         <is>
-          <t>Calves</t>
+          <t>Biceps, Upper back, Midline</t>
         </is>
       </c>
       <c r="E54" s="1" t="inlineStr">
@@ -1944,7 +1919,11 @@
           <t>everyone</t>
         </is>
       </c>
-      <c r="F54" s="1" t="inlineStr"/>
+      <c r="F54" s="1" t="inlineStr">
+        <is>
+          <t>MERGED per Sam: absorbs Single-Arm Pulldown (alias). Keeping this name + cue — say the word to flip the name.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
@@ -1954,7 +1933,7 @@
       </c>
       <c r="B55" s="1" t="inlineStr">
         <is>
-          <t>Broad Jumps</t>
+          <t>Box Jumps</t>
         </is>
       </c>
       <c r="C55" s="1" t="inlineStr">
@@ -1964,12 +1943,12 @@
       </c>
       <c r="D55" s="1" t="inlineStr">
         <is>
-          <t>Hamstrings, Calves</t>
+          <t>Calves</t>
         </is>
       </c>
       <c r="E55" s="1" t="inlineStr">
         <is>
-          <t>2+ years</t>
+          <t>everyone</t>
         </is>
       </c>
       <c r="F55" s="1" t="inlineStr"/>
@@ -1982,7 +1961,7 @@
       </c>
       <c r="B56" s="1" t="inlineStr">
         <is>
-          <t>Jump Squats</t>
+          <t>Broad Jumps</t>
         </is>
       </c>
       <c r="C56" s="1" t="inlineStr">
@@ -1992,12 +1971,12 @@
       </c>
       <c r="D56" s="1" t="inlineStr">
         <is>
-          <t>Calves</t>
+          <t>Hamstrings, Calves</t>
         </is>
       </c>
       <c r="E56" s="1" t="inlineStr">
         <is>
-          <t>1+ years</t>
+          <t>2+ years</t>
         </is>
       </c>
       <c r="F56" s="1" t="inlineStr"/>
@@ -2010,7 +1989,7 @@
       </c>
       <c r="B57" s="1" t="inlineStr">
         <is>
-          <t>Lateral Bounds</t>
+          <t>Jump Squats</t>
         </is>
       </c>
       <c r="C57" s="1" t="inlineStr">
@@ -2020,19 +1999,15 @@
       </c>
       <c r="D57" s="1" t="inlineStr">
         <is>
-          <t>Groin, Calves</t>
+          <t>Calves</t>
         </is>
       </c>
       <c r="E57" s="1" t="inlineStr">
         <is>
-          <t>2+ years</t>
-        </is>
-      </c>
-      <c r="F57" s="1" t="inlineStr">
-        <is>
-          <t>⚑ adductor tagged 'avoid' (highest injury rating) for a unilateral lateral landing — genuinely borderline vs. advanced-only.</t>
-        </is>
-      </c>
+          <t>1+ years</t>
+        </is>
+      </c>
+      <c r="F57" s="1" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
@@ -2042,7 +2017,7 @@
       </c>
       <c r="B58" s="1" t="inlineStr">
         <is>
-          <t>Depth Jumps</t>
+          <t>Lateral Bounds</t>
         </is>
       </c>
       <c r="C58" s="1" t="inlineStr">
@@ -2052,47 +2027,51 @@
       </c>
       <c r="D58" s="1" t="inlineStr">
         <is>
-          <t>Calves, Hamstrings</t>
+          <t>Groin, Calves</t>
         </is>
       </c>
       <c r="E58" s="1" t="inlineStr">
         <is>
-          <t>advanced only</t>
+          <t>2+ years</t>
         </is>
       </c>
       <c r="F58" s="1" t="inlineStr">
         <is>
-          <t>knee + ankle both tagged 'avoid'; classic high eccentric-overload drop-jump reserved for qualified athletes.</t>
+          <t>⚑ adductor tagged 'avoid' (highest injury rating) for a unilateral lateral landing — genuinely borderline vs. advanced-only.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>Carries</t>
+          <t>Lower plyometric</t>
         </is>
       </c>
       <c r="B59" s="1" t="inlineStr">
         <is>
-          <t>Farmer Carry</t>
+          <t>Depth Jumps</t>
         </is>
       </c>
       <c r="C59" s="1" t="inlineStr">
         <is>
-          <t>Midline, Upper back</t>
+          <t>Quads, Glutes</t>
         </is>
       </c>
       <c r="D59" s="1" t="inlineStr">
         <is>
-          <t>Shoulders</t>
+          <t>Calves, Hamstrings</t>
         </is>
       </c>
       <c r="E59" s="1" t="inlineStr">
         <is>
-          <t>everyone</t>
-        </is>
-      </c>
-      <c r="F59" s="1" t="inlineStr"/>
+          <t>advanced only</t>
+        </is>
+      </c>
+      <c r="F59" s="1" t="inlineStr">
+        <is>
+          <t>knee + ankle both tagged 'avoid'; classic high eccentric-overload drop-jump reserved for qualified athletes.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
@@ -2102,7 +2081,7 @@
       </c>
       <c r="B60" s="1" t="inlineStr">
         <is>
-          <t>Bear Carry</t>
+          <t>Farmer Carry</t>
         </is>
       </c>
       <c r="C60" s="1" t="inlineStr">
@@ -2117,7 +2096,7 @@
       </c>
       <c r="E60" s="1" t="inlineStr">
         <is>
-          <t>2+ years</t>
+          <t>everyone</t>
         </is>
       </c>
       <c r="F60" s="1" t="inlineStr"/>
@@ -2130,22 +2109,22 @@
       </c>
       <c r="B61" s="1" t="inlineStr">
         <is>
-          <t>Suitcase Carry</t>
+          <t>Bear Carry</t>
         </is>
       </c>
       <c r="C61" s="1" t="inlineStr">
         <is>
-          <t>Midline</t>
+          <t>Midline, Upper back</t>
         </is>
       </c>
       <c r="D61" s="1" t="inlineStr">
         <is>
-          <t>Upper back, Shoulders</t>
+          <t>Shoulders</t>
         </is>
       </c>
       <c r="E61" s="1" t="inlineStr">
         <is>
-          <t>Everyone</t>
+          <t>2+ years</t>
         </is>
       </c>
       <c r="F61" s="1" t="inlineStr"/>
@@ -2158,22 +2137,22 @@
       </c>
       <c r="B62" s="1" t="inlineStr">
         <is>
-          <t>Overhead Carry</t>
+          <t>Suitcase Carry</t>
         </is>
       </c>
       <c r="C62" s="1" t="inlineStr">
         <is>
-          <t>Shoulders, Midline</t>
+          <t>Midline</t>
         </is>
       </c>
       <c r="D62" s="1" t="inlineStr">
         <is>
-          <t>Upper back</t>
+          <t>Upper back, Shoulders</t>
         </is>
       </c>
       <c r="E62" s="1" t="inlineStr">
         <is>
-          <t>2+ years</t>
+          <t>everyone</t>
         </is>
       </c>
       <c r="F62" s="1" t="inlineStr"/>
@@ -2181,27 +2160,27 @@
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>Accessories upper</t>
+          <t>Carries</t>
         </is>
       </c>
       <c r="B63" s="1" t="inlineStr">
         <is>
-          <t>Shrugs</t>
+          <t>Overhead Carry</t>
         </is>
       </c>
       <c r="C63" s="1" t="inlineStr">
         <is>
+          <t>Shoulders, Midline</t>
+        </is>
+      </c>
+      <c r="D63" s="1" t="inlineStr">
+        <is>
           <t>Upper back</t>
         </is>
       </c>
-      <c r="D63" s="1" t="inlineStr">
-        <is>
-          <t>Traps</t>
-        </is>
-      </c>
       <c r="E63" s="1" t="inlineStr">
         <is>
-          <t>everyone</t>
+          <t>2+ years</t>
         </is>
       </c>
       <c r="F63" s="1" t="inlineStr"/>
@@ -2214,29 +2193,25 @@
       </c>
       <c r="B64" s="1" t="inlineStr">
         <is>
-          <t>Skull Crushers</t>
+          <t>Shrugs</t>
         </is>
       </c>
       <c r="C64" s="1" t="inlineStr">
         <is>
-          <t>Triceps</t>
+          <t>Upper back</t>
         </is>
       </c>
       <c r="D64" s="1" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Traps</t>
         </is>
       </c>
       <c r="E64" s="1" t="inlineStr">
         <is>
-          <t>Everyone</t>
-        </is>
-      </c>
-      <c r="F64" s="1" t="inlineStr">
-        <is>
-          <t>elbow-strain-prone lockout under barbell load vs. the dumbbell version.</t>
-        </is>
-      </c>
+          <t>everyone</t>
+        </is>
+      </c>
+      <c r="F64" s="1" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
@@ -2246,12 +2221,12 @@
       </c>
       <c r="B65" s="1" t="inlineStr">
         <is>
-          <t>Bicep Curl (Barbell)</t>
+          <t>Skull Crushers</t>
         </is>
       </c>
       <c r="C65" s="1" t="inlineStr">
         <is>
-          <t>Biceps</t>
+          <t>Triceps</t>
         </is>
       </c>
       <c r="D65" s="1" t="inlineStr">
@@ -2264,7 +2239,11 @@
           <t>everyone</t>
         </is>
       </c>
-      <c r="F65" s="1" t="inlineStr"/>
+      <c r="F65" s="1" t="inlineStr">
+        <is>
+          <t>elbow-strain-prone lockout under barbell load vs. the dumbbell version.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
@@ -2274,7 +2253,7 @@
       </c>
       <c r="B66" s="1" t="inlineStr">
         <is>
-          <t>Bicep Curl (Dumbbell)</t>
+          <t>Bicep Curl (Barbell)</t>
         </is>
       </c>
       <c r="C66" s="1" t="inlineStr">
@@ -2302,7 +2281,7 @@
       </c>
       <c r="B67" s="1" t="inlineStr">
         <is>
-          <t>Hammer Curl</t>
+          <t>Bicep Curl (Dumbbell)</t>
         </is>
       </c>
       <c r="C67" s="1" t="inlineStr">
@@ -2330,7 +2309,7 @@
       </c>
       <c r="B68" s="1" t="inlineStr">
         <is>
-          <t>Incline Dumbbell Curl</t>
+          <t>Hammer Curl</t>
         </is>
       </c>
       <c r="C68" s="1" t="inlineStr">
@@ -2358,7 +2337,7 @@
       </c>
       <c r="B69" s="1" t="inlineStr">
         <is>
-          <t>Lying Dumbbell Curl</t>
+          <t>Incline Dumbbell Curl</t>
         </is>
       </c>
       <c r="C69" s="1" t="inlineStr">
@@ -2386,7 +2365,7 @@
       </c>
       <c r="B70" s="1" t="inlineStr">
         <is>
-          <t>Banded Bicep Curl</t>
+          <t>Lying Dumbbell Curl</t>
         </is>
       </c>
       <c r="C70" s="1" t="inlineStr">
@@ -2401,14 +2380,10 @@
       </c>
       <c r="E70" s="1" t="inlineStr">
         <is>
-          <t>everyone (regression)</t>
-        </is>
-      </c>
-      <c r="F70" s="1" t="inlineStr">
-        <is>
-          <t>Regression per Sam 2026-07-25: above-beginner doesn't need banded curls</t>
-        </is>
-      </c>
+          <t>everyone</t>
+        </is>
+      </c>
+      <c r="F70" s="1" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
@@ -2418,7 +2393,7 @@
       </c>
       <c r="B71" s="1" t="inlineStr">
         <is>
-          <t>Concentration Curl</t>
+          <t>Banded Bicep Curl</t>
         </is>
       </c>
       <c r="C71" s="1" t="inlineStr">
@@ -2433,10 +2408,14 @@
       </c>
       <c r="E71" s="1" t="inlineStr">
         <is>
-          <t>everyone</t>
-        </is>
-      </c>
-      <c r="F71" s="1" t="inlineStr"/>
+          <t>everyone (regression)</t>
+        </is>
+      </c>
+      <c r="F71" s="1" t="inlineStr">
+        <is>
+          <t>Regression per Sam 2026-07-25: above-beginner doesn't need banded curls</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
@@ -2446,12 +2425,12 @@
       </c>
       <c r="B72" s="1" t="inlineStr">
         <is>
-          <t>Tricep Pushdown</t>
+          <t>Concentration Curl</t>
         </is>
       </c>
       <c r="C72" s="1" t="inlineStr">
         <is>
-          <t>Triceps</t>
+          <t>Biceps</t>
         </is>
       </c>
       <c r="D72" s="1" t="inlineStr">
@@ -2474,7 +2453,7 @@
       </c>
       <c r="B73" s="1" t="inlineStr">
         <is>
-          <t>Banded Tricep Pushdown</t>
+          <t>Tricep Pushdown</t>
         </is>
       </c>
       <c r="C73" s="1" t="inlineStr">
@@ -2502,7 +2481,7 @@
       </c>
       <c r="B74" s="1" t="inlineStr">
         <is>
-          <t>Overhead Tricep Extension</t>
+          <t>Banded Tricep Pushdown</t>
         </is>
       </c>
       <c r="C74" s="1" t="inlineStr">
@@ -2530,7 +2509,7 @@
       </c>
       <c r="B75" s="1" t="inlineStr">
         <is>
-          <t>Dumbbell Skull Crusher</t>
+          <t>Overhead Tricep Extension</t>
         </is>
       </c>
       <c r="C75" s="1" t="inlineStr">
@@ -2548,11 +2527,7 @@
           <t>everyone</t>
         </is>
       </c>
-      <c r="F75" s="1" t="inlineStr">
-        <is>
-          <t>same elbow lockout concern as the barbell version, lighter load.</t>
-        </is>
-      </c>
+      <c r="F75" s="1" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
@@ -2562,7 +2537,7 @@
       </c>
       <c r="B76" s="1" t="inlineStr">
         <is>
-          <t>Dumbbell Kickback</t>
+          <t>Dumbbell Skull Crusher</t>
         </is>
       </c>
       <c r="C76" s="1" t="inlineStr">
@@ -2580,7 +2555,11 @@
           <t>everyone</t>
         </is>
       </c>
-      <c r="F76" s="1" t="inlineStr"/>
+      <c r="F76" s="1" t="inlineStr">
+        <is>
+          <t>same elbow lockout concern as the barbell version, lighter load.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
@@ -2590,7 +2569,7 @@
       </c>
       <c r="B77" s="1" t="inlineStr">
         <is>
-          <t>Tricep Circuit (Dirty 30)</t>
+          <t>Dumbbell Kickback</t>
         </is>
       </c>
       <c r="C77" s="1" t="inlineStr">
@@ -2618,12 +2597,12 @@
       </c>
       <c r="B78" s="1" t="inlineStr">
         <is>
-          <t>Lateral Raise</t>
+          <t>Tricep Circuit (Dirty 30)</t>
         </is>
       </c>
       <c r="C78" s="1" t="inlineStr">
         <is>
-          <t>Shoulders</t>
+          <t>Triceps</t>
         </is>
       </c>
       <c r="D78" s="1" t="inlineStr">
@@ -2646,12 +2625,12 @@
       </c>
       <c r="B79" s="1" t="inlineStr">
         <is>
-          <t>Incline Y Raise</t>
+          <t>Lateral Raise</t>
         </is>
       </c>
       <c r="C79" s="1" t="inlineStr">
         <is>
-          <t>Shoulders, Upper back</t>
+          <t>Shoulders</t>
         </is>
       </c>
       <c r="D79" s="1" t="inlineStr">
@@ -2674,12 +2653,12 @@
       </c>
       <c r="B80" s="1" t="inlineStr">
         <is>
-          <t>Single-Arm Shrug</t>
+          <t>Incline Y Raise</t>
         </is>
       </c>
       <c r="C80" s="1" t="inlineStr">
         <is>
-          <t>Upper back</t>
+          <t>Shoulders, Upper back</t>
         </is>
       </c>
       <c r="D80" s="1" t="inlineStr">
@@ -2697,17 +2676,17 @@
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>Accessories lower</t>
+          <t>Accessories upper</t>
         </is>
       </c>
       <c r="B81" s="1" t="inlineStr">
         <is>
-          <t>Nordic Lower</t>
+          <t>Single-Arm Shrug</t>
         </is>
       </c>
       <c r="C81" s="1" t="inlineStr">
         <is>
-          <t>Hamstrings</t>
+          <t>Upper back</t>
         </is>
       </c>
       <c r="D81" s="1" t="inlineStr">
@@ -2717,14 +2696,10 @@
       </c>
       <c r="E81" s="1" t="inlineStr">
         <is>
-          <t>2+ years</t>
-        </is>
-      </c>
-      <c r="F81" s="1" t="inlineStr">
-        <is>
-          <t>hamstring tagged 'avoid'; classic high-eccentric-overload movement — standard guidance is an eccentric-strength base before loading this.</t>
-        </is>
-      </c>
+          <t>everyone</t>
+        </is>
+      </c>
+      <c r="F81" s="1" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
@@ -2734,7 +2709,7 @@
       </c>
       <c r="B82" s="1" t="inlineStr">
         <is>
-          <t>Hamstring Curl</t>
+          <t>Nordic Lower</t>
         </is>
       </c>
       <c r="C82" s="1" t="inlineStr">
@@ -2749,10 +2724,14 @@
       </c>
       <c r="E82" s="1" t="inlineStr">
         <is>
-          <t>everyone</t>
-        </is>
-      </c>
-      <c r="F82" s="1" t="inlineStr"/>
+          <t>2+ years</t>
+        </is>
+      </c>
+      <c r="F82" s="1" t="inlineStr">
+        <is>
+          <t>hamstring tagged 'avoid'; classic high-eccentric-overload movement — standard guidance is an eccentric-strength base before loading this.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
@@ -2762,12 +2741,12 @@
       </c>
       <c r="B83" s="1" t="inlineStr">
         <is>
-          <t>Leg Extension</t>
+          <t>Hamstring Curl</t>
         </is>
       </c>
       <c r="C83" s="1" t="inlineStr">
         <is>
-          <t>Quads</t>
+          <t>Hamstrings</t>
         </is>
       </c>
       <c r="D83" s="1" t="inlineStr">
@@ -2790,12 +2769,12 @@
       </c>
       <c r="B84" s="1" t="inlineStr">
         <is>
-          <t>Calf Raises</t>
+          <t>Leg Extension</t>
         </is>
       </c>
       <c r="C84" s="1" t="inlineStr">
         <is>
-          <t>Calves</t>
+          <t>Quads</t>
         </is>
       </c>
       <c r="D84" s="1" t="inlineStr">
@@ -2818,7 +2797,7 @@
       </c>
       <c r="B85" s="1" t="inlineStr">
         <is>
-          <t>Tib Raises</t>
+          <t>Calf Raises</t>
         </is>
       </c>
       <c r="C85" s="1" t="inlineStr">
@@ -2836,11 +2815,7 @@
           <t>everyone</t>
         </is>
       </c>
-      <c r="F85" s="1" t="inlineStr">
-        <is>
-          <t>targets tibialis anterior (shin) specifically; 'Calves' is the closest plain-language bucket.</t>
-        </is>
-      </c>
+      <c r="F85" s="1" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
@@ -2850,25 +2825,29 @@
       </c>
       <c r="B86" s="1" t="inlineStr">
         <is>
-          <t>Single-Leg Hip Thrust</t>
+          <t>Tib Raises</t>
         </is>
       </c>
       <c r="C86" s="1" t="inlineStr">
         <is>
-          <t>Glutes</t>
+          <t>Calves</t>
         </is>
       </c>
       <c r="D86" s="1" t="inlineStr">
         <is>
-          <t>Hamstrings</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E86" s="1" t="inlineStr">
         <is>
-          <t>everyone (regression)</t>
-        </is>
-      </c>
-      <c r="F86" s="1" t="inlineStr"/>
+          <t>everyone</t>
+        </is>
+      </c>
+      <c r="F86" s="1" t="inlineStr">
+        <is>
+          <t>targets tibialis anterior (shin) specifically; 'Calves' is the closest plain-language bucket.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
@@ -2878,142 +2857,142 @@
       </c>
       <c r="B87" s="1" t="inlineStr">
         <is>
-          <t>Back Extension</t>
+          <t>Single-Leg Hip Thrust</t>
         </is>
       </c>
       <c r="C87" s="1" t="inlineStr">
         <is>
-          <t>Hamstrings, Glutes, Low back</t>
+          <t>Glutes</t>
         </is>
       </c>
       <c r="D87" s="1" t="inlineStr">
         <is>
-          <t>Midline</t>
+          <t>Hamstrings</t>
         </is>
       </c>
       <c r="E87" s="1" t="inlineStr">
         <is>
-          <t>everyone</t>
-        </is>
-      </c>
-      <c r="F87" s="1" t="inlineStr">
-        <is>
-          <t>targets lower-back extensors specifically; 'Midline' is the closest plain-language bucket.</t>
-        </is>
-      </c>
+          <t>everyone (regression)</t>
+        </is>
+      </c>
+      <c r="F87" s="1" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>Upper pull vertical</t>
+          <t>Accessories lower</t>
         </is>
       </c>
       <c r="B88" s="1" t="inlineStr">
         <is>
-          <t>Chin-Up Negative (Slow)</t>
+          <t>Back Extension</t>
         </is>
       </c>
       <c r="C88" s="1" t="inlineStr">
         <is>
-          <t>Lats, Biceps</t>
+          <t>Hamstrings, Glutes, Low back</t>
         </is>
       </c>
       <c r="D88" s="1" t="inlineStr">
         <is>
-          <t>Upper back, midline</t>
+          <t>Midline</t>
         </is>
       </c>
       <c r="E88" s="1" t="inlineStr">
         <is>
-          <t>everyone (regression)</t>
+          <t>everyone</t>
         </is>
       </c>
       <c r="F88" s="1" t="inlineStr">
         <is>
-          <t>Moved per Sam from Arms—biceps (it lived in the biceps pool; now vertical pull).</t>
+          <t>targets lower-back extensors specifically; 'Midline' is the closest plain-language bucket.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>Shoulders</t>
+          <t>Upper pull vertical</t>
         </is>
       </c>
       <c r="B89" s="1" t="inlineStr">
         <is>
-          <t>Cable Face Pull</t>
+          <t>Chin-Up Negative (Slow)</t>
         </is>
       </c>
       <c r="C89" s="1" t="inlineStr">
         <is>
-          <t>Shoulders, Upper back</t>
+          <t>Lats, Biceps</t>
         </is>
       </c>
       <c r="D89" s="1" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Upper back, Midline</t>
         </is>
       </c>
       <c r="E89" s="1" t="inlineStr">
         <is>
-          <t>everyone</t>
-        </is>
-      </c>
-      <c r="F89" s="1" t="inlineStr"/>
+          <t>everyone (regression)</t>
+        </is>
+      </c>
+      <c r="F89" s="1" t="inlineStr">
+        <is>
+          <t>Moved per Sam from Arms—biceps (it lived in the biceps pool; now vertical pull).</t>
+        </is>
+      </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="inlineStr">
-        <is>
-          <t>Upper back</t>
-        </is>
-      </c>
-      <c r="B90" s="1" t="inlineStr">
-        <is>
-          <t>Chest-Supported DB Row</t>
-        </is>
-      </c>
-      <c r="C90" s="1" t="inlineStr">
-        <is>
-          <t>Upper back, Lats</t>
-        </is>
-      </c>
-      <c r="D90" s="1" t="inlineStr">
-        <is>
-          <t>Biceps</t>
-        </is>
-      </c>
-      <c r="E90" s="1" t="inlineStr">
-        <is>
-          <t>everyone</t>
-        </is>
-      </c>
-      <c r="F90" s="1" t="inlineStr"/>
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Upper pull vertical</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Single-Arm Pulldown</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Lats</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Upper back, Midline</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>everyone</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>Upper back</t>
+          <t>Shoulders</t>
         </is>
       </c>
       <c r="B91" s="1" t="inlineStr">
         <is>
-          <t>Inverted Row (Bodyweight)</t>
+          <t>Cable Face Pull</t>
         </is>
       </c>
       <c r="C91" s="1" t="inlineStr">
         <is>
-          <t>Upper back, Lats</t>
+          <t>Shoulders, Upper back</t>
         </is>
       </c>
       <c r="D91" s="1" t="inlineStr">
         <is>
-          <t>Biceps</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E91" s="1" t="inlineStr">
         <is>
-          <t>everyone (regression)</t>
+          <t>everyone</t>
         </is>
       </c>
       <c r="F91" s="1" t="inlineStr"/>
@@ -3021,27 +3000,27 @@
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>Groin / adductors</t>
+          <t>Upper back</t>
         </is>
       </c>
       <c r="B92" s="1" t="inlineStr">
         <is>
-          <t>Copenhagen Plank (Half)</t>
+          <t>Chest-Supported DB Row</t>
         </is>
       </c>
       <c r="C92" s="1" t="inlineStr">
         <is>
-          <t>Groin</t>
+          <t>Upper back, Lats</t>
         </is>
       </c>
       <c r="D92" s="1" t="inlineStr">
         <is>
-          <t>Midline</t>
+          <t>Biceps</t>
         </is>
       </c>
       <c r="E92" s="1" t="inlineStr">
         <is>
-          <t>1+ years</t>
+          <t>everyone</t>
         </is>
       </c>
       <c r="F92" s="1" t="inlineStr"/>
@@ -3049,27 +3028,27 @@
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>Groin / adductors</t>
+          <t>Upper back</t>
         </is>
       </c>
       <c r="B93" s="1" t="inlineStr">
         <is>
-          <t>Long-Lever Copenhagen</t>
+          <t>Inverted Row (Bodyweight)</t>
         </is>
       </c>
       <c r="C93" s="1" t="inlineStr">
         <is>
-          <t>Groin</t>
+          <t>Upper back, Lats</t>
         </is>
       </c>
       <c r="D93" s="1" t="inlineStr">
         <is>
-          <t>Midline</t>
+          <t>Biceps</t>
         </is>
       </c>
       <c r="E93" s="1" t="inlineStr">
         <is>
-          <t>2+ years</t>
+          <t>everyone (regression)</t>
         </is>
       </c>
       <c r="F93" s="1" t="inlineStr"/>
@@ -3082,7 +3061,7 @@
       </c>
       <c r="B94" s="1" t="inlineStr">
         <is>
-          <t>Groin Squeeze</t>
+          <t>Copenhagen Plank (Half)</t>
         </is>
       </c>
       <c r="C94" s="1" t="inlineStr">
@@ -3092,12 +3071,12 @@
       </c>
       <c r="D94" s="1" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Midline</t>
         </is>
       </c>
       <c r="E94" s="1" t="inlineStr">
         <is>
-          <t>everyone</t>
+          <t>1+ years</t>
         </is>
       </c>
       <c r="F94" s="1" t="inlineStr"/>
@@ -3110,22 +3089,22 @@
       </c>
       <c r="B95" s="1" t="inlineStr">
         <is>
-          <t>Cossack Squat</t>
+          <t>Long-Lever Copenhagen</t>
         </is>
       </c>
       <c r="C95" s="1" t="inlineStr">
         <is>
-          <t>Groin, Quads</t>
+          <t>Groin</t>
         </is>
       </c>
       <c r="D95" s="1" t="inlineStr">
         <is>
-          <t>Glutes, Hips</t>
+          <t>Midline</t>
         </is>
       </c>
       <c r="E95" s="1" t="inlineStr">
         <is>
-          <t>1+ years</t>
+          <t>2+ years</t>
         </is>
       </c>
       <c r="F95" s="1" t="inlineStr"/>
@@ -3138,22 +3117,22 @@
       </c>
       <c r="B96" s="1" t="inlineStr">
         <is>
-          <t>Lateral Lunge</t>
+          <t>Groin Squeeze</t>
         </is>
       </c>
       <c r="C96" s="1" t="inlineStr">
         <is>
-          <t>Groin, Quads</t>
+          <t>Groin</t>
         </is>
       </c>
       <c r="D96" s="1" t="inlineStr">
         <is>
-          <t>Glutes, Hips</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E96" s="1" t="inlineStr">
         <is>
-          <t>1+ years</t>
+          <t>everyone</t>
         </is>
       </c>
       <c r="F96" s="1" t="inlineStr"/>
@@ -3161,27 +3140,27 @@
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>Calves</t>
+          <t>Groin / adductors</t>
         </is>
       </c>
       <c r="B97" s="1" t="inlineStr">
         <is>
-          <t>Single-Leg Calf Raise</t>
+          <t>Cossack Squat</t>
         </is>
       </c>
       <c r="C97" s="1" t="inlineStr">
         <is>
-          <t>Calves</t>
+          <t>Groin, Quads</t>
         </is>
       </c>
       <c r="D97" s="1" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Glutes, Hips</t>
         </is>
       </c>
       <c r="E97" s="1" t="inlineStr">
         <is>
-          <t>everyone</t>
+          <t>1+ years</t>
         </is>
       </c>
       <c r="F97" s="1" t="inlineStr"/>
@@ -3189,27 +3168,27 @@
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>Calves</t>
+          <t>Groin / adductors</t>
         </is>
       </c>
       <c r="B98" s="1" t="inlineStr">
         <is>
-          <t>Seated Calf Raise</t>
+          <t>Lateral Lunge</t>
         </is>
       </c>
       <c r="C98" s="1" t="inlineStr">
         <is>
-          <t>Calves</t>
+          <t>Groin, Quads</t>
         </is>
       </c>
       <c r="D98" s="1" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Glutes, Hips</t>
         </is>
       </c>
       <c r="E98" s="1" t="inlineStr">
         <is>
-          <t>everyone</t>
+          <t>1+ years</t>
         </is>
       </c>
       <c r="F98" s="1" t="inlineStr"/>
@@ -3217,17 +3196,17 @@
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>Lower prehab</t>
+          <t>Calves</t>
         </is>
       </c>
       <c r="B99" s="1" t="inlineStr">
         <is>
-          <t>Banded TKE</t>
+          <t>Single-Leg Calf Raise</t>
         </is>
       </c>
       <c r="C99" s="1" t="inlineStr">
         <is>
-          <t>Quads, Knee</t>
+          <t>Calves</t>
         </is>
       </c>
       <c r="D99" s="1" t="inlineStr">
@@ -3245,17 +3224,17 @@
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>Lower prehab</t>
+          <t>Calves</t>
         </is>
       </c>
       <c r="B100" s="1" t="inlineStr">
         <is>
-          <t>Bosch Hold</t>
+          <t>Seated Calf Raise</t>
         </is>
       </c>
       <c r="C100" s="1" t="inlineStr">
         <is>
-          <t>Hamstrings, Calves</t>
+          <t>Calves</t>
         </is>
       </c>
       <c r="D100" s="1" t="inlineStr">
@@ -3278,7 +3257,7 @@
       </c>
       <c r="B101" s="1" t="inlineStr">
         <is>
-          <t>Spanish Squat Hold</t>
+          <t>Banded TKE</t>
         </is>
       </c>
       <c r="C101" s="1" t="inlineStr">
@@ -3306,17 +3285,17 @@
       </c>
       <c r="B102" s="1" t="inlineStr">
         <is>
-          <t>Slant Board Step-Down</t>
+          <t>Bosch Hold</t>
         </is>
       </c>
       <c r="C102" s="1" t="inlineStr">
         <is>
-          <t>Quads, Knee</t>
+          <t>Hamstrings, Calves</t>
         </is>
       </c>
       <c r="D102" s="1" t="inlineStr">
         <is>
-          <t>Hips</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E102" s="1" t="inlineStr">
@@ -3334,12 +3313,12 @@
       </c>
       <c r="B103" s="1" t="inlineStr">
         <is>
-          <t>Crab Walks</t>
+          <t>Spanish Squat Hold</t>
         </is>
       </c>
       <c r="C103" s="1" t="inlineStr">
         <is>
-          <t>Glutes, Hips</t>
+          <t>Quads, Knee</t>
         </is>
       </c>
       <c r="D103" s="1" t="inlineStr">
@@ -3357,22 +3336,22 @@
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>Midline</t>
+          <t>Lower prehab</t>
         </is>
       </c>
       <c r="B104" s="1" t="inlineStr">
         <is>
-          <t>Band Pallof Press</t>
+          <t>Slant Board Step-Down</t>
         </is>
       </c>
       <c r="C104" s="1" t="inlineStr">
         <is>
-          <t>Midline</t>
+          <t>Quads, Knee</t>
         </is>
       </c>
       <c r="D104" s="1" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Hips</t>
         </is>
       </c>
       <c r="E104" s="1" t="inlineStr">
@@ -3385,17 +3364,17 @@
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>Midline</t>
+          <t>Lower prehab</t>
         </is>
       </c>
       <c r="B105" s="1" t="inlineStr">
         <is>
-          <t>Dead Bug</t>
+          <t>Crab Walks</t>
         </is>
       </c>
       <c r="C105" s="1" t="inlineStr">
         <is>
-          <t>Midline</t>
+          <t>Glutes, Hips</t>
         </is>
       </c>
       <c r="D105" s="1" t="inlineStr">
@@ -3405,14 +3384,10 @@
       </c>
       <c r="E105" s="1" t="inlineStr">
         <is>
-          <t>everyone (regression)</t>
-        </is>
-      </c>
-      <c r="F105" s="1" t="inlineStr">
-        <is>
-          <t>Regression confirmed by Sam: plain version — advanced get Banded/Weighted Dead Bug instead</t>
-        </is>
-      </c>
+          <t>everyone</t>
+        </is>
+      </c>
+      <c r="F105" s="1" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
@@ -3422,7 +3397,7 @@
       </c>
       <c r="B106" s="1" t="inlineStr">
         <is>
-          <t>Banded Dead Bug</t>
+          <t>Band Pallof Press</t>
         </is>
       </c>
       <c r="C106" s="1" t="inlineStr">
@@ -3450,7 +3425,7 @@
       </c>
       <c r="B107" s="1" t="inlineStr">
         <is>
-          <t>Weighted Dead Bug</t>
+          <t>Dead Bug</t>
         </is>
       </c>
       <c r="C107" s="1" t="inlineStr">
@@ -3460,15 +3435,19 @@
       </c>
       <c r="D107" s="1" t="inlineStr">
         <is>
-          <t>Shoulders</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E107" s="1" t="inlineStr">
         <is>
-          <t>1+ years</t>
-        </is>
-      </c>
-      <c r="F107" s="1" t="inlineStr"/>
+          <t>everyone (regression)</t>
+        </is>
+      </c>
+      <c r="F107" s="1" t="inlineStr">
+        <is>
+          <t>Regression confirmed by Sam: plain version — advanced get Banded/Weighted Dead Bug instead</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
@@ -3478,7 +3457,7 @@
       </c>
       <c r="B108" s="1" t="inlineStr">
         <is>
-          <t>McGill Sit Up</t>
+          <t>Banded Dead Bug</t>
         </is>
       </c>
       <c r="C108" s="1" t="inlineStr">
@@ -3506,7 +3485,7 @@
       </c>
       <c r="B109" s="1" t="inlineStr">
         <is>
-          <t>Ab Wheel</t>
+          <t>Weighted Dead Bug</t>
         </is>
       </c>
       <c r="C109" s="1" t="inlineStr">
@@ -3521,14 +3500,10 @@
       </c>
       <c r="E109" s="1" t="inlineStr">
         <is>
-          <t>2+ years</t>
-        </is>
-      </c>
-      <c r="F109" s="1" t="inlineStr">
-        <is>
-          <t>⚑ progressive anti-extension skill move; pubalgia tagged 'avoid' — could arguably be 1+ years depending on how far the rollout range is regressed.</t>
-        </is>
-      </c>
+          <t>1+ years</t>
+        </is>
+      </c>
+      <c r="F109" s="1" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
@@ -3538,7 +3513,7 @@
       </c>
       <c r="B110" s="1" t="inlineStr">
         <is>
-          <t>Hanging Leg Raise</t>
+          <t>McGill Sit Up</t>
         </is>
       </c>
       <c r="C110" s="1" t="inlineStr">
@@ -3548,12 +3523,12 @@
       </c>
       <c r="D110" s="1" t="inlineStr">
         <is>
-          <t>Hips</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E110" s="1" t="inlineStr">
         <is>
-          <t>1+ years</t>
+          <t>everyone</t>
         </is>
       </c>
       <c r="F110" s="1" t="inlineStr"/>
@@ -3566,7 +3541,7 @@
       </c>
       <c r="B111" s="1" t="inlineStr">
         <is>
-          <t>Bird Dog</t>
+          <t>Ab Wheel</t>
         </is>
       </c>
       <c r="C111" s="1" t="inlineStr">
@@ -3576,17 +3551,17 @@
       </c>
       <c r="D111" s="1" t="inlineStr">
         <is>
-          <t>Glutes</t>
+          <t>Shoulders</t>
         </is>
       </c>
       <c r="E111" s="1" t="inlineStr">
         <is>
-          <t>everyone (regression)</t>
+          <t>2+ years</t>
         </is>
       </c>
       <c r="F111" s="1" t="inlineStr">
         <is>
-          <t>Regression confirmed by Sam: foundational motor control — or does it belong in the flow?</t>
+          <t>⚑ progressive anti-extension skill move; pubalgia tagged 'avoid' — could arguably be 1+ years depending on how far the rollout range is regressed.</t>
         </is>
       </c>
     </row>
@@ -3598,7 +3573,7 @@
       </c>
       <c r="B112" s="1" t="inlineStr">
         <is>
-          <t>Side Plank</t>
+          <t>Hanging Leg Raise</t>
         </is>
       </c>
       <c r="C112" s="1" t="inlineStr">
@@ -3608,12 +3583,12 @@
       </c>
       <c r="D112" s="1" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Hips</t>
         </is>
       </c>
       <c r="E112" s="1" t="inlineStr">
         <is>
-          <t>everyone</t>
+          <t>1+ years</t>
         </is>
       </c>
       <c r="F112" s="1" t="inlineStr"/>
@@ -3626,7 +3601,7 @@
       </c>
       <c r="B113" s="1" t="inlineStr">
         <is>
-          <t>Plank</t>
+          <t>Bird Dog</t>
         </is>
       </c>
       <c r="C113" s="1" t="inlineStr">
@@ -3636,7 +3611,7 @@
       </c>
       <c r="D113" s="1" t="inlineStr">
         <is>
-          <t>Shoulders</t>
+          <t>Glutes</t>
         </is>
       </c>
       <c r="E113" s="1" t="inlineStr">
@@ -3646,7 +3621,7 @@
       </c>
       <c r="F113" s="1" t="inlineStr">
         <is>
-          <t>Regression confirmed by Sam: plain plank — advanced get Stir the Pot / Side Plank Row / Ab Wheel</t>
+          <t>Regression confirmed by Sam: foundational motor control — or does it belong in the flow?</t>
         </is>
       </c>
     </row>
@@ -3658,7 +3633,7 @@
       </c>
       <c r="B114" s="1" t="inlineStr">
         <is>
-          <t>Hollow Hold</t>
+          <t>Side Plank</t>
         </is>
       </c>
       <c r="C114" s="1" t="inlineStr">
@@ -3686,7 +3661,7 @@
       </c>
       <c r="B115" s="1" t="inlineStr">
         <is>
-          <t>Stir the Pot</t>
+          <t>Plank</t>
         </is>
       </c>
       <c r="C115" s="1" t="inlineStr">
@@ -3701,10 +3676,14 @@
       </c>
       <c r="E115" s="1" t="inlineStr">
         <is>
-          <t>everyone</t>
-        </is>
-      </c>
-      <c r="F115" s="1" t="inlineStr"/>
+          <t>everyone (regression)</t>
+        </is>
+      </c>
+      <c r="F115" s="1" t="inlineStr">
+        <is>
+          <t>Regression confirmed by Sam: plain plank — advanced get Stir the Pot / Side Plank Row / Ab Wheel</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
@@ -3714,7 +3693,7 @@
       </c>
       <c r="B116" s="1" t="inlineStr">
         <is>
-          <t>Dragon Flag</t>
+          <t>Hollow Hold</t>
         </is>
       </c>
       <c r="C116" s="1" t="inlineStr">
@@ -3724,19 +3703,15 @@
       </c>
       <c r="D116" s="1" t="inlineStr">
         <is>
-          <t>Shoulders</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E116" s="1" t="inlineStr">
         <is>
-          <t>advanced only</t>
-        </is>
-      </c>
-      <c r="F116" s="1" t="inlineStr">
-        <is>
-          <t>lower back tagged 'avoid'; classic advanced core skill move, high eccentric demand through the full posterior chain.</t>
-        </is>
-      </c>
+          <t>everyone</t>
+        </is>
+      </c>
+      <c r="F116" s="1" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
@@ -3746,7 +3721,7 @@
       </c>
       <c r="B117" s="1" t="inlineStr">
         <is>
-          <t>Side Plank Row</t>
+          <t>Stir the Pot</t>
         </is>
       </c>
       <c r="C117" s="1" t="inlineStr">
@@ -3756,7 +3731,7 @@
       </c>
       <c r="D117" s="1" t="inlineStr">
         <is>
-          <t>Upper back</t>
+          <t>Shoulders</t>
         </is>
       </c>
       <c r="E117" s="1" t="inlineStr">
@@ -3774,7 +3749,7 @@
       </c>
       <c r="B118" s="1" t="inlineStr">
         <is>
-          <t>Woodchop (Standing)</t>
+          <t>Dragon Flag</t>
         </is>
       </c>
       <c r="C118" s="1" t="inlineStr">
@@ -3789,10 +3764,14 @@
       </c>
       <c r="E118" s="1" t="inlineStr">
         <is>
-          <t>everyone</t>
-        </is>
-      </c>
-      <c r="F118" s="1" t="inlineStr"/>
+          <t>advanced only</t>
+        </is>
+      </c>
+      <c r="F118" s="1" t="inlineStr">
+        <is>
+          <t>lower back tagged 'avoid'; classic advanced core skill move, high eccentric demand through the full posterior chain.</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
@@ -3802,7 +3781,7 @@
       </c>
       <c r="B119" s="1" t="inlineStr">
         <is>
-          <t>Woodchop (Half Kneeling)</t>
+          <t>Side Plank Row</t>
         </is>
       </c>
       <c r="C119" s="1" t="inlineStr">
@@ -3812,7 +3791,7 @@
       </c>
       <c r="D119" s="1" t="inlineStr">
         <is>
-          <t>Shoulders</t>
+          <t>Upper back</t>
         </is>
       </c>
       <c r="E119" s="1" t="inlineStr">
@@ -3825,22 +3804,22 @@
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>Shoulder health</t>
+          <t>Midline</t>
         </is>
       </c>
       <c r="B120" s="1" t="inlineStr">
         <is>
-          <t>Banded External Rotation</t>
+          <t>Woodchop (Standing)</t>
         </is>
       </c>
       <c r="C120" s="1" t="inlineStr">
         <is>
+          <t>Midline</t>
+        </is>
+      </c>
+      <c r="D120" s="1" t="inlineStr">
+        <is>
           <t>Shoulders</t>
-        </is>
-      </c>
-      <c r="D120" s="1" t="inlineStr">
-        <is>
-          <t>—</t>
         </is>
       </c>
       <c r="E120" s="1" t="inlineStr">
@@ -3853,34 +3832,30 @@
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>Shoulder health</t>
+          <t>Midline</t>
         </is>
       </c>
       <c r="B121" s="1" t="inlineStr">
         <is>
-          <t>Bottoms-Up KB Press</t>
+          <t>Woodchop (Half Kneeling)</t>
         </is>
       </c>
       <c r="C121" s="1" t="inlineStr">
         <is>
+          <t>Midline</t>
+        </is>
+      </c>
+      <c r="D121" s="1" t="inlineStr">
+        <is>
           <t>Shoulders</t>
         </is>
       </c>
-      <c r="D121" s="1" t="inlineStr">
-        <is>
-          <t>Midline</t>
-        </is>
-      </c>
       <c r="E121" s="1" t="inlineStr">
         <is>
           <t>everyone</t>
         </is>
       </c>
-      <c r="F121" s="1" t="inlineStr">
-        <is>
-          <t>⚑ wrist/shoulder stabilisation demand is real even at light load — could be 1+ years.</t>
-        </is>
-      </c>
+      <c r="F121" s="1" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
@@ -3890,17 +3865,17 @@
       </c>
       <c r="B122" s="1" t="inlineStr">
         <is>
-          <t>Scap Push-Up</t>
+          <t>Banded External Rotation</t>
         </is>
       </c>
       <c r="C122" s="1" t="inlineStr">
         <is>
-          <t>Shoulders, Upper back</t>
+          <t>Shoulders</t>
         </is>
       </c>
       <c r="D122" s="1" t="inlineStr">
         <is>
-          <t>Midline</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E122" s="1" t="inlineStr">
@@ -3913,17 +3888,17 @@
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>Hamstring (light)</t>
+          <t>Shoulder health</t>
         </is>
       </c>
       <c r="B123" s="1" t="inlineStr">
         <is>
-          <t>Swiss Ball Hamstring Curl</t>
+          <t>Bottoms-Up KB Press</t>
         </is>
       </c>
       <c r="C123" s="1" t="inlineStr">
         <is>
-          <t>Hamstrings</t>
+          <t>Shoulders</t>
         </is>
       </c>
       <c r="D123" s="1" t="inlineStr">
@@ -3936,27 +3911,31 @@
           <t>everyone</t>
         </is>
       </c>
-      <c r="F123" s="1" t="inlineStr"/>
+      <c r="F123" s="1" t="inlineStr">
+        <is>
+          <t>⚑ wrist/shoulder stabilisation demand is real even at light load — could be 1+ years.</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>Tissue quality</t>
+          <t>Shoulder health</t>
         </is>
       </c>
       <c r="B124" s="1" t="inlineStr">
         <is>
-          <t>Foam Roll — Hip Flexor, Quad, Adductors</t>
+          <t>Scap Push-Up</t>
         </is>
       </c>
       <c r="C124" s="1" t="inlineStr">
         <is>
-          <t>Quads, Groin</t>
+          <t>Shoulders, Upper back</t>
         </is>
       </c>
       <c r="D124" s="1" t="inlineStr">
         <is>
-          <t>Hips</t>
+          <t>Midline</t>
         </is>
       </c>
       <c r="E124" s="1" t="inlineStr">
@@ -3969,22 +3948,22 @@
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>Tissue quality</t>
+          <t>Hamstring (light)</t>
         </is>
       </c>
       <c r="B125" s="1" t="inlineStr">
         <is>
-          <t>Foam Roll — T-Spine</t>
+          <t>Swiss Ball Hamstring Curl</t>
         </is>
       </c>
       <c r="C125" s="1" t="inlineStr">
         <is>
-          <t>Upper back</t>
+          <t>Hamstrings</t>
         </is>
       </c>
       <c r="D125" s="1" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Midline</t>
         </is>
       </c>
       <c r="E125" s="1" t="inlineStr">
@@ -4002,12 +3981,12 @@
       </c>
       <c r="B126" s="1" t="inlineStr">
         <is>
-          <t>Foam Roll — IT Band</t>
+          <t>Foam Roll — Hip Flexor, Quad, Adductors</t>
         </is>
       </c>
       <c r="C126" s="1" t="inlineStr">
         <is>
-          <t>Quads</t>
+          <t>Quads, Groin</t>
         </is>
       </c>
       <c r="D126" s="1" t="inlineStr">
@@ -4030,12 +4009,12 @@
       </c>
       <c r="B127" s="1" t="inlineStr">
         <is>
-          <t>Foam Roll — Lats</t>
+          <t>Foam Roll — T-Spine</t>
         </is>
       </c>
       <c r="C127" s="1" t="inlineStr">
         <is>
-          <t>Lats</t>
+          <t>Upper back</t>
         </is>
       </c>
       <c r="D127" s="1" t="inlineStr">
@@ -4058,17 +4037,17 @@
       </c>
       <c r="B128" s="1" t="inlineStr">
         <is>
-          <t>Foam Roll — Calves &amp; Outer Shins</t>
+          <t>Foam Roll — IT Band</t>
         </is>
       </c>
       <c r="C128" s="1" t="inlineStr">
         <is>
-          <t>Calves</t>
+          <t>Quads</t>
         </is>
       </c>
       <c r="D128" s="1" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Hips</t>
         </is>
       </c>
       <c r="E128" s="1" t="inlineStr">
@@ -4086,17 +4065,17 @@
       </c>
       <c r="B129" s="1" t="inlineStr">
         <is>
-          <t>Lacrosse Ball Glute Release</t>
+          <t>Foam Roll — Lats</t>
         </is>
       </c>
       <c r="C129" s="1" t="inlineStr">
         <is>
-          <t>Glutes</t>
+          <t>Lats</t>
         </is>
       </c>
       <c r="D129" s="1" t="inlineStr">
         <is>
-          <t>Hips</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E129" s="1" t="inlineStr">
@@ -4109,22 +4088,22 @@
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>Mobility</t>
+          <t>Tissue quality</t>
         </is>
       </c>
       <c r="B130" s="1" t="inlineStr">
         <is>
-          <t>Hip 90/90 Stretch</t>
+          <t>Foam Roll — Calves &amp; Outer Shins</t>
         </is>
       </c>
       <c r="C130" s="1" t="inlineStr">
         <is>
-          <t>Hips</t>
+          <t>Calves</t>
         </is>
       </c>
       <c r="D130" s="1" t="inlineStr">
         <is>
-          <t>Groin</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E130" s="1" t="inlineStr">
@@ -4137,22 +4116,22 @@
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>Mobility</t>
+          <t>Tissue quality</t>
         </is>
       </c>
       <c r="B131" s="1" t="inlineStr">
         <is>
-          <t>Cat-Cow</t>
+          <t>Lacrosse Ball Glute Release</t>
         </is>
       </c>
       <c r="C131" s="1" t="inlineStr">
         <is>
-          <t>Midline</t>
+          <t>Glutes</t>
         </is>
       </c>
       <c r="D131" s="1" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Hips</t>
         </is>
       </c>
       <c r="E131" s="1" t="inlineStr">
@@ -4170,17 +4149,17 @@
       </c>
       <c r="B132" s="1" t="inlineStr">
         <is>
-          <t>World's Greatest Stretch</t>
+          <t>Hip 90/90 Stretch</t>
         </is>
       </c>
       <c r="C132" s="1" t="inlineStr">
         <is>
-          <t>Hips, Groin</t>
+          <t>Hips</t>
         </is>
       </c>
       <c r="D132" s="1" t="inlineStr">
         <is>
-          <t>Midline</t>
+          <t>Groin</t>
         </is>
       </c>
       <c r="E132" s="1" t="inlineStr">
@@ -4198,17 +4177,17 @@
       </c>
       <c r="B133" s="1" t="inlineStr">
         <is>
-          <t>Deep Squat Hold</t>
+          <t>Cat-Cow</t>
         </is>
       </c>
       <c r="C133" s="1" t="inlineStr">
         <is>
-          <t>Hips, Groin</t>
+          <t>Midline</t>
         </is>
       </c>
       <c r="D133" s="1" t="inlineStr">
         <is>
-          <t>Calves</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E133" s="1" t="inlineStr">
@@ -4226,17 +4205,17 @@
       </c>
       <c r="B134" s="1" t="inlineStr">
         <is>
-          <t>Couch Stretch</t>
+          <t>World's Greatest Stretch</t>
         </is>
       </c>
       <c r="C134" s="1" t="inlineStr">
         <is>
-          <t>Quads, Hips</t>
+          <t>Hips, Groin</t>
         </is>
       </c>
       <c r="D134" s="1" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Midline</t>
         </is>
       </c>
       <c r="E134" s="1" t="inlineStr">
@@ -4254,17 +4233,17 @@
       </c>
       <c r="B135" s="1" t="inlineStr">
         <is>
-          <t>Open Book Thoracic Rotation</t>
+          <t>Deep Squat Hold</t>
         </is>
       </c>
       <c r="C135" s="1" t="inlineStr">
         <is>
-          <t>Upper back</t>
+          <t>Hips, Groin</t>
         </is>
       </c>
       <c r="D135" s="1" t="inlineStr">
         <is>
-          <t>Midline</t>
+          <t>Calves</t>
         </is>
       </c>
       <c r="E135" s="1" t="inlineStr">
@@ -4282,17 +4261,17 @@
       </c>
       <c r="B136" s="1" t="inlineStr">
         <is>
-          <t>Pigeon Stretch</t>
+          <t>Couch Stretch</t>
         </is>
       </c>
       <c r="C136" s="1" t="inlineStr">
         <is>
-          <t>Hips, Glutes</t>
+          <t>Quads, Hips</t>
         </is>
       </c>
       <c r="D136" s="1" t="inlineStr">
         <is>
-          <t>Groin</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E136" s="1" t="inlineStr">
@@ -4310,17 +4289,17 @@
       </c>
       <c r="B137" s="1" t="inlineStr">
         <is>
-          <t>Adductor Rockback</t>
+          <t>Open Book Thoracic Rotation</t>
         </is>
       </c>
       <c r="C137" s="1" t="inlineStr">
         <is>
-          <t>Groin</t>
+          <t>Upper back</t>
         </is>
       </c>
       <c r="D137" s="1" t="inlineStr">
         <is>
-          <t>Hips</t>
+          <t>Midline</t>
         </is>
       </c>
       <c r="E137" s="1" t="inlineStr">
@@ -4338,17 +4317,17 @@
       </c>
       <c r="B138" s="1" t="inlineStr">
         <is>
-          <t>Chest / Pec Stretch (Doorway)</t>
+          <t>Pigeon Stretch</t>
         </is>
       </c>
       <c r="C138" s="1" t="inlineStr">
         <is>
-          <t>Chest</t>
+          <t>Hips, Glutes</t>
         </is>
       </c>
       <c r="D138" s="1" t="inlineStr">
         <is>
-          <t>Shoulders</t>
+          <t>Groin</t>
         </is>
       </c>
       <c r="E138" s="1" t="inlineStr">
@@ -4366,17 +4345,17 @@
       </c>
       <c r="B139" s="1" t="inlineStr">
         <is>
-          <t>Lat Stretch</t>
+          <t>Adductor Rockback</t>
         </is>
       </c>
       <c r="C139" s="1" t="inlineStr">
         <is>
-          <t>Lats</t>
+          <t>Groin</t>
         </is>
       </c>
       <c r="D139" s="1" t="inlineStr">
         <is>
-          <t>Shoulders</t>
+          <t>Hips</t>
         </is>
       </c>
       <c r="E139" s="1" t="inlineStr">
@@ -4394,17 +4373,17 @@
       </c>
       <c r="B140" s="1" t="inlineStr">
         <is>
-          <t>Dead Hang</t>
+          <t>Chest / Pec Stretch (Doorway)</t>
         </is>
       </c>
       <c r="C140" s="1" t="inlineStr">
         <is>
-          <t>Lats, Shoulders</t>
+          <t>Chest</t>
         </is>
       </c>
       <c r="D140" s="1" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Shoulders</t>
         </is>
       </c>
       <c r="E140" s="1" t="inlineStr">
@@ -4422,17 +4401,17 @@
       </c>
       <c r="B141" s="1" t="inlineStr">
         <is>
-          <t>Toe Stretch</t>
+          <t>Lat Stretch</t>
         </is>
       </c>
       <c r="C141" s="1" t="inlineStr">
         <is>
-          <t>Calves, Feet</t>
+          <t>Lats</t>
         </is>
       </c>
       <c r="D141" s="1" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Shoulders</t>
         </is>
       </c>
       <c r="E141" s="1" t="inlineStr">
@@ -4440,11 +4419,7 @@
           <t>everyone</t>
         </is>
       </c>
-      <c r="F141" s="1" t="inlineStr">
-        <is>
-          <t>targets the foot/ankle specifically; 'Calves' is the closest plain-language bucket.</t>
-        </is>
-      </c>
+      <c r="F141" s="1" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
@@ -4454,12 +4429,12 @@
       </c>
       <c r="B142" s="1" t="inlineStr">
         <is>
-          <t>Calf Stretch</t>
+          <t>Dead Hang</t>
         </is>
       </c>
       <c r="C142" s="1" t="inlineStr">
         <is>
-          <t>Calves</t>
+          <t>Lats, Shoulders</t>
         </is>
       </c>
       <c r="D142" s="1" t="inlineStr">
@@ -4482,12 +4457,12 @@
       </c>
       <c r="B143" s="1" t="inlineStr">
         <is>
-          <t>QL Back Extension</t>
+          <t>Toe Stretch</t>
         </is>
       </c>
       <c r="C143" s="1" t="inlineStr">
         <is>
-          <t>Midline</t>
+          <t>Calves, Feet</t>
         </is>
       </c>
       <c r="D143" s="1" t="inlineStr">
@@ -4502,7 +4477,7 @@
       </c>
       <c r="F143" s="1" t="inlineStr">
         <is>
-          <t>targets the quadratus lumborum (side of lower back) specifically; 'Midline' is the closest plain-language bucket.</t>
+          <t>targets the foot/ankle specifically; 'Calves' is the closest plain-language bucket.</t>
         </is>
       </c>
     </row>
@@ -4514,17 +4489,17 @@
       </c>
       <c r="B144" s="1" t="inlineStr">
         <is>
-          <t>ATG Split Squat</t>
+          <t>Calf Stretch</t>
         </is>
       </c>
       <c r="C144" s="1" t="inlineStr">
         <is>
-          <t>Quads, Hips</t>
+          <t>Calves</t>
         </is>
       </c>
       <c r="D144" s="1" t="inlineStr">
         <is>
-          <t>Groin, Calves</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E144" s="1" t="inlineStr">
@@ -4532,11 +4507,7 @@
           <t>everyone</t>
         </is>
       </c>
-      <c r="F144" s="1" t="inlineStr">
-        <is>
-          <t>⚑ deep ankle/hip mobility demand — some athletes may need to regress the range; could be 1+ years.</t>
-        </is>
-      </c>
+      <c r="F144" s="1" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
@@ -4546,17 +4517,17 @@
       </c>
       <c r="B145" s="1" t="inlineStr">
         <is>
-          <t>Elephant Walks</t>
+          <t>QL Back Extension</t>
         </is>
       </c>
       <c r="C145" s="1" t="inlineStr">
         <is>
-          <t>Hamstrings</t>
+          <t>Midline</t>
         </is>
       </c>
       <c r="D145" s="1" t="inlineStr">
         <is>
-          <t>Calves</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E145" s="1" t="inlineStr">
@@ -4564,27 +4535,31 @@
           <t>everyone</t>
         </is>
       </c>
-      <c r="F145" s="1" t="inlineStr"/>
+      <c r="F145" s="1" t="inlineStr">
+        <is>
+          <t>targets the quadratus lumborum (side of lower back) specifically; 'Midline' is the closest plain-language bucket.</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>Easy cardio (zone 1)</t>
+          <t>Mobility</t>
         </is>
       </c>
       <c r="B146" s="1" t="inlineStr">
         <is>
-          <t>Light Walk or Stationary Bike</t>
+          <t>ATG Split Squat</t>
         </is>
       </c>
       <c r="C146" s="1" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Quads, Hips</t>
         </is>
       </c>
       <c r="D146" s="1" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Groin, Calves</t>
         </is>
       </c>
       <c r="E146" s="1" t="inlineStr">
@@ -4592,27 +4567,31 @@
           <t>everyone</t>
         </is>
       </c>
-      <c r="F146" s="1" t="inlineStr"/>
+      <c r="F146" s="1" t="inlineStr">
+        <is>
+          <t>⚑ deep ankle/hip mobility demand — some athletes may need to regress the range; could be 1+ years.</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>Easy cardio (zone 1)</t>
+          <t>Mobility</t>
         </is>
       </c>
       <c r="B147" s="1" t="inlineStr">
         <is>
-          <t>Incline Treadmill Walk</t>
+          <t>Elephant Walks</t>
         </is>
       </c>
       <c r="C147" s="1" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Hamstrings</t>
         </is>
       </c>
       <c r="D147" s="1" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Calves</t>
         </is>
       </c>
       <c r="E147" s="1" t="inlineStr">
@@ -4630,7 +4609,7 @@
       </c>
       <c r="B148" s="1" t="inlineStr">
         <is>
-          <t>Outdoor Walk</t>
+          <t>Light Walk or Stationary Bike</t>
         </is>
       </c>
       <c r="C148" s="1" t="inlineStr">
@@ -4658,12 +4637,12 @@
       </c>
       <c r="B149" s="1" t="inlineStr">
         <is>
-          <t>Light Skipping</t>
+          <t>Incline Treadmill Walk</t>
         </is>
       </c>
       <c r="C149" s="1" t="inlineStr">
         <is>
-          <t>Calves</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D149" s="1" t="inlineStr">
@@ -4681,12 +4660,12 @@
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>Breathing reset</t>
+          <t>Easy cardio (zone 1)</t>
         </is>
       </c>
       <c r="B150" s="1" t="inlineStr">
         <is>
-          <t>90/90 Breathing</t>
+          <t>Outdoor Walk</t>
         </is>
       </c>
       <c r="C150" s="1" t="inlineStr">
@@ -4709,17 +4688,17 @@
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>Breathing reset</t>
+          <t>Easy cardio (zone 1)</t>
         </is>
       </c>
       <c r="B151" s="1" t="inlineStr">
         <is>
-          <t>Crocodile Breathing</t>
+          <t>Light Skipping</t>
         </is>
       </c>
       <c r="C151" s="1" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Calves</t>
         </is>
       </c>
       <c r="D151" s="1" t="inlineStr">
@@ -4742,7 +4721,7 @@
       </c>
       <c r="B152" s="1" t="inlineStr">
         <is>
-          <t>Box Breathing</t>
+          <t>90/90 Breathing</t>
         </is>
       </c>
       <c r="C152" s="1" t="inlineStr">
@@ -4770,7 +4749,7 @@
       </c>
       <c r="B153" s="1" t="inlineStr">
         <is>
-          <t>Child's Pose with Breathing</t>
+          <t>Crocodile Breathing</t>
         </is>
       </c>
       <c r="C153" s="1" t="inlineStr">
@@ -4793,12 +4772,12 @@
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>Conditioning</t>
+          <t>Breathing reset</t>
         </is>
       </c>
       <c r="B154" s="1" t="inlineStr">
         <is>
-          <t>Sprint Intervals</t>
+          <t>Box Breathing</t>
         </is>
       </c>
       <c r="C154" s="1" t="inlineStr">
@@ -4813,24 +4792,20 @@
       </c>
       <c r="E154" s="1" t="inlineStr">
         <is>
-          <t>1+ years</t>
-        </is>
-      </c>
-      <c r="F154" s="1" t="inlineStr">
-        <is>
-          <t>⚑ field sprint at top-end speed; hamstring/calf tagged 'avoid'. Gate here is conditioning base, not lifting experience, so this ladder may not be the right instrument at all.</t>
-        </is>
-      </c>
+          <t>everyone</t>
+        </is>
+      </c>
+      <c r="F154" s="1" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>Conditioning</t>
+          <t>Breathing reset</t>
         </is>
       </c>
       <c r="B155" s="1" t="inlineStr">
         <is>
-          <t>Hill Sprints</t>
+          <t>Child's Pose with Breathing</t>
         </is>
       </c>
       <c r="C155" s="1" t="inlineStr">
@@ -4845,14 +4820,10 @@
       </c>
       <c r="E155" s="1" t="inlineStr">
         <is>
-          <t>1+ years</t>
-        </is>
-      </c>
-      <c r="F155" s="1" t="inlineStr">
-        <is>
-          <t>⚑ field sprint at top-end speed; hamstring/calf tagged 'avoid'. Gate here is conditioning base, not lifting experience, so this ladder may not be the right instrument at all.</t>
-        </is>
-      </c>
+          <t>everyone</t>
+        </is>
+      </c>
+      <c r="F155" s="1" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
@@ -4862,7 +4833,7 @@
       </c>
       <c r="B156" s="1" t="inlineStr">
         <is>
-          <t>Quality Sprints</t>
+          <t>Sprint Intervals</t>
         </is>
       </c>
       <c r="C156" s="1" t="inlineStr">
@@ -4894,7 +4865,7 @@
       </c>
       <c r="B157" s="1" t="inlineStr">
         <is>
-          <t>MAS Training</t>
+          <t>Hill Sprints</t>
         </is>
       </c>
       <c r="C157" s="1" t="inlineStr">
@@ -4926,7 +4897,7 @@
       </c>
       <c r="B158" s="1" t="inlineStr">
         <is>
-          <t>Flying Sprints</t>
+          <t>Quality Sprints</t>
         </is>
       </c>
       <c r="C158" s="1" t="inlineStr">
@@ -4946,7 +4917,7 @@
       </c>
       <c r="F158" s="1" t="inlineStr">
         <is>
-          <t>⚑ field sprint at top-end speed. Gate here is conditioning base, not lifting experience, so this ladder may not be the right instrument at all.</t>
+          <t>⚑ field sprint at top-end speed; hamstring/calf tagged 'avoid'. Gate here is conditioning base, not lifting experience, so this ladder may not be the right instrument at all.</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4929,7 @@
       </c>
       <c r="B159" s="1" t="inlineStr">
         <is>
-          <t>MAS 15:15 Blocks</t>
+          <t>MAS Training</t>
         </is>
       </c>
       <c r="C159" s="1" t="inlineStr">
@@ -4978,7 +4949,7 @@
       </c>
       <c r="F159" s="1" t="inlineStr">
         <is>
-          <t>⚑ field sprint at top-end speed. Gate here is conditioning base, not lifting experience, so this ladder may not be the right instrument at all.</t>
+          <t>⚑ field sprint at top-end speed; hamstring/calf tagged 'avoid'. Gate here is conditioning base, not lifting experience, so this ladder may not be the right instrument at all.</t>
         </is>
       </c>
     </row>
@@ -4990,7 +4961,7 @@
       </c>
       <c r="B160" s="1" t="inlineStr">
         <is>
-          <t>Tabata Intervals</t>
+          <t>Flying Sprints</t>
         </is>
       </c>
       <c r="C160" s="1" t="inlineStr">
@@ -5005,12 +4976,12 @@
       </c>
       <c r="E160" s="1" t="inlineStr">
         <is>
-          <t>everyone</t>
+          <t>1+ years</t>
         </is>
       </c>
       <c r="F160" s="1" t="inlineStr">
         <is>
-          <t>session format, not an individual movement — no meaningful muscle group.</t>
+          <t>⚑ field sprint at top-end speed. Gate here is conditioning base, not lifting experience, so this ladder may not be the right instrument at all.</t>
         </is>
       </c>
     </row>
@@ -5022,7 +4993,7 @@
       </c>
       <c r="B161" s="1" t="inlineStr">
         <is>
-          <t>Inverse Tabata</t>
+          <t>MAS 15:15 Blocks</t>
         </is>
       </c>
       <c r="C161" s="1" t="inlineStr">
@@ -5037,12 +5008,12 @@
       </c>
       <c r="E161" s="1" t="inlineStr">
         <is>
-          <t>everyone</t>
+          <t>1+ years</t>
         </is>
       </c>
       <c r="F161" s="1" t="inlineStr">
         <is>
-          <t>session format, not an individual movement — no meaningful muscle group.</t>
+          <t>⚑ field sprint at top-end speed. Gate here is conditioning base, not lifting experience, so this ladder may not be the right instrument at all.</t>
         </is>
       </c>
     </row>
@@ -5054,7 +5025,7 @@
       </c>
       <c r="B162" s="1" t="inlineStr">
         <is>
-          <t>Max Effort Sprint Accumulation</t>
+          <t>Tabata Intervals</t>
         </is>
       </c>
       <c r="C162" s="1" t="inlineStr">
@@ -5086,7 +5057,7 @@
       </c>
       <c r="B163" s="1" t="inlineStr">
         <is>
-          <t>Free Sprint Session</t>
+          <t>Inverse Tabata</t>
         </is>
       </c>
       <c r="C163" s="1" t="inlineStr">
@@ -5101,12 +5072,12 @@
       </c>
       <c r="E163" s="1" t="inlineStr">
         <is>
-          <t>1+ years</t>
+          <t>everyone</t>
         </is>
       </c>
       <c r="F163" s="1" t="inlineStr">
         <is>
-          <t>⚑ field sprint at top-end speed; hamstring/calf tagged 'avoid'. Gate here is conditioning base, not lifting experience, so this ladder may not be the right instrument at all.</t>
+          <t>session format, not an individual movement — no meaningful muscle group.</t>
         </is>
       </c>
     </row>
@@ -5118,7 +5089,7 @@
       </c>
       <c r="B164" s="1" t="inlineStr">
         <is>
-          <t>MetCon</t>
+          <t>Max Effort Sprint Accumulation</t>
         </is>
       </c>
       <c r="C164" s="1" t="inlineStr">
@@ -5133,12 +5104,12 @@
       </c>
       <c r="E164" s="1" t="inlineStr">
         <is>
-          <t>1+ years</t>
+          <t>everyone</t>
         </is>
       </c>
       <c r="F164" s="1" t="inlineStr">
         <is>
-          <t>⚑ mixed high-output format with technical/coordination demand across movements — the training-age ladder is a rough fit for a session format.</t>
+          <t>session format, not an individual movement — no meaningful muscle group.</t>
         </is>
       </c>
     </row>
@@ -5150,7 +5121,7 @@
       </c>
       <c r="B165" s="1" t="inlineStr">
         <is>
-          <t>Long Run</t>
+          <t>Free Sprint Session</t>
         </is>
       </c>
       <c r="C165" s="1" t="inlineStr">
@@ -5165,12 +5136,12 @@
       </c>
       <c r="E165" s="1" t="inlineStr">
         <is>
-          <t>everyone</t>
+          <t>1+ years</t>
         </is>
       </c>
       <c r="F165" s="1" t="inlineStr">
         <is>
-          <t>session format, not an individual movement — no meaningful muscle group.</t>
+          <t>⚑ field sprint at top-end speed; hamstring/calf tagged 'avoid'. Gate here is conditioning base, not lifting experience, so this ladder may not be the right instrument at all.</t>
         </is>
       </c>
     </row>
@@ -5182,7 +5153,7 @@
       </c>
       <c r="B166" s="1" t="inlineStr">
         <is>
-          <t>6x1km</t>
+          <t>Long Run</t>
         </is>
       </c>
       <c r="C166" s="1" t="inlineStr">
@@ -5214,7 +5185,7 @@
       </c>
       <c r="B167" s="1" t="inlineStr">
         <is>
-          <t>1km Repeat Intervals</t>
+          <t>6x1km</t>
         </is>
       </c>
       <c r="C167" s="1" t="inlineStr">
@@ -5246,7 +5217,7 @@
       </c>
       <c r="B168" s="1" t="inlineStr">
         <is>
-          <t>4x4 VO2</t>
+          <t>1km Repeat Intervals</t>
         </is>
       </c>
       <c r="C168" s="1" t="inlineStr">
@@ -5278,7 +5249,7 @@
       </c>
       <c r="B169" s="1" t="inlineStr">
         <is>
-          <t>200m/400m Repeat Runs</t>
+          <t>4x4 VO2</t>
         </is>
       </c>
       <c r="C169" s="1" t="inlineStr">
@@ -5293,12 +5264,12 @@
       </c>
       <c r="E169" s="1" t="inlineStr">
         <is>
-          <t>1+ years</t>
+          <t>everyone</t>
         </is>
       </c>
       <c r="F169" s="1" t="inlineStr">
         <is>
-          <t>⚑ sprint-adjacent speed endurance at high impact — the training-age ladder is a rough fit for a session format.</t>
+          <t>session format, not an individual movement — no meaningful muscle group.</t>
         </is>
       </c>
     </row>
@@ -5310,7 +5281,7 @@
       </c>
       <c r="B170" s="1" t="inlineStr">
         <is>
-          <t>Footy Fartlek</t>
+          <t>200m/400m Repeat Runs</t>
         </is>
       </c>
       <c r="C170" s="1" t="inlineStr">
@@ -5325,12 +5296,12 @@
       </c>
       <c r="E170" s="1" t="inlineStr">
         <is>
-          <t>everyone</t>
+          <t>1+ years</t>
         </is>
       </c>
       <c r="F170" s="1" t="inlineStr">
         <is>
-          <t>session format, not an individual movement — no meaningful muscle group.</t>
+          <t>⚑ sprint-adjacent speed endurance at high impact — the training-age ladder is a rough fit for a session format.</t>
         </is>
       </c>
     </row>
@@ -5342,7 +5313,7 @@
       </c>
       <c r="B171" s="1" t="inlineStr">
         <is>
-          <t>Hard Row Intervals</t>
+          <t>Footy Fartlek</t>
         </is>
       </c>
       <c r="C171" s="1" t="inlineStr">
@@ -5374,7 +5345,7 @@
       </c>
       <c r="B172" s="1" t="inlineStr">
         <is>
-          <t>Hard SkiErg Intervals</t>
+          <t>Hard Row Intervals</t>
         </is>
       </c>
       <c r="C172" s="1" t="inlineStr">
@@ -5406,7 +5377,7 @@
       </c>
       <c r="B173" s="1" t="inlineStr">
         <is>
-          <t>Hard Assault Bike Intervals</t>
+          <t>Hard SkiErg Intervals</t>
         </is>
       </c>
       <c r="C173" s="1" t="inlineStr">
@@ -5438,7 +5409,7 @@
       </c>
       <c r="B174" s="1" t="inlineStr">
         <is>
-          <t>Erg EMOM</t>
+          <t>Hard Assault Bike Intervals</t>
         </is>
       </c>
       <c r="C174" s="1" t="inlineStr">
@@ -5470,7 +5441,7 @@
       </c>
       <c r="B175" s="1" t="inlineStr">
         <is>
-          <t>Tempo Run</t>
+          <t>Erg EMOM</t>
         </is>
       </c>
       <c r="C175" s="1" t="inlineStr">
@@ -5502,7 +5473,7 @@
       </c>
       <c r="B176" s="1" t="inlineStr">
         <is>
-          <t>Long Nasal Run</t>
+          <t>Tempo Run</t>
         </is>
       </c>
       <c r="C176" s="1" t="inlineStr">
@@ -5534,7 +5505,7 @@
       </c>
       <c r="B177" s="1" t="inlineStr">
         <is>
-          <t>30:30 Tempo Blocks</t>
+          <t>Long Nasal Run</t>
         </is>
       </c>
       <c r="C177" s="1" t="inlineStr">
@@ -5566,7 +5537,7 @@
       </c>
       <c r="B178" s="1" t="inlineStr">
         <is>
-          <t>Tempo Intervals (1min on / 1min easy)</t>
+          <t>30:30 Tempo Blocks</t>
         </is>
       </c>
       <c r="C178" s="1" t="inlineStr">
@@ -5598,7 +5569,7 @@
       </c>
       <c r="B179" s="1" t="inlineStr">
         <is>
-          <t>Cruise Intervals</t>
+          <t>Tempo Intervals (1min on / 1min easy)</t>
         </is>
       </c>
       <c r="C179" s="1" t="inlineStr">
@@ -5630,7 +5601,7 @@
       </c>
       <c r="B180" s="1" t="inlineStr">
         <is>
-          <t>Bike/Row/Ski Tempo Intervals</t>
+          <t>Cruise Intervals</t>
         </is>
       </c>
       <c r="C180" s="1" t="inlineStr">
@@ -5662,7 +5633,7 @@
       </c>
       <c r="B181" s="1" t="inlineStr">
         <is>
-          <t>Air Bike Sprints</t>
+          <t>Bike/Row/Ski Tempo Intervals</t>
         </is>
       </c>
       <c r="C181" s="1" t="inlineStr">
@@ -5694,7 +5665,7 @@
       </c>
       <c r="B182" s="1" t="inlineStr">
         <is>
-          <t>Row Intervals</t>
+          <t>Air Bike Sprints</t>
         </is>
       </c>
       <c r="C182" s="1" t="inlineStr">
@@ -5726,7 +5697,7 @@
       </c>
       <c r="B183" s="1" t="inlineStr">
         <is>
-          <t>SkiErg Intervals</t>
+          <t>Row Intervals</t>
         </is>
       </c>
       <c r="C183" s="1" t="inlineStr">
@@ -5758,7 +5729,7 @@
       </c>
       <c r="B184" s="1" t="inlineStr">
         <is>
-          <t>Assault Bike Intervals</t>
+          <t>SkiErg Intervals</t>
         </is>
       </c>
       <c r="C184" s="1" t="inlineStr">
@@ -5790,7 +5761,7 @@
       </c>
       <c r="B185" s="1" t="inlineStr">
         <is>
-          <t>Flush Run</t>
+          <t>Assault Bike Intervals</t>
         </is>
       </c>
       <c r="C185" s="1" t="inlineStr">
@@ -5822,7 +5793,7 @@
       </c>
       <c r="B186" s="1" t="inlineStr">
         <is>
-          <t>Easy Bike</t>
+          <t>Flush Run</t>
         </is>
       </c>
       <c r="C186" s="1" t="inlineStr">
@@ -5854,7 +5825,7 @@
       </c>
       <c r="B187" s="1" t="inlineStr">
         <is>
-          <t>Easy Row</t>
+          <t>Easy Bike</t>
         </is>
       </c>
       <c r="C187" s="1" t="inlineStr">
@@ -5886,7 +5857,7 @@
       </c>
       <c r="B188" s="1" t="inlineStr">
         <is>
-          <t>Easy Ski</t>
+          <t>Easy Row</t>
         </is>
       </c>
       <c r="C188" s="1" t="inlineStr">
@@ -5918,7 +5889,7 @@
       </c>
       <c r="B189" s="1" t="inlineStr">
         <is>
-          <t>Easy Swim</t>
+          <t>Easy Ski</t>
         </is>
       </c>
       <c r="C189" s="1" t="inlineStr">
@@ -5950,59 +5921,63 @@
       </c>
       <c r="B190" s="1" t="inlineStr">
         <is>
+          <t>Easy Swim</t>
+        </is>
+      </c>
+      <c r="C190" s="1" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D190" s="1" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E190" s="1" t="inlineStr">
+        <is>
+          <t>everyone</t>
+        </is>
+      </c>
+      <c r="F190" s="1" t="inlineStr">
+        <is>
+          <t>session format, not an individual movement — no meaningful muscle group.</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="1" t="inlineStr">
+        <is>
+          <t>Conditioning</t>
+        </is>
+      </c>
+      <c r="B191" s="1" t="inlineStr">
+        <is>
           <t>Light Circuits</t>
         </is>
       </c>
-      <c r="C190" s="1" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D190" s="1" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E190" s="1" t="inlineStr">
-        <is>
-          <t>everyone</t>
-        </is>
-      </c>
-      <c r="F190" s="1" t="inlineStr">
+      <c r="C191" s="1" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D191" s="1" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E191" s="1" t="inlineStr">
+        <is>
+          <t>everyone</t>
+        </is>
+      </c>
+      <c r="F191" s="1" t="inlineStr">
         <is>
           <t>session format, not an individual movement — no meaningful muscle group.</t>
         </is>
       </c>
     </row>
-    <row r="191"/>
-    <row r="192">
-      <c r="A192" s="1" t="inlineStr">
-        <is>
-          <t>Power</t>
-        </is>
-      </c>
-      <c r="B192" s="1" t="inlineStr">
-        <is>
-          <t>Vertical Jump</t>
-        </is>
-      </c>
-      <c r="C192" s="1" t="inlineStr">
-        <is>
-          <t>Glutes, Quads, Calves</t>
-        </is>
-      </c>
-      <c r="D192" s="1" t="inlineStr">
-        <is>
-          <t>Hamstrings, Midline</t>
-        </is>
-      </c>
-      <c r="E192" s="1" t="inlineStr">
-        <is>
-          <t>everyone</t>
-        </is>
-      </c>
-      <c r="F192" s="1" t="inlineStr"/>
-    </row>
+    <row r="192"/>
     <row r="193">
       <c r="A193" s="1" t="inlineStr">
         <is>
@@ -6011,17 +5986,17 @@
       </c>
       <c r="B193" s="1" t="inlineStr">
         <is>
-          <t>Pogo Hops</t>
+          <t>Vertical Jump</t>
         </is>
       </c>
       <c r="C193" s="1" t="inlineStr">
         <is>
-          <t>Calves</t>
+          <t>Glutes, Quads, Calves</t>
         </is>
       </c>
       <c r="D193" s="1" t="inlineStr">
         <is>
-          <t>Quads, Midline</t>
+          <t>Hamstrings, Midline</t>
         </is>
       </c>
       <c r="E193" s="1" t="inlineStr">
@@ -6029,11 +6004,7 @@
           <t>everyone</t>
         </is>
       </c>
-      <c r="F193" s="1" t="inlineStr">
-        <is>
-          <t>takes over when lower niggle (your spec)</t>
-        </is>
-      </c>
+      <c r="F193" s="1" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" s="1" t="inlineStr">
@@ -6043,17 +6014,17 @@
       </c>
       <c r="B194" s="1" t="inlineStr">
         <is>
-          <t>Lateral Jump</t>
+          <t>Pogo Hops</t>
         </is>
       </c>
       <c r="C194" s="1" t="inlineStr">
         <is>
-          <t>Glutes, Outer hip</t>
+          <t>Calves</t>
         </is>
       </c>
       <c r="D194" s="1" t="inlineStr">
         <is>
-          <t>Quads, Calves, Midline</t>
+          <t>Quads, Midline</t>
         </is>
       </c>
       <c r="E194" s="1" t="inlineStr">
@@ -6063,7 +6034,7 @@
       </c>
       <c r="F194" s="1" t="inlineStr">
         <is>
-          <t>your spec: beginner friendly</t>
+          <t>takes over when lower niggle (your spec)</t>
         </is>
       </c>
     </row>
@@ -6075,27 +6046,27 @@
       </c>
       <c r="B195" s="1" t="inlineStr">
         <is>
-          <t>Kneeling Jump</t>
+          <t>Lateral Jump</t>
         </is>
       </c>
       <c r="C195" s="1" t="inlineStr">
         <is>
-          <t>Glutes, Quads</t>
+          <t>Glutes, Outer hip</t>
         </is>
       </c>
       <c r="D195" s="1" t="inlineStr">
         <is>
-          <t>Hamstrings, Midline</t>
+          <t>Quads, Calves, Midline</t>
         </is>
       </c>
       <c r="E195" s="1" t="inlineStr">
         <is>
-          <t>2+ years</t>
+          <t>everyone</t>
         </is>
       </c>
       <c r="F195" s="1" t="inlineStr">
         <is>
-          <t>your spec: consistent+</t>
+          <t>your spec: beginner friendly</t>
         </is>
       </c>
     </row>
@@ -6107,17 +6078,17 @@
       </c>
       <c r="B196" s="1" t="inlineStr">
         <is>
-          <t>RFE Split Squat Jump</t>
+          <t>Kneeling Jump</t>
         </is>
       </c>
       <c r="C196" s="1" t="inlineStr">
         <is>
-          <t>Quads, Glutes</t>
+          <t>Glutes, Quads</t>
         </is>
       </c>
       <c r="D196" s="1" t="inlineStr">
         <is>
-          <t>Hamstrings, Calves, Midline</t>
+          <t>Hamstrings, Midline</t>
         </is>
       </c>
       <c r="E196" s="1" t="inlineStr">
@@ -6125,9 +6096,9 @@
           <t>2+ years</t>
         </is>
       </c>
-      <c r="F196" s="3" t="inlineStr">
-        <is>
-          <t>FLAG — gate proposed, confirm</t>
+      <c r="F196" s="1" t="inlineStr">
+        <is>
+          <t>your spec: consistent+</t>
         </is>
       </c>
     </row>
@@ -6139,25 +6110,29 @@
       </c>
       <c r="B197" s="1" t="inlineStr">
         <is>
-          <t>Explosive Push-up</t>
+          <t>RFE Split Squat Jump</t>
         </is>
       </c>
       <c r="C197" s="1" t="inlineStr">
         <is>
-          <t>Chest, Triceps</t>
+          <t>Quads, Glutes</t>
         </is>
       </c>
       <c r="D197" s="1" t="inlineStr">
         <is>
-          <t>Shoulders, Midline</t>
+          <t>Hamstrings, Calves, Midline</t>
         </is>
       </c>
       <c r="E197" s="1" t="inlineStr">
         <is>
-          <t>everyone</t>
-        </is>
-      </c>
-      <c r="F197" s="1" t="inlineStr"/>
+          <t>2+ years</t>
+        </is>
+      </c>
+      <c r="F197" s="3" t="inlineStr">
+        <is>
+          <t>FLAG — gate proposed, confirm</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="1" t="inlineStr">
@@ -6167,7 +6142,7 @@
       </c>
       <c r="B198" s="1" t="inlineStr">
         <is>
-          <t>Speed Bench</t>
+          <t>Explosive Push-up</t>
         </is>
       </c>
       <c r="C198" s="1" t="inlineStr">
@@ -6177,19 +6152,15 @@
       </c>
       <c r="D198" s="1" t="inlineStr">
         <is>
-          <t>Shoulders, Lats</t>
+          <t>Shoulders, Midline</t>
         </is>
       </c>
       <c r="E198" s="1" t="inlineStr">
         <is>
-          <t>2+ years</t>
-        </is>
-      </c>
-      <c r="F198" s="3" t="inlineStr">
-        <is>
-          <t>FLAG — gate proposed, confirm</t>
-        </is>
-      </c>
+          <t>everyone</t>
+        </is>
+      </c>
+      <c r="F198" s="1" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" s="1" t="inlineStr">
@@ -6199,25 +6170,57 @@
       </c>
       <c r="B199" s="1" t="inlineStr">
         <is>
+          <t>Speed Bench</t>
+        </is>
+      </c>
+      <c r="C199" s="1" t="inlineStr">
+        <is>
+          <t>Chest, Triceps</t>
+        </is>
+      </c>
+      <c r="D199" s="1" t="inlineStr">
+        <is>
+          <t>Shoulders, Lats</t>
+        </is>
+      </c>
+      <c r="E199" s="1" t="inlineStr">
+        <is>
+          <t>2+ years</t>
+        </is>
+      </c>
+      <c r="F199" s="3" t="inlineStr">
+        <is>
+          <t>FLAG — gate proposed, confirm</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="1" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="B200" s="1" t="inlineStr">
+        <is>
           <t>Speed Trap Bar Deadlift</t>
         </is>
       </c>
-      <c r="C199" s="1" t="inlineStr">
+      <c r="C200" s="1" t="inlineStr">
         <is>
           <t>Glutes, Hamstrings</t>
         </is>
       </c>
-      <c r="D199" s="1" t="inlineStr">
+      <c r="D200" s="1" t="inlineStr">
         <is>
           <t>Quads, Upper back, Grip</t>
         </is>
       </c>
-      <c r="E199" s="1" t="inlineStr">
+      <c r="E200" s="1" t="inlineStr">
         <is>
           <t>2+ years</t>
         </is>
       </c>
-      <c r="F199" s="3" t="inlineStr">
+      <c r="F200" s="3" t="inlineStr">
         <is>
           <t>FLAG — gate proposed, confirm</t>
         </is>

--- a/docs/MUSCLE_EXPERIENCE_FINAL_2026-07-25.xlsx
+++ b/docs/MUSCLE_EXPERIENCE_FINAL_2026-07-25.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F200"/>
+  <dimension ref="A1:F203"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -4604,17 +4604,17 @@
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>Easy cardio (zone 1)</t>
+          <t>Mobility</t>
         </is>
       </c>
       <c r="B148" s="1" t="inlineStr">
         <is>
-          <t>Light Walk or Stationary Bike</t>
+          <t>Butterfly Stretch</t>
         </is>
       </c>
       <c r="C148" s="1" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Groin, Hips</t>
         </is>
       </c>
       <c r="D148" s="1" t="inlineStr">
@@ -4632,17 +4632,17 @@
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>Easy cardio (zone 1)</t>
+          <t>Mobility</t>
         </is>
       </c>
       <c r="B149" s="1" t="inlineStr">
         <is>
-          <t>Incline Treadmill Walk</t>
+          <t>Pissing Dog Against Wall</t>
         </is>
       </c>
       <c r="C149" s="1" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Glutes, Hips</t>
         </is>
       </c>
       <c r="D149" s="1" t="inlineStr">
@@ -4660,17 +4660,17 @@
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>Easy cardio (zone 1)</t>
+          <t>Mobility</t>
         </is>
       </c>
       <c r="B150" s="1" t="inlineStr">
         <is>
-          <t>Outdoor Walk</t>
+          <t>Jefferson Curl</t>
         </is>
       </c>
       <c r="C150" s="1" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Upper back, Low back, Hamstrings</t>
         </is>
       </c>
       <c r="D150" s="1" t="inlineStr">
@@ -4693,12 +4693,12 @@
       </c>
       <c r="B151" s="1" t="inlineStr">
         <is>
-          <t>Light Skipping</t>
+          <t>Light Walk or Stationary Bike</t>
         </is>
       </c>
       <c r="C151" s="1" t="inlineStr">
         <is>
-          <t>Calves</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D151" s="1" t="inlineStr">
@@ -4716,12 +4716,12 @@
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>Breathing reset</t>
+          <t>Easy cardio (zone 1)</t>
         </is>
       </c>
       <c r="B152" s="1" t="inlineStr">
         <is>
-          <t>90/90 Breathing</t>
+          <t>Incline Treadmill Walk</t>
         </is>
       </c>
       <c r="C152" s="1" t="inlineStr">
@@ -4744,12 +4744,12 @@
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>Breathing reset</t>
+          <t>Easy cardio (zone 1)</t>
         </is>
       </c>
       <c r="B153" s="1" t="inlineStr">
         <is>
-          <t>Crocodile Breathing</t>
+          <t>Outdoor Walk</t>
         </is>
       </c>
       <c r="C153" s="1" t="inlineStr">
@@ -4772,17 +4772,17 @@
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>Breathing reset</t>
+          <t>Easy cardio (zone 1)</t>
         </is>
       </c>
       <c r="B154" s="1" t="inlineStr">
         <is>
-          <t>Box Breathing</t>
+          <t>Light Skipping</t>
         </is>
       </c>
       <c r="C154" s="1" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Calves</t>
         </is>
       </c>
       <c r="D154" s="1" t="inlineStr">
@@ -4805,7 +4805,7 @@
       </c>
       <c r="B155" s="1" t="inlineStr">
         <is>
-          <t>Child's Pose with Breathing</t>
+          <t>90/90 Breathing</t>
         </is>
       </c>
       <c r="C155" s="1" t="inlineStr">
@@ -4828,12 +4828,12 @@
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>Conditioning</t>
+          <t>Breathing reset</t>
         </is>
       </c>
       <c r="B156" s="1" t="inlineStr">
         <is>
-          <t>Sprint Intervals</t>
+          <t>Crocodile Breathing</t>
         </is>
       </c>
       <c r="C156" s="1" t="inlineStr">
@@ -4848,24 +4848,20 @@
       </c>
       <c r="E156" s="1" t="inlineStr">
         <is>
-          <t>1+ years</t>
-        </is>
-      </c>
-      <c r="F156" s="1" t="inlineStr">
-        <is>
-          <t>⚑ field sprint at top-end speed; hamstring/calf tagged 'avoid'. Gate here is conditioning base, not lifting experience, so this ladder may not be the right instrument at all.</t>
-        </is>
-      </c>
+          <t>everyone</t>
+        </is>
+      </c>
+      <c r="F156" s="1" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="1" t="inlineStr">
         <is>
-          <t>Conditioning</t>
+          <t>Breathing reset</t>
         </is>
       </c>
       <c r="B157" s="1" t="inlineStr">
         <is>
-          <t>Hill Sprints</t>
+          <t>Box Breathing</t>
         </is>
       </c>
       <c r="C157" s="1" t="inlineStr">
@@ -4880,24 +4876,20 @@
       </c>
       <c r="E157" s="1" t="inlineStr">
         <is>
-          <t>1+ years</t>
-        </is>
-      </c>
-      <c r="F157" s="1" t="inlineStr">
-        <is>
-          <t>⚑ field sprint at top-end speed; hamstring/calf tagged 'avoid'. Gate here is conditioning base, not lifting experience, so this ladder may not be the right instrument at all.</t>
-        </is>
-      </c>
+          <t>everyone</t>
+        </is>
+      </c>
+      <c r="F157" s="1" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="1" t="inlineStr">
         <is>
-          <t>Conditioning</t>
+          <t>Breathing reset</t>
         </is>
       </c>
       <c r="B158" s="1" t="inlineStr">
         <is>
-          <t>Quality Sprints</t>
+          <t>Child's Pose with Breathing</t>
         </is>
       </c>
       <c r="C158" s="1" t="inlineStr">
@@ -4912,14 +4904,10 @@
       </c>
       <c r="E158" s="1" t="inlineStr">
         <is>
-          <t>1+ years</t>
-        </is>
-      </c>
-      <c r="F158" s="1" t="inlineStr">
-        <is>
-          <t>⚑ field sprint at top-end speed; hamstring/calf tagged 'avoid'. Gate here is conditioning base, not lifting experience, so this ladder may not be the right instrument at all.</t>
-        </is>
-      </c>
+          <t>everyone</t>
+        </is>
+      </c>
+      <c r="F158" s="1" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" s="1" t="inlineStr">
@@ -4929,7 +4917,7 @@
       </c>
       <c r="B159" s="1" t="inlineStr">
         <is>
-          <t>MAS Training</t>
+          <t>Sprint Intervals</t>
         </is>
       </c>
       <c r="C159" s="1" t="inlineStr">
@@ -4961,7 +4949,7 @@
       </c>
       <c r="B160" s="1" t="inlineStr">
         <is>
-          <t>Flying Sprints</t>
+          <t>Hill Sprints</t>
         </is>
       </c>
       <c r="C160" s="1" t="inlineStr">
@@ -4981,7 +4969,7 @@
       </c>
       <c r="F160" s="1" t="inlineStr">
         <is>
-          <t>⚑ field sprint at top-end speed. Gate here is conditioning base, not lifting experience, so this ladder may not be the right instrument at all.</t>
+          <t>⚑ field sprint at top-end speed; hamstring/calf tagged 'avoid'. Gate here is conditioning base, not lifting experience, so this ladder may not be the right instrument at all.</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4981,7 @@
       </c>
       <c r="B161" s="1" t="inlineStr">
         <is>
-          <t>MAS 15:15 Blocks</t>
+          <t>Quality Sprints</t>
         </is>
       </c>
       <c r="C161" s="1" t="inlineStr">
@@ -5013,7 +5001,7 @@
       </c>
       <c r="F161" s="1" t="inlineStr">
         <is>
-          <t>⚑ field sprint at top-end speed. Gate here is conditioning base, not lifting experience, so this ladder may not be the right instrument at all.</t>
+          <t>⚑ field sprint at top-end speed; hamstring/calf tagged 'avoid'. Gate here is conditioning base, not lifting experience, so this ladder may not be the right instrument at all.</t>
         </is>
       </c>
     </row>
@@ -5025,7 +5013,7 @@
       </c>
       <c r="B162" s="1" t="inlineStr">
         <is>
-          <t>Tabata Intervals</t>
+          <t>MAS Training</t>
         </is>
       </c>
       <c r="C162" s="1" t="inlineStr">
@@ -5040,12 +5028,12 @@
       </c>
       <c r="E162" s="1" t="inlineStr">
         <is>
-          <t>everyone</t>
+          <t>1+ years</t>
         </is>
       </c>
       <c r="F162" s="1" t="inlineStr">
         <is>
-          <t>session format, not an individual movement — no meaningful muscle group.</t>
+          <t>⚑ field sprint at top-end speed; hamstring/calf tagged 'avoid'. Gate here is conditioning base, not lifting experience, so this ladder may not be the right instrument at all.</t>
         </is>
       </c>
     </row>
@@ -5057,7 +5045,7 @@
       </c>
       <c r="B163" s="1" t="inlineStr">
         <is>
-          <t>Inverse Tabata</t>
+          <t>Flying Sprints</t>
         </is>
       </c>
       <c r="C163" s="1" t="inlineStr">
@@ -5072,12 +5060,12 @@
       </c>
       <c r="E163" s="1" t="inlineStr">
         <is>
-          <t>everyone</t>
+          <t>1+ years</t>
         </is>
       </c>
       <c r="F163" s="1" t="inlineStr">
         <is>
-          <t>session format, not an individual movement — no meaningful muscle group.</t>
+          <t>⚑ field sprint at top-end speed. Gate here is conditioning base, not lifting experience, so this ladder may not be the right instrument at all.</t>
         </is>
       </c>
     </row>
@@ -5089,7 +5077,7 @@
       </c>
       <c r="B164" s="1" t="inlineStr">
         <is>
-          <t>Max Effort Sprint Accumulation</t>
+          <t>MAS 15:15 Blocks</t>
         </is>
       </c>
       <c r="C164" s="1" t="inlineStr">
@@ -5104,12 +5092,12 @@
       </c>
       <c r="E164" s="1" t="inlineStr">
         <is>
-          <t>everyone</t>
+          <t>1+ years</t>
         </is>
       </c>
       <c r="F164" s="1" t="inlineStr">
         <is>
-          <t>session format, not an individual movement — no meaningful muscle group.</t>
+          <t>⚑ field sprint at top-end speed. Gate here is conditioning base, not lifting experience, so this ladder may not be the right instrument at all.</t>
         </is>
       </c>
     </row>
@@ -5121,7 +5109,7 @@
       </c>
       <c r="B165" s="1" t="inlineStr">
         <is>
-          <t>Free Sprint Session</t>
+          <t>Tabata Intervals</t>
         </is>
       </c>
       <c r="C165" s="1" t="inlineStr">
@@ -5136,12 +5124,12 @@
       </c>
       <c r="E165" s="1" t="inlineStr">
         <is>
-          <t>1+ years</t>
+          <t>everyone</t>
         </is>
       </c>
       <c r="F165" s="1" t="inlineStr">
         <is>
-          <t>⚑ field sprint at top-end speed; hamstring/calf tagged 'avoid'. Gate here is conditioning base, not lifting experience, so this ladder may not be the right instrument at all.</t>
+          <t>session format, not an individual movement — no meaningful muscle group.</t>
         </is>
       </c>
     </row>
@@ -5153,7 +5141,7 @@
       </c>
       <c r="B166" s="1" t="inlineStr">
         <is>
-          <t>Long Run</t>
+          <t>Inverse Tabata</t>
         </is>
       </c>
       <c r="C166" s="1" t="inlineStr">
@@ -5185,7 +5173,7 @@
       </c>
       <c r="B167" s="1" t="inlineStr">
         <is>
-          <t>6x1km</t>
+          <t>Max Effort Sprint Accumulation</t>
         </is>
       </c>
       <c r="C167" s="1" t="inlineStr">
@@ -5217,7 +5205,7 @@
       </c>
       <c r="B168" s="1" t="inlineStr">
         <is>
-          <t>1km Repeat Intervals</t>
+          <t>Free Sprint Session</t>
         </is>
       </c>
       <c r="C168" s="1" t="inlineStr">
@@ -5232,12 +5220,12 @@
       </c>
       <c r="E168" s="1" t="inlineStr">
         <is>
-          <t>everyone</t>
+          <t>1+ years</t>
         </is>
       </c>
       <c r="F168" s="1" t="inlineStr">
         <is>
-          <t>session format, not an individual movement — no meaningful muscle group.</t>
+          <t>⚑ field sprint at top-end speed; hamstring/calf tagged 'avoid'. Gate here is conditioning base, not lifting experience, so this ladder may not be the right instrument at all.</t>
         </is>
       </c>
     </row>
@@ -5249,7 +5237,7 @@
       </c>
       <c r="B169" s="1" t="inlineStr">
         <is>
-          <t>4x4 VO2</t>
+          <t>Long Run</t>
         </is>
       </c>
       <c r="C169" s="1" t="inlineStr">
@@ -5281,7 +5269,7 @@
       </c>
       <c r="B170" s="1" t="inlineStr">
         <is>
-          <t>200m/400m Repeat Runs</t>
+          <t>6x1km</t>
         </is>
       </c>
       <c r="C170" s="1" t="inlineStr">
@@ -5296,12 +5284,12 @@
       </c>
       <c r="E170" s="1" t="inlineStr">
         <is>
-          <t>1+ years</t>
+          <t>everyone</t>
         </is>
       </c>
       <c r="F170" s="1" t="inlineStr">
         <is>
-          <t>⚑ sprint-adjacent speed endurance at high impact — the training-age ladder is a rough fit for a session format.</t>
+          <t>session format, not an individual movement — no meaningful muscle group.</t>
         </is>
       </c>
     </row>
@@ -5313,7 +5301,7 @@
       </c>
       <c r="B171" s="1" t="inlineStr">
         <is>
-          <t>Footy Fartlek</t>
+          <t>1km Repeat Intervals</t>
         </is>
       </c>
       <c r="C171" s="1" t="inlineStr">
@@ -5345,7 +5333,7 @@
       </c>
       <c r="B172" s="1" t="inlineStr">
         <is>
-          <t>Hard Row Intervals</t>
+          <t>4x4 VO2</t>
         </is>
       </c>
       <c r="C172" s="1" t="inlineStr">
@@ -5377,7 +5365,7 @@
       </c>
       <c r="B173" s="1" t="inlineStr">
         <is>
-          <t>Hard SkiErg Intervals</t>
+          <t>200m/400m Repeat Runs</t>
         </is>
       </c>
       <c r="C173" s="1" t="inlineStr">
@@ -5392,12 +5380,12 @@
       </c>
       <c r="E173" s="1" t="inlineStr">
         <is>
-          <t>everyone</t>
+          <t>1+ years</t>
         </is>
       </c>
       <c r="F173" s="1" t="inlineStr">
         <is>
-          <t>session format, not an individual movement — no meaningful muscle group.</t>
+          <t>⚑ sprint-adjacent speed endurance at high impact — the training-age ladder is a rough fit for a session format.</t>
         </is>
       </c>
     </row>
@@ -5409,7 +5397,7 @@
       </c>
       <c r="B174" s="1" t="inlineStr">
         <is>
-          <t>Hard Assault Bike Intervals</t>
+          <t>Footy Fartlek</t>
         </is>
       </c>
       <c r="C174" s="1" t="inlineStr">
@@ -5441,7 +5429,7 @@
       </c>
       <c r="B175" s="1" t="inlineStr">
         <is>
-          <t>Erg EMOM</t>
+          <t>Hard Row Intervals</t>
         </is>
       </c>
       <c r="C175" s="1" t="inlineStr">
@@ -5473,7 +5461,7 @@
       </c>
       <c r="B176" s="1" t="inlineStr">
         <is>
-          <t>Tempo Run</t>
+          <t>Hard SkiErg Intervals</t>
         </is>
       </c>
       <c r="C176" s="1" t="inlineStr">
@@ -5505,7 +5493,7 @@
       </c>
       <c r="B177" s="1" t="inlineStr">
         <is>
-          <t>Long Nasal Run</t>
+          <t>Hard Assault Bike Intervals</t>
         </is>
       </c>
       <c r="C177" s="1" t="inlineStr">
@@ -5537,7 +5525,7 @@
       </c>
       <c r="B178" s="1" t="inlineStr">
         <is>
-          <t>30:30 Tempo Blocks</t>
+          <t>Erg EMOM</t>
         </is>
       </c>
       <c r="C178" s="1" t="inlineStr">
@@ -5569,7 +5557,7 @@
       </c>
       <c r="B179" s="1" t="inlineStr">
         <is>
-          <t>Tempo Intervals (1min on / 1min easy)</t>
+          <t>Tempo Run</t>
         </is>
       </c>
       <c r="C179" s="1" t="inlineStr">
@@ -5601,7 +5589,7 @@
       </c>
       <c r="B180" s="1" t="inlineStr">
         <is>
-          <t>Cruise Intervals</t>
+          <t>Long Nasal Run</t>
         </is>
       </c>
       <c r="C180" s="1" t="inlineStr">
@@ -5633,7 +5621,7 @@
       </c>
       <c r="B181" s="1" t="inlineStr">
         <is>
-          <t>Bike/Row/Ski Tempo Intervals</t>
+          <t>30:30 Tempo Blocks</t>
         </is>
       </c>
       <c r="C181" s="1" t="inlineStr">
@@ -5665,7 +5653,7 @@
       </c>
       <c r="B182" s="1" t="inlineStr">
         <is>
-          <t>Air Bike Sprints</t>
+          <t>Tempo Intervals (1min on / 1min easy)</t>
         </is>
       </c>
       <c r="C182" s="1" t="inlineStr">
@@ -5697,7 +5685,7 @@
       </c>
       <c r="B183" s="1" t="inlineStr">
         <is>
-          <t>Row Intervals</t>
+          <t>Cruise Intervals</t>
         </is>
       </c>
       <c r="C183" s="1" t="inlineStr">
@@ -5729,7 +5717,7 @@
       </c>
       <c r="B184" s="1" t="inlineStr">
         <is>
-          <t>SkiErg Intervals</t>
+          <t>Bike/Row/Ski Tempo Intervals</t>
         </is>
       </c>
       <c r="C184" s="1" t="inlineStr">
@@ -5761,7 +5749,7 @@
       </c>
       <c r="B185" s="1" t="inlineStr">
         <is>
-          <t>Assault Bike Intervals</t>
+          <t>Air Bike Sprints</t>
         </is>
       </c>
       <c r="C185" s="1" t="inlineStr">
@@ -5793,7 +5781,7 @@
       </c>
       <c r="B186" s="1" t="inlineStr">
         <is>
-          <t>Flush Run</t>
+          <t>Row Intervals</t>
         </is>
       </c>
       <c r="C186" s="1" t="inlineStr">
@@ -5825,7 +5813,7 @@
       </c>
       <c r="B187" s="1" t="inlineStr">
         <is>
-          <t>Easy Bike</t>
+          <t>SkiErg Intervals</t>
         </is>
       </c>
       <c r="C187" s="1" t="inlineStr">
@@ -5857,7 +5845,7 @@
       </c>
       <c r="B188" s="1" t="inlineStr">
         <is>
-          <t>Easy Row</t>
+          <t>Assault Bike Intervals</t>
         </is>
       </c>
       <c r="C188" s="1" t="inlineStr">
@@ -5889,7 +5877,7 @@
       </c>
       <c r="B189" s="1" t="inlineStr">
         <is>
-          <t>Easy Ski</t>
+          <t>Flush Run</t>
         </is>
       </c>
       <c r="C189" s="1" t="inlineStr">
@@ -5921,7 +5909,7 @@
       </c>
       <c r="B190" s="1" t="inlineStr">
         <is>
-          <t>Easy Swim</t>
+          <t>Easy Bike</t>
         </is>
       </c>
       <c r="C190" s="1" t="inlineStr">
@@ -5953,7 +5941,7 @@
       </c>
       <c r="B191" s="1" t="inlineStr">
         <is>
-          <t>Light Circuits</t>
+          <t>Easy Row</t>
         </is>
       </c>
       <c r="C191" s="1" t="inlineStr">
@@ -5977,26 +5965,57 @@
         </is>
       </c>
     </row>
-    <row r="192"/>
+    <row r="192">
+      <c r="A192" s="1" t="inlineStr">
+        <is>
+          <t>Conditioning</t>
+        </is>
+      </c>
+      <c r="B192" s="1" t="inlineStr">
+        <is>
+          <t>Easy Ski</t>
+        </is>
+      </c>
+      <c r="C192" s="1" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D192" s="1" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E192" s="1" t="inlineStr">
+        <is>
+          <t>everyone</t>
+        </is>
+      </c>
+      <c r="F192" s="1" t="inlineStr">
+        <is>
+          <t>session format, not an individual movement — no meaningful muscle group.</t>
+        </is>
+      </c>
+    </row>
     <row r="193">
       <c r="A193" s="1" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Conditioning</t>
         </is>
       </c>
       <c r="B193" s="1" t="inlineStr">
         <is>
-          <t>Vertical Jump</t>
+          <t>Easy Swim</t>
         </is>
       </c>
       <c r="C193" s="1" t="inlineStr">
         <is>
-          <t>Glutes, Quads, Calves</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D193" s="1" t="inlineStr">
         <is>
-          <t>Hamstrings, Midline</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E193" s="1" t="inlineStr">
@@ -6004,27 +6023,31 @@
           <t>everyone</t>
         </is>
       </c>
-      <c r="F193" s="1" t="inlineStr"/>
+      <c r="F193" s="1" t="inlineStr">
+        <is>
+          <t>session format, not an individual movement — no meaningful muscle group.</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="1" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Conditioning</t>
         </is>
       </c>
       <c r="B194" s="1" t="inlineStr">
         <is>
-          <t>Pogo Hops</t>
+          <t>Light Circuits</t>
         </is>
       </c>
       <c r="C194" s="1" t="inlineStr">
         <is>
-          <t>Calves</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D194" s="1" t="inlineStr">
         <is>
-          <t>Quads, Midline</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E194" s="1" t="inlineStr">
@@ -6034,42 +6057,11 @@
       </c>
       <c r="F194" s="1" t="inlineStr">
         <is>
-          <t>takes over when lower niggle (your spec)</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" s="1" t="inlineStr">
-        <is>
-          <t>Power</t>
-        </is>
-      </c>
-      <c r="B195" s="1" t="inlineStr">
-        <is>
-          <t>Lateral Jump</t>
-        </is>
-      </c>
-      <c r="C195" s="1" t="inlineStr">
-        <is>
-          <t>Glutes, Outer hip</t>
-        </is>
-      </c>
-      <c r="D195" s="1" t="inlineStr">
-        <is>
-          <t>Quads, Calves, Midline</t>
-        </is>
-      </c>
-      <c r="E195" s="1" t="inlineStr">
-        <is>
-          <t>everyone</t>
-        </is>
-      </c>
-      <c r="F195" s="1" t="inlineStr">
-        <is>
-          <t>your spec: beginner friendly</t>
-        </is>
-      </c>
-    </row>
+          <t>session format, not an individual movement — no meaningful muscle group.</t>
+        </is>
+      </c>
+    </row>
+    <row r="195"/>
     <row r="196">
       <c r="A196" s="1" t="inlineStr">
         <is>
@@ -6078,12 +6070,12 @@
       </c>
       <c r="B196" s="1" t="inlineStr">
         <is>
-          <t>Kneeling Jump</t>
+          <t>Vertical Jump</t>
         </is>
       </c>
       <c r="C196" s="1" t="inlineStr">
         <is>
-          <t>Glutes, Quads</t>
+          <t>Glutes, Quads, Calves</t>
         </is>
       </c>
       <c r="D196" s="1" t="inlineStr">
@@ -6093,14 +6085,10 @@
       </c>
       <c r="E196" s="1" t="inlineStr">
         <is>
-          <t>2+ years</t>
-        </is>
-      </c>
-      <c r="F196" s="1" t="inlineStr">
-        <is>
-          <t>your spec: consistent+</t>
-        </is>
-      </c>
+          <t>everyone</t>
+        </is>
+      </c>
+      <c r="F196" s="1" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" s="1" t="inlineStr">
@@ -6110,27 +6098,27 @@
       </c>
       <c r="B197" s="1" t="inlineStr">
         <is>
-          <t>RFE Split Squat Jump</t>
+          <t>Pogo Hops</t>
         </is>
       </c>
       <c r="C197" s="1" t="inlineStr">
         <is>
-          <t>Quads, Glutes</t>
+          <t>Calves</t>
         </is>
       </c>
       <c r="D197" s="1" t="inlineStr">
         <is>
-          <t>Hamstrings, Calves, Midline</t>
+          <t>Quads, Midline</t>
         </is>
       </c>
       <c r="E197" s="1" t="inlineStr">
         <is>
-          <t>2+ years</t>
-        </is>
-      </c>
-      <c r="F197" s="3" t="inlineStr">
-        <is>
-          <t>FLAG — gate proposed, confirm</t>
+          <t>everyone</t>
+        </is>
+      </c>
+      <c r="F197" s="1" t="inlineStr">
+        <is>
+          <t>takes over when lower niggle (your spec)</t>
         </is>
       </c>
     </row>
@@ -6142,17 +6130,17 @@
       </c>
       <c r="B198" s="1" t="inlineStr">
         <is>
-          <t>Explosive Push-up</t>
+          <t>Lateral Jump</t>
         </is>
       </c>
       <c r="C198" s="1" t="inlineStr">
         <is>
-          <t>Chest, Triceps</t>
+          <t>Glutes, Outer hip</t>
         </is>
       </c>
       <c r="D198" s="1" t="inlineStr">
         <is>
-          <t>Shoulders, Midline</t>
+          <t>Quads, Calves, Midline</t>
         </is>
       </c>
       <c r="E198" s="1" t="inlineStr">
@@ -6160,7 +6148,11 @@
           <t>everyone</t>
         </is>
       </c>
-      <c r="F198" s="1" t="inlineStr"/>
+      <c r="F198" s="1" t="inlineStr">
+        <is>
+          <t>your spec: beginner friendly</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="1" t="inlineStr">
@@ -6170,17 +6162,17 @@
       </c>
       <c r="B199" s="1" t="inlineStr">
         <is>
-          <t>Speed Bench</t>
+          <t>Kneeling Jump</t>
         </is>
       </c>
       <c r="C199" s="1" t="inlineStr">
         <is>
-          <t>Chest, Triceps</t>
+          <t>Glutes, Quads</t>
         </is>
       </c>
       <c r="D199" s="1" t="inlineStr">
         <is>
-          <t>Shoulders, Lats</t>
+          <t>Hamstrings, Midline</t>
         </is>
       </c>
       <c r="E199" s="1" t="inlineStr">
@@ -6188,9 +6180,9 @@
           <t>2+ years</t>
         </is>
       </c>
-      <c r="F199" s="3" t="inlineStr">
-        <is>
-          <t>FLAG — gate proposed, confirm</t>
+      <c r="F199" s="1" t="inlineStr">
+        <is>
+          <t>your spec: consistent+</t>
         </is>
       </c>
     </row>
@@ -6202,25 +6194,117 @@
       </c>
       <c r="B200" s="1" t="inlineStr">
         <is>
+          <t>RFE Split Squat Jump</t>
+        </is>
+      </c>
+      <c r="C200" s="1" t="inlineStr">
+        <is>
+          <t>Quads, Glutes</t>
+        </is>
+      </c>
+      <c r="D200" s="1" t="inlineStr">
+        <is>
+          <t>Hamstrings, Calves, Midline</t>
+        </is>
+      </c>
+      <c r="E200" s="1" t="inlineStr">
+        <is>
+          <t>2+ years</t>
+        </is>
+      </c>
+      <c r="F200" s="3" t="inlineStr">
+        <is>
+          <t>FLAG — gate proposed, confirm</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="1" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="B201" s="1" t="inlineStr">
+        <is>
+          <t>Explosive Push-up</t>
+        </is>
+      </c>
+      <c r="C201" s="1" t="inlineStr">
+        <is>
+          <t>Chest, Triceps</t>
+        </is>
+      </c>
+      <c r="D201" s="1" t="inlineStr">
+        <is>
+          <t>Shoulders, Midline</t>
+        </is>
+      </c>
+      <c r="E201" s="1" t="inlineStr">
+        <is>
+          <t>everyone</t>
+        </is>
+      </c>
+      <c r="F201" s="1" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="1" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="B202" s="1" t="inlineStr">
+        <is>
+          <t>Speed Bench</t>
+        </is>
+      </c>
+      <c r="C202" s="1" t="inlineStr">
+        <is>
+          <t>Chest, Triceps</t>
+        </is>
+      </c>
+      <c r="D202" s="1" t="inlineStr">
+        <is>
+          <t>Shoulders, Lats</t>
+        </is>
+      </c>
+      <c r="E202" s="1" t="inlineStr">
+        <is>
+          <t>2+ years</t>
+        </is>
+      </c>
+      <c r="F202" s="3" t="inlineStr">
+        <is>
+          <t>FLAG — gate proposed, confirm</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="1" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="B203" s="1" t="inlineStr">
+        <is>
           <t>Speed Trap Bar Deadlift</t>
         </is>
       </c>
-      <c r="C200" s="1" t="inlineStr">
+      <c r="C203" s="1" t="inlineStr">
         <is>
           <t>Glutes, Hamstrings</t>
         </is>
       </c>
-      <c r="D200" s="1" t="inlineStr">
+      <c r="D203" s="1" t="inlineStr">
         <is>
           <t>Quads, Upper back, Grip</t>
         </is>
       </c>
-      <c r="E200" s="1" t="inlineStr">
+      <c r="E203" s="1" t="inlineStr">
         <is>
           <t>2+ years</t>
         </is>
       </c>
-      <c r="F200" s="3" t="inlineStr">
+      <c r="F203" s="3" t="inlineStr">
         <is>
           <t>FLAG — gate proposed, confirm</t>
         </is>

--- a/docs/MUSCLE_EXPERIENCE_FINAL_2026-07-25.xlsx
+++ b/docs/MUSCLE_EXPERIENCE_FINAL_2026-07-25.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F203"/>
+  <dimension ref="A1:F204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -4688,17 +4688,17 @@
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>Easy cardio (zone 1)</t>
+          <t>Mobility</t>
         </is>
       </c>
       <c r="B151" s="1" t="inlineStr">
         <is>
-          <t>Light Walk or Stationary Bike</t>
+          <t>Dumbbell Pullovers</t>
         </is>
       </c>
       <c r="C151" s="1" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Upper back, Shoulders</t>
         </is>
       </c>
       <c r="D151" s="1" t="inlineStr">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="B152" s="1" t="inlineStr">
         <is>
-          <t>Incline Treadmill Walk</t>
+          <t>Light Walk or Stationary Bike</t>
         </is>
       </c>
       <c r="C152" s="1" t="inlineStr">
@@ -4749,7 +4749,7 @@
       </c>
       <c r="B153" s="1" t="inlineStr">
         <is>
-          <t>Outdoor Walk</t>
+          <t>Incline Treadmill Walk</t>
         </is>
       </c>
       <c r="C153" s="1" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="B154" s="1" t="inlineStr">
         <is>
-          <t>Light Skipping</t>
+          <t>Outdoor Walk</t>
         </is>
       </c>
       <c r="C154" s="1" t="inlineStr">
         <is>
-          <t>Calves</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D154" s="1" t="inlineStr">
@@ -4800,17 +4800,17 @@
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>Breathing reset</t>
+          <t>Easy cardio (zone 1)</t>
         </is>
       </c>
       <c r="B155" s="1" t="inlineStr">
         <is>
-          <t>90/90 Breathing</t>
+          <t>Light Skipping</t>
         </is>
       </c>
       <c r="C155" s="1" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Calves</t>
         </is>
       </c>
       <c r="D155" s="1" t="inlineStr">
@@ -4833,7 +4833,7 @@
       </c>
       <c r="B156" s="1" t="inlineStr">
         <is>
-          <t>Crocodile Breathing</t>
+          <t>90/90 Breathing</t>
         </is>
       </c>
       <c r="C156" s="1" t="inlineStr">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="B157" s="1" t="inlineStr">
         <is>
-          <t>Box Breathing</t>
+          <t>Crocodile Breathing</t>
         </is>
       </c>
       <c r="C157" s="1" t="inlineStr">
@@ -4889,7 +4889,7 @@
       </c>
       <c r="B158" s="1" t="inlineStr">
         <is>
-          <t>Child's Pose with Breathing</t>
+          <t>Box Breathing</t>
         </is>
       </c>
       <c r="C158" s="1" t="inlineStr">
@@ -4912,12 +4912,12 @@
     <row r="159">
       <c r="A159" s="1" t="inlineStr">
         <is>
-          <t>Conditioning</t>
+          <t>Breathing reset</t>
         </is>
       </c>
       <c r="B159" s="1" t="inlineStr">
         <is>
-          <t>Sprint Intervals</t>
+          <t>Child's Pose with Breathing</t>
         </is>
       </c>
       <c r="C159" s="1" t="inlineStr">
@@ -4932,14 +4932,10 @@
       </c>
       <c r="E159" s="1" t="inlineStr">
         <is>
-          <t>1+ years</t>
-        </is>
-      </c>
-      <c r="F159" s="1" t="inlineStr">
-        <is>
-          <t>⚑ field sprint at top-end speed; hamstring/calf tagged 'avoid'. Gate here is conditioning base, not lifting experience, so this ladder may not be the right instrument at all.</t>
-        </is>
-      </c>
+          <t>everyone</t>
+        </is>
+      </c>
+      <c r="F159" s="1" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" s="1" t="inlineStr">
@@ -4949,7 +4945,7 @@
       </c>
       <c r="B160" s="1" t="inlineStr">
         <is>
-          <t>Hill Sprints</t>
+          <t>Sprint Intervals</t>
         </is>
       </c>
       <c r="C160" s="1" t="inlineStr">
@@ -4981,7 +4977,7 @@
       </c>
       <c r="B161" s="1" t="inlineStr">
         <is>
-          <t>Quality Sprints</t>
+          <t>Hill Sprints</t>
         </is>
       </c>
       <c r="C161" s="1" t="inlineStr">
@@ -5013,7 +5009,7 @@
       </c>
       <c r="B162" s="1" t="inlineStr">
         <is>
-          <t>MAS Training</t>
+          <t>Quality Sprints</t>
         </is>
       </c>
       <c r="C162" s="1" t="inlineStr">
@@ -5045,7 +5041,7 @@
       </c>
       <c r="B163" s="1" t="inlineStr">
         <is>
-          <t>Flying Sprints</t>
+          <t>MAS Training</t>
         </is>
       </c>
       <c r="C163" s="1" t="inlineStr">
@@ -5065,7 +5061,7 @@
       </c>
       <c r="F163" s="1" t="inlineStr">
         <is>
-          <t>⚑ field sprint at top-end speed. Gate here is conditioning base, not lifting experience, so this ladder may not be the right instrument at all.</t>
+          <t>⚑ field sprint at top-end speed; hamstring/calf tagged 'avoid'. Gate here is conditioning base, not lifting experience, so this ladder may not be the right instrument at all.</t>
         </is>
       </c>
     </row>
@@ -5077,7 +5073,7 @@
       </c>
       <c r="B164" s="1" t="inlineStr">
         <is>
-          <t>MAS 15:15 Blocks</t>
+          <t>Flying Sprints</t>
         </is>
       </c>
       <c r="C164" s="1" t="inlineStr">
@@ -5109,7 +5105,7 @@
       </c>
       <c r="B165" s="1" t="inlineStr">
         <is>
-          <t>Tabata Intervals</t>
+          <t>MAS 15:15 Blocks</t>
         </is>
       </c>
       <c r="C165" s="1" t="inlineStr">
@@ -5124,12 +5120,12 @@
       </c>
       <c r="E165" s="1" t="inlineStr">
         <is>
-          <t>everyone</t>
+          <t>1+ years</t>
         </is>
       </c>
       <c r="F165" s="1" t="inlineStr">
         <is>
-          <t>session format, not an individual movement — no meaningful muscle group.</t>
+          <t>⚑ field sprint at top-end speed. Gate here is conditioning base, not lifting experience, so this ladder may not be the right instrument at all.</t>
         </is>
       </c>
     </row>
@@ -5141,7 +5137,7 @@
       </c>
       <c r="B166" s="1" t="inlineStr">
         <is>
-          <t>Inverse Tabata</t>
+          <t>Tabata Intervals</t>
         </is>
       </c>
       <c r="C166" s="1" t="inlineStr">
@@ -5173,7 +5169,7 @@
       </c>
       <c r="B167" s="1" t="inlineStr">
         <is>
-          <t>Max Effort Sprint Accumulation</t>
+          <t>Inverse Tabata</t>
         </is>
       </c>
       <c r="C167" s="1" t="inlineStr">
@@ -5205,7 +5201,7 @@
       </c>
       <c r="B168" s="1" t="inlineStr">
         <is>
-          <t>Free Sprint Session</t>
+          <t>Max Effort Sprint Accumulation</t>
         </is>
       </c>
       <c r="C168" s="1" t="inlineStr">
@@ -5220,12 +5216,12 @@
       </c>
       <c r="E168" s="1" t="inlineStr">
         <is>
-          <t>1+ years</t>
+          <t>everyone</t>
         </is>
       </c>
       <c r="F168" s="1" t="inlineStr">
         <is>
-          <t>⚑ field sprint at top-end speed; hamstring/calf tagged 'avoid'. Gate here is conditioning base, not lifting experience, so this ladder may not be the right instrument at all.</t>
+          <t>session format, not an individual movement — no meaningful muscle group.</t>
         </is>
       </c>
     </row>
@@ -5237,7 +5233,7 @@
       </c>
       <c r="B169" s="1" t="inlineStr">
         <is>
-          <t>Long Run</t>
+          <t>Free Sprint Session</t>
         </is>
       </c>
       <c r="C169" s="1" t="inlineStr">
@@ -5252,12 +5248,12 @@
       </c>
       <c r="E169" s="1" t="inlineStr">
         <is>
-          <t>everyone</t>
+          <t>1+ years</t>
         </is>
       </c>
       <c r="F169" s="1" t="inlineStr">
         <is>
-          <t>session format, not an individual movement — no meaningful muscle group.</t>
+          <t>⚑ field sprint at top-end speed; hamstring/calf tagged 'avoid'. Gate here is conditioning base, not lifting experience, so this ladder may not be the right instrument at all.</t>
         </is>
       </c>
     </row>
@@ -5269,7 +5265,7 @@
       </c>
       <c r="B170" s="1" t="inlineStr">
         <is>
-          <t>6x1km</t>
+          <t>Long Run</t>
         </is>
       </c>
       <c r="C170" s="1" t="inlineStr">
@@ -5301,7 +5297,7 @@
       </c>
       <c r="B171" s="1" t="inlineStr">
         <is>
-          <t>1km Repeat Intervals</t>
+          <t>6x1km</t>
         </is>
       </c>
       <c r="C171" s="1" t="inlineStr">
@@ -5333,7 +5329,7 @@
       </c>
       <c r="B172" s="1" t="inlineStr">
         <is>
-          <t>4x4 VO2</t>
+          <t>1km Repeat Intervals</t>
         </is>
       </c>
       <c r="C172" s="1" t="inlineStr">
@@ -5365,7 +5361,7 @@
       </c>
       <c r="B173" s="1" t="inlineStr">
         <is>
-          <t>200m/400m Repeat Runs</t>
+          <t>4x4 VO2</t>
         </is>
       </c>
       <c r="C173" s="1" t="inlineStr">
@@ -5380,12 +5376,12 @@
       </c>
       <c r="E173" s="1" t="inlineStr">
         <is>
-          <t>1+ years</t>
+          <t>everyone</t>
         </is>
       </c>
       <c r="F173" s="1" t="inlineStr">
         <is>
-          <t>⚑ sprint-adjacent speed endurance at high impact — the training-age ladder is a rough fit for a session format.</t>
+          <t>session format, not an individual movement — no meaningful muscle group.</t>
         </is>
       </c>
     </row>
@@ -5397,7 +5393,7 @@
       </c>
       <c r="B174" s="1" t="inlineStr">
         <is>
-          <t>Footy Fartlek</t>
+          <t>200m/400m Repeat Runs</t>
         </is>
       </c>
       <c r="C174" s="1" t="inlineStr">
@@ -5412,12 +5408,12 @@
       </c>
       <c r="E174" s="1" t="inlineStr">
         <is>
-          <t>everyone</t>
+          <t>1+ years</t>
         </is>
       </c>
       <c r="F174" s="1" t="inlineStr">
         <is>
-          <t>session format, not an individual movement — no meaningful muscle group.</t>
+          <t>⚑ sprint-adjacent speed endurance at high impact — the training-age ladder is a rough fit for a session format.</t>
         </is>
       </c>
     </row>
@@ -5429,7 +5425,7 @@
       </c>
       <c r="B175" s="1" t="inlineStr">
         <is>
-          <t>Hard Row Intervals</t>
+          <t>Footy Fartlek</t>
         </is>
       </c>
       <c r="C175" s="1" t="inlineStr">
@@ -5461,7 +5457,7 @@
       </c>
       <c r="B176" s="1" t="inlineStr">
         <is>
-          <t>Hard SkiErg Intervals</t>
+          <t>Hard Row Intervals</t>
         </is>
       </c>
       <c r="C176" s="1" t="inlineStr">
@@ -5493,7 +5489,7 @@
       </c>
       <c r="B177" s="1" t="inlineStr">
         <is>
-          <t>Hard Assault Bike Intervals</t>
+          <t>Hard SkiErg Intervals</t>
         </is>
       </c>
       <c r="C177" s="1" t="inlineStr">
@@ -5525,7 +5521,7 @@
       </c>
       <c r="B178" s="1" t="inlineStr">
         <is>
-          <t>Erg EMOM</t>
+          <t>Hard Assault Bike Intervals</t>
         </is>
       </c>
       <c r="C178" s="1" t="inlineStr">
@@ -5557,7 +5553,7 @@
       </c>
       <c r="B179" s="1" t="inlineStr">
         <is>
-          <t>Tempo Run</t>
+          <t>Erg EMOM</t>
         </is>
       </c>
       <c r="C179" s="1" t="inlineStr">
@@ -5589,7 +5585,7 @@
       </c>
       <c r="B180" s="1" t="inlineStr">
         <is>
-          <t>Long Nasal Run</t>
+          <t>Tempo Run</t>
         </is>
       </c>
       <c r="C180" s="1" t="inlineStr">
@@ -5621,7 +5617,7 @@
       </c>
       <c r="B181" s="1" t="inlineStr">
         <is>
-          <t>30:30 Tempo Blocks</t>
+          <t>Long Nasal Run</t>
         </is>
       </c>
       <c r="C181" s="1" t="inlineStr">
@@ -5653,7 +5649,7 @@
       </c>
       <c r="B182" s="1" t="inlineStr">
         <is>
-          <t>Tempo Intervals (1min on / 1min easy)</t>
+          <t>30:30 Tempo Blocks</t>
         </is>
       </c>
       <c r="C182" s="1" t="inlineStr">
@@ -5685,7 +5681,7 @@
       </c>
       <c r="B183" s="1" t="inlineStr">
         <is>
-          <t>Cruise Intervals</t>
+          <t>Tempo Intervals (1min on / 1min easy)</t>
         </is>
       </c>
       <c r="C183" s="1" t="inlineStr">
@@ -5717,7 +5713,7 @@
       </c>
       <c r="B184" s="1" t="inlineStr">
         <is>
-          <t>Bike/Row/Ski Tempo Intervals</t>
+          <t>Cruise Intervals</t>
         </is>
       </c>
       <c r="C184" s="1" t="inlineStr">
@@ -5749,7 +5745,7 @@
       </c>
       <c r="B185" s="1" t="inlineStr">
         <is>
-          <t>Air Bike Sprints</t>
+          <t>Bike/Row/Ski Tempo Intervals</t>
         </is>
       </c>
       <c r="C185" s="1" t="inlineStr">
@@ -5781,7 +5777,7 @@
       </c>
       <c r="B186" s="1" t="inlineStr">
         <is>
-          <t>Row Intervals</t>
+          <t>Air Bike Sprints</t>
         </is>
       </c>
       <c r="C186" s="1" t="inlineStr">
@@ -5813,7 +5809,7 @@
       </c>
       <c r="B187" s="1" t="inlineStr">
         <is>
-          <t>SkiErg Intervals</t>
+          <t>Row Intervals</t>
         </is>
       </c>
       <c r="C187" s="1" t="inlineStr">
@@ -5845,7 +5841,7 @@
       </c>
       <c r="B188" s="1" t="inlineStr">
         <is>
-          <t>Assault Bike Intervals</t>
+          <t>SkiErg Intervals</t>
         </is>
       </c>
       <c r="C188" s="1" t="inlineStr">
@@ -5877,7 +5873,7 @@
       </c>
       <c r="B189" s="1" t="inlineStr">
         <is>
-          <t>Flush Run</t>
+          <t>Assault Bike Intervals</t>
         </is>
       </c>
       <c r="C189" s="1" t="inlineStr">
@@ -5909,7 +5905,7 @@
       </c>
       <c r="B190" s="1" t="inlineStr">
         <is>
-          <t>Easy Bike</t>
+          <t>Flush Run</t>
         </is>
       </c>
       <c r="C190" s="1" t="inlineStr">
@@ -5941,7 +5937,7 @@
       </c>
       <c r="B191" s="1" t="inlineStr">
         <is>
-          <t>Easy Row</t>
+          <t>Easy Bike</t>
         </is>
       </c>
       <c r="C191" s="1" t="inlineStr">
@@ -5973,7 +5969,7 @@
       </c>
       <c r="B192" s="1" t="inlineStr">
         <is>
-          <t>Easy Ski</t>
+          <t>Easy Row</t>
         </is>
       </c>
       <c r="C192" s="1" t="inlineStr">
@@ -6005,7 +6001,7 @@
       </c>
       <c r="B193" s="1" t="inlineStr">
         <is>
-          <t>Easy Swim</t>
+          <t>Easy Ski</t>
         </is>
       </c>
       <c r="C193" s="1" t="inlineStr">
@@ -6037,59 +6033,63 @@
       </c>
       <c r="B194" s="1" t="inlineStr">
         <is>
+          <t>Easy Swim</t>
+        </is>
+      </c>
+      <c r="C194" s="1" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D194" s="1" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E194" s="1" t="inlineStr">
+        <is>
+          <t>everyone</t>
+        </is>
+      </c>
+      <c r="F194" s="1" t="inlineStr">
+        <is>
+          <t>session format, not an individual movement — no meaningful muscle group.</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="1" t="inlineStr">
+        <is>
+          <t>Conditioning</t>
+        </is>
+      </c>
+      <c r="B195" s="1" t="inlineStr">
+        <is>
           <t>Light Circuits</t>
         </is>
       </c>
-      <c r="C194" s="1" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D194" s="1" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E194" s="1" t="inlineStr">
-        <is>
-          <t>everyone</t>
-        </is>
-      </c>
-      <c r="F194" s="1" t="inlineStr">
+      <c r="C195" s="1" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D195" s="1" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E195" s="1" t="inlineStr">
+        <is>
+          <t>everyone</t>
+        </is>
+      </c>
+      <c r="F195" s="1" t="inlineStr">
         <is>
           <t>session format, not an individual movement — no meaningful muscle group.</t>
         </is>
       </c>
     </row>
-    <row r="195"/>
-    <row r="196">
-      <c r="A196" s="1" t="inlineStr">
-        <is>
-          <t>Power</t>
-        </is>
-      </c>
-      <c r="B196" s="1" t="inlineStr">
-        <is>
-          <t>Vertical Jump</t>
-        </is>
-      </c>
-      <c r="C196" s="1" t="inlineStr">
-        <is>
-          <t>Glutes, Quads, Calves</t>
-        </is>
-      </c>
-      <c r="D196" s="1" t="inlineStr">
-        <is>
-          <t>Hamstrings, Midline</t>
-        </is>
-      </c>
-      <c r="E196" s="1" t="inlineStr">
-        <is>
-          <t>everyone</t>
-        </is>
-      </c>
-      <c r="F196" s="1" t="inlineStr"/>
-    </row>
+    <row r="196"/>
     <row r="197">
       <c r="A197" s="1" t="inlineStr">
         <is>
@@ -6098,17 +6098,17 @@
       </c>
       <c r="B197" s="1" t="inlineStr">
         <is>
-          <t>Pogo Hops</t>
+          <t>Vertical Jump</t>
         </is>
       </c>
       <c r="C197" s="1" t="inlineStr">
         <is>
-          <t>Calves</t>
+          <t>Glutes, Quads, Calves</t>
         </is>
       </c>
       <c r="D197" s="1" t="inlineStr">
         <is>
-          <t>Quads, Midline</t>
+          <t>Hamstrings, Midline</t>
         </is>
       </c>
       <c r="E197" s="1" t="inlineStr">
@@ -6116,11 +6116,7 @@
           <t>everyone</t>
         </is>
       </c>
-      <c r="F197" s="1" t="inlineStr">
-        <is>
-          <t>takes over when lower niggle (your spec)</t>
-        </is>
-      </c>
+      <c r="F197" s="1" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" s="1" t="inlineStr">
@@ -6130,17 +6126,17 @@
       </c>
       <c r="B198" s="1" t="inlineStr">
         <is>
-          <t>Lateral Jump</t>
+          <t>Pogo Hops</t>
         </is>
       </c>
       <c r="C198" s="1" t="inlineStr">
         <is>
-          <t>Glutes, Outer hip</t>
+          <t>Calves</t>
         </is>
       </c>
       <c r="D198" s="1" t="inlineStr">
         <is>
-          <t>Quads, Calves, Midline</t>
+          <t>Quads, Midline</t>
         </is>
       </c>
       <c r="E198" s="1" t="inlineStr">
@@ -6150,7 +6146,7 @@
       </c>
       <c r="F198" s="1" t="inlineStr">
         <is>
-          <t>your spec: beginner friendly</t>
+          <t>takes over when lower niggle (your spec)</t>
         </is>
       </c>
     </row>
@@ -6162,27 +6158,27 @@
       </c>
       <c r="B199" s="1" t="inlineStr">
         <is>
-          <t>Kneeling Jump</t>
+          <t>Lateral Jump</t>
         </is>
       </c>
       <c r="C199" s="1" t="inlineStr">
         <is>
-          <t>Glutes, Quads</t>
+          <t>Glutes, Outer hip</t>
         </is>
       </c>
       <c r="D199" s="1" t="inlineStr">
         <is>
-          <t>Hamstrings, Midline</t>
+          <t>Quads, Calves, Midline</t>
         </is>
       </c>
       <c r="E199" s="1" t="inlineStr">
         <is>
-          <t>2+ years</t>
+          <t>everyone</t>
         </is>
       </c>
       <c r="F199" s="1" t="inlineStr">
         <is>
-          <t>your spec: consistent+</t>
+          <t>your spec: beginner friendly</t>
         </is>
       </c>
     </row>
@@ -6194,17 +6190,17 @@
       </c>
       <c r="B200" s="1" t="inlineStr">
         <is>
-          <t>RFE Split Squat Jump</t>
+          <t>Kneeling Jump</t>
         </is>
       </c>
       <c r="C200" s="1" t="inlineStr">
         <is>
-          <t>Quads, Glutes</t>
+          <t>Glutes, Quads</t>
         </is>
       </c>
       <c r="D200" s="1" t="inlineStr">
         <is>
-          <t>Hamstrings, Calves, Midline</t>
+          <t>Hamstrings, Midline</t>
         </is>
       </c>
       <c r="E200" s="1" t="inlineStr">
@@ -6212,9 +6208,9 @@
           <t>2+ years</t>
         </is>
       </c>
-      <c r="F200" s="3" t="inlineStr">
-        <is>
-          <t>FLAG — gate proposed, confirm</t>
+      <c r="F200" s="1" t="inlineStr">
+        <is>
+          <t>your spec: consistent+</t>
         </is>
       </c>
     </row>
@@ -6226,25 +6222,29 @@
       </c>
       <c r="B201" s="1" t="inlineStr">
         <is>
-          <t>Explosive Push-up</t>
+          <t>RFE Split Squat Jump</t>
         </is>
       </c>
       <c r="C201" s="1" t="inlineStr">
         <is>
-          <t>Chest, Triceps</t>
+          <t>Quads, Glutes</t>
         </is>
       </c>
       <c r="D201" s="1" t="inlineStr">
         <is>
-          <t>Shoulders, Midline</t>
+          <t>Hamstrings, Calves, Midline</t>
         </is>
       </c>
       <c r="E201" s="1" t="inlineStr">
         <is>
-          <t>everyone</t>
-        </is>
-      </c>
-      <c r="F201" s="1" t="inlineStr"/>
+          <t>2+ years</t>
+        </is>
+      </c>
+      <c r="F201" s="3" t="inlineStr">
+        <is>
+          <t>FLAG — gate proposed, confirm</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="1" t="inlineStr">
@@ -6254,7 +6254,7 @@
       </c>
       <c r="B202" s="1" t="inlineStr">
         <is>
-          <t>Speed Bench</t>
+          <t>Explosive Push-up</t>
         </is>
       </c>
       <c r="C202" s="1" t="inlineStr">
@@ -6264,19 +6264,15 @@
       </c>
       <c r="D202" s="1" t="inlineStr">
         <is>
-          <t>Shoulders, Lats</t>
+          <t>Shoulders, Midline</t>
         </is>
       </c>
       <c r="E202" s="1" t="inlineStr">
         <is>
-          <t>2+ years</t>
-        </is>
-      </c>
-      <c r="F202" s="3" t="inlineStr">
-        <is>
-          <t>FLAG — gate proposed, confirm</t>
-        </is>
-      </c>
+          <t>everyone</t>
+        </is>
+      </c>
+      <c r="F202" s="1" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" s="1" t="inlineStr">
@@ -6286,25 +6282,57 @@
       </c>
       <c r="B203" s="1" t="inlineStr">
         <is>
+          <t>Speed Bench</t>
+        </is>
+      </c>
+      <c r="C203" s="1" t="inlineStr">
+        <is>
+          <t>Chest, Triceps</t>
+        </is>
+      </c>
+      <c r="D203" s="1" t="inlineStr">
+        <is>
+          <t>Shoulders, Lats</t>
+        </is>
+      </c>
+      <c r="E203" s="1" t="inlineStr">
+        <is>
+          <t>2+ years</t>
+        </is>
+      </c>
+      <c r="F203" s="3" t="inlineStr">
+        <is>
+          <t>FLAG — gate proposed, confirm</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="1" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="B204" s="1" t="inlineStr">
+        <is>
           <t>Speed Trap Bar Deadlift</t>
         </is>
       </c>
-      <c r="C203" s="1" t="inlineStr">
+      <c r="C204" s="1" t="inlineStr">
         <is>
           <t>Glutes, Hamstrings</t>
         </is>
       </c>
-      <c r="D203" s="1" t="inlineStr">
+      <c r="D204" s="1" t="inlineStr">
         <is>
           <t>Quads, Upper back, Grip</t>
         </is>
       </c>
-      <c r="E203" s="1" t="inlineStr">
+      <c r="E204" s="1" t="inlineStr">
         <is>
           <t>2+ years</t>
         </is>
       </c>
-      <c r="F203" s="3" t="inlineStr">
+      <c r="F204" s="3" t="inlineStr">
         <is>
           <t>FLAG — gate proposed, confirm</t>
         </is>

--- a/docs/MUSCLE_EXPERIENCE_FINAL_2026-07-25.xlsx
+++ b/docs/MUSCLE_EXPERIENCE_FINAL_2026-07-25.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F204"/>
+  <dimension ref="A1:F205"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3948,22 +3948,22 @@
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>Hamstring (light)</t>
+          <t>Shoulder health</t>
         </is>
       </c>
       <c r="B125" s="1" t="inlineStr">
         <is>
-          <t>Swiss Ball Hamstring Curl</t>
+          <t>Scap Pull Ups</t>
         </is>
       </c>
       <c r="C125" s="1" t="inlineStr">
         <is>
-          <t>Hamstrings</t>
+          <t>Shoulders, Upper back, Lats</t>
         </is>
       </c>
       <c r="D125" s="1" t="inlineStr">
         <is>
-          <t>Midline</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E125" s="1" t="inlineStr">
@@ -3976,22 +3976,22 @@
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>Tissue quality</t>
+          <t>Hamstring (light)</t>
         </is>
       </c>
       <c r="B126" s="1" t="inlineStr">
         <is>
-          <t>Foam Roll — Hip Flexor, Quad, Adductors</t>
+          <t>Swiss Ball Hamstring Curl</t>
         </is>
       </c>
       <c r="C126" s="1" t="inlineStr">
         <is>
-          <t>Quads, Groin</t>
+          <t>Hamstrings</t>
         </is>
       </c>
       <c r="D126" s="1" t="inlineStr">
         <is>
-          <t>Hips</t>
+          <t>Midline</t>
         </is>
       </c>
       <c r="E126" s="1" t="inlineStr">
@@ -4009,17 +4009,17 @@
       </c>
       <c r="B127" s="1" t="inlineStr">
         <is>
-          <t>Foam Roll — T-Spine</t>
+          <t>Foam Roll — Hip Flexor, Quad, Adductors</t>
         </is>
       </c>
       <c r="C127" s="1" t="inlineStr">
         <is>
-          <t>Upper back</t>
+          <t>Quads, Groin</t>
         </is>
       </c>
       <c r="D127" s="1" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Hips</t>
         </is>
       </c>
       <c r="E127" s="1" t="inlineStr">
@@ -4037,17 +4037,17 @@
       </c>
       <c r="B128" s="1" t="inlineStr">
         <is>
-          <t>Foam Roll — IT Band</t>
+          <t>Foam Roll — T-Spine</t>
         </is>
       </c>
       <c r="C128" s="1" t="inlineStr">
         <is>
-          <t>Quads</t>
+          <t>Upper back</t>
         </is>
       </c>
       <c r="D128" s="1" t="inlineStr">
         <is>
-          <t>Hips</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E128" s="1" t="inlineStr">
@@ -4065,17 +4065,17 @@
       </c>
       <c r="B129" s="1" t="inlineStr">
         <is>
-          <t>Foam Roll — Lats</t>
+          <t>Foam Roll — IT Band</t>
         </is>
       </c>
       <c r="C129" s="1" t="inlineStr">
         <is>
-          <t>Lats</t>
+          <t>Quads</t>
         </is>
       </c>
       <c r="D129" s="1" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Hips</t>
         </is>
       </c>
       <c r="E129" s="1" t="inlineStr">
@@ -4093,12 +4093,12 @@
       </c>
       <c r="B130" s="1" t="inlineStr">
         <is>
-          <t>Foam Roll — Calves &amp; Outer Shins</t>
+          <t>Foam Roll — Lats</t>
         </is>
       </c>
       <c r="C130" s="1" t="inlineStr">
         <is>
-          <t>Calves</t>
+          <t>Lats</t>
         </is>
       </c>
       <c r="D130" s="1" t="inlineStr">
@@ -4121,17 +4121,17 @@
       </c>
       <c r="B131" s="1" t="inlineStr">
         <is>
-          <t>Lacrosse Ball Glute Release</t>
+          <t>Foam Roll — Calves &amp; Outer Shins</t>
         </is>
       </c>
       <c r="C131" s="1" t="inlineStr">
         <is>
-          <t>Glutes</t>
+          <t>Calves</t>
         </is>
       </c>
       <c r="D131" s="1" t="inlineStr">
         <is>
-          <t>Hips</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E131" s="1" t="inlineStr">
@@ -4144,22 +4144,22 @@
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>Mobility</t>
+          <t>Tissue quality</t>
         </is>
       </c>
       <c r="B132" s="1" t="inlineStr">
         <is>
-          <t>Hip 90/90 Stretch</t>
+          <t>Lacrosse Ball Glute Release</t>
         </is>
       </c>
       <c r="C132" s="1" t="inlineStr">
         <is>
+          <t>Glutes</t>
+        </is>
+      </c>
+      <c r="D132" s="1" t="inlineStr">
+        <is>
           <t>Hips</t>
-        </is>
-      </c>
-      <c r="D132" s="1" t="inlineStr">
-        <is>
-          <t>Groin</t>
         </is>
       </c>
       <c r="E132" s="1" t="inlineStr">
@@ -4177,17 +4177,17 @@
       </c>
       <c r="B133" s="1" t="inlineStr">
         <is>
-          <t>Cat-Cow</t>
+          <t>Hip 90/90 Stretch</t>
         </is>
       </c>
       <c r="C133" s="1" t="inlineStr">
         <is>
-          <t>Midline</t>
+          <t>Hips</t>
         </is>
       </c>
       <c r="D133" s="1" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Groin</t>
         </is>
       </c>
       <c r="E133" s="1" t="inlineStr">
@@ -4205,17 +4205,17 @@
       </c>
       <c r="B134" s="1" t="inlineStr">
         <is>
-          <t>World's Greatest Stretch</t>
+          <t>Cat-Cow</t>
         </is>
       </c>
       <c r="C134" s="1" t="inlineStr">
         <is>
-          <t>Hips, Groin</t>
+          <t>Midline</t>
         </is>
       </c>
       <c r="D134" s="1" t="inlineStr">
         <is>
-          <t>Midline</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E134" s="1" t="inlineStr">
@@ -4233,7 +4233,7 @@
       </c>
       <c r="B135" s="1" t="inlineStr">
         <is>
-          <t>Deep Squat Hold</t>
+          <t>World's Greatest Stretch</t>
         </is>
       </c>
       <c r="C135" s="1" t="inlineStr">
@@ -4243,7 +4243,7 @@
       </c>
       <c r="D135" s="1" t="inlineStr">
         <is>
-          <t>Calves</t>
+          <t>Midline</t>
         </is>
       </c>
       <c r="E135" s="1" t="inlineStr">
@@ -4261,17 +4261,17 @@
       </c>
       <c r="B136" s="1" t="inlineStr">
         <is>
-          <t>Couch Stretch</t>
+          <t>Deep Squat Hold</t>
         </is>
       </c>
       <c r="C136" s="1" t="inlineStr">
         <is>
-          <t>Quads, Hips</t>
+          <t>Hips, Groin</t>
         </is>
       </c>
       <c r="D136" s="1" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Calves</t>
         </is>
       </c>
       <c r="E136" s="1" t="inlineStr">
@@ -4289,17 +4289,17 @@
       </c>
       <c r="B137" s="1" t="inlineStr">
         <is>
-          <t>Open Book Thoracic Rotation</t>
+          <t>Couch Stretch</t>
         </is>
       </c>
       <c r="C137" s="1" t="inlineStr">
         <is>
-          <t>Upper back</t>
+          <t>Quads, Hips</t>
         </is>
       </c>
       <c r="D137" s="1" t="inlineStr">
         <is>
-          <t>Midline</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E137" s="1" t="inlineStr">
@@ -4317,17 +4317,17 @@
       </c>
       <c r="B138" s="1" t="inlineStr">
         <is>
-          <t>Pigeon Stretch</t>
+          <t>Open Book Thoracic Rotation</t>
         </is>
       </c>
       <c r="C138" s="1" t="inlineStr">
         <is>
-          <t>Hips, Glutes</t>
+          <t>Upper back</t>
         </is>
       </c>
       <c r="D138" s="1" t="inlineStr">
         <is>
-          <t>Groin</t>
+          <t>Midline</t>
         </is>
       </c>
       <c r="E138" s="1" t="inlineStr">
@@ -4345,17 +4345,17 @@
       </c>
       <c r="B139" s="1" t="inlineStr">
         <is>
-          <t>Adductor Rockback</t>
+          <t>Pigeon Stretch</t>
         </is>
       </c>
       <c r="C139" s="1" t="inlineStr">
         <is>
+          <t>Hips, Glutes</t>
+        </is>
+      </c>
+      <c r="D139" s="1" t="inlineStr">
+        <is>
           <t>Groin</t>
-        </is>
-      </c>
-      <c r="D139" s="1" t="inlineStr">
-        <is>
-          <t>Hips</t>
         </is>
       </c>
       <c r="E139" s="1" t="inlineStr">
@@ -4373,17 +4373,17 @@
       </c>
       <c r="B140" s="1" t="inlineStr">
         <is>
-          <t>Chest / Pec Stretch (Doorway)</t>
+          <t>Adductor Rockback</t>
         </is>
       </c>
       <c r="C140" s="1" t="inlineStr">
         <is>
-          <t>Chest</t>
+          <t>Groin</t>
         </is>
       </c>
       <c r="D140" s="1" t="inlineStr">
         <is>
-          <t>Shoulders</t>
+          <t>Hips</t>
         </is>
       </c>
       <c r="E140" s="1" t="inlineStr">
@@ -4401,12 +4401,12 @@
       </c>
       <c r="B141" s="1" t="inlineStr">
         <is>
-          <t>Lat Stretch</t>
+          <t>Chest / Pec Stretch (Doorway)</t>
         </is>
       </c>
       <c r="C141" s="1" t="inlineStr">
         <is>
-          <t>Lats</t>
+          <t>Chest</t>
         </is>
       </c>
       <c r="D141" s="1" t="inlineStr">
@@ -4429,17 +4429,17 @@
       </c>
       <c r="B142" s="1" t="inlineStr">
         <is>
-          <t>Dead Hang</t>
+          <t>Lat Stretch</t>
         </is>
       </c>
       <c r="C142" s="1" t="inlineStr">
         <is>
-          <t>Lats, Shoulders</t>
+          <t>Lats</t>
         </is>
       </c>
       <c r="D142" s="1" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Shoulders</t>
         </is>
       </c>
       <c r="E142" s="1" t="inlineStr">
@@ -4457,12 +4457,12 @@
       </c>
       <c r="B143" s="1" t="inlineStr">
         <is>
-          <t>Toe Stretch</t>
+          <t>Dead Hang</t>
         </is>
       </c>
       <c r="C143" s="1" t="inlineStr">
         <is>
-          <t>Calves, Feet</t>
+          <t>Lats, Shoulders</t>
         </is>
       </c>
       <c r="D143" s="1" t="inlineStr">
@@ -4475,11 +4475,7 @@
           <t>everyone</t>
         </is>
       </c>
-      <c r="F143" s="1" t="inlineStr">
-        <is>
-          <t>targets the foot/ankle specifically; 'Calves' is the closest plain-language bucket.</t>
-        </is>
-      </c>
+      <c r="F143" s="1" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
@@ -4489,12 +4485,12 @@
       </c>
       <c r="B144" s="1" t="inlineStr">
         <is>
-          <t>Calf Stretch</t>
+          <t>Toe Stretch</t>
         </is>
       </c>
       <c r="C144" s="1" t="inlineStr">
         <is>
-          <t>Calves</t>
+          <t>Calves, Feet</t>
         </is>
       </c>
       <c r="D144" s="1" t="inlineStr">
@@ -4507,7 +4503,11 @@
           <t>everyone</t>
         </is>
       </c>
-      <c r="F144" s="1" t="inlineStr"/>
+      <c r="F144" s="1" t="inlineStr">
+        <is>
+          <t>targets the foot/ankle specifically; 'Calves' is the closest plain-language bucket.</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
@@ -4517,12 +4517,12 @@
       </c>
       <c r="B145" s="1" t="inlineStr">
         <is>
-          <t>QL Back Extension</t>
+          <t>Calf Stretch</t>
         </is>
       </c>
       <c r="C145" s="1" t="inlineStr">
         <is>
-          <t>Midline</t>
+          <t>Calves</t>
         </is>
       </c>
       <c r="D145" s="1" t="inlineStr">
@@ -4535,11 +4535,7 @@
           <t>everyone</t>
         </is>
       </c>
-      <c r="F145" s="1" t="inlineStr">
-        <is>
-          <t>targets the quadratus lumborum (side of lower back) specifically; 'Midline' is the closest plain-language bucket.</t>
-        </is>
-      </c>
+      <c r="F145" s="1" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
@@ -4549,17 +4545,17 @@
       </c>
       <c r="B146" s="1" t="inlineStr">
         <is>
-          <t>ATG Split Squat</t>
+          <t>QL Back Extension</t>
         </is>
       </c>
       <c r="C146" s="1" t="inlineStr">
         <is>
-          <t>Quads, Hips</t>
+          <t>Midline</t>
         </is>
       </c>
       <c r="D146" s="1" t="inlineStr">
         <is>
-          <t>Groin, Calves</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E146" s="1" t="inlineStr">
@@ -4569,7 +4565,7 @@
       </c>
       <c r="F146" s="1" t="inlineStr">
         <is>
-          <t>⚑ deep ankle/hip mobility demand — some athletes may need to regress the range; could be 1+ years.</t>
+          <t>targets the quadratus lumborum (side of lower back) specifically; 'Midline' is the closest plain-language bucket.</t>
         </is>
       </c>
     </row>
@@ -4581,17 +4577,17 @@
       </c>
       <c r="B147" s="1" t="inlineStr">
         <is>
-          <t>Elephant Walks</t>
+          <t>ATG Split Squat</t>
         </is>
       </c>
       <c r="C147" s="1" t="inlineStr">
         <is>
-          <t>Hamstrings</t>
+          <t>Quads, Hips</t>
         </is>
       </c>
       <c r="D147" s="1" t="inlineStr">
         <is>
-          <t>Calves</t>
+          <t>Groin, Calves</t>
         </is>
       </c>
       <c r="E147" s="1" t="inlineStr">
@@ -4599,7 +4595,11 @@
           <t>everyone</t>
         </is>
       </c>
-      <c r="F147" s="1" t="inlineStr"/>
+      <c r="F147" s="1" t="inlineStr">
+        <is>
+          <t>⚑ deep ankle/hip mobility demand — some athletes may need to regress the range; could be 1+ years.</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
@@ -4609,17 +4609,17 @@
       </c>
       <c r="B148" s="1" t="inlineStr">
         <is>
-          <t>Butterfly Stretch</t>
+          <t>Elephant Walks</t>
         </is>
       </c>
       <c r="C148" s="1" t="inlineStr">
         <is>
-          <t>Groin, Hips</t>
+          <t>Hamstrings</t>
         </is>
       </c>
       <c r="D148" s="1" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Calves</t>
         </is>
       </c>
       <c r="E148" s="1" t="inlineStr">
@@ -4637,12 +4637,12 @@
       </c>
       <c r="B149" s="1" t="inlineStr">
         <is>
-          <t>Pissing Dog Against Wall</t>
+          <t>Butterfly Stretch</t>
         </is>
       </c>
       <c r="C149" s="1" t="inlineStr">
         <is>
-          <t>Glutes, Hips</t>
+          <t>Groin, Hips</t>
         </is>
       </c>
       <c r="D149" s="1" t="inlineStr">
@@ -4665,12 +4665,12 @@
       </c>
       <c r="B150" s="1" t="inlineStr">
         <is>
-          <t>Jefferson Curl</t>
+          <t>Pissing Dog Against Wall</t>
         </is>
       </c>
       <c r="C150" s="1" t="inlineStr">
         <is>
-          <t>Upper back, Low back, Hamstrings</t>
+          <t>Glutes, Hips</t>
         </is>
       </c>
       <c r="D150" s="1" t="inlineStr">
@@ -4693,12 +4693,12 @@
       </c>
       <c r="B151" s="1" t="inlineStr">
         <is>
-          <t>Dumbbell Pullovers</t>
+          <t>Jefferson Curl</t>
         </is>
       </c>
       <c r="C151" s="1" t="inlineStr">
         <is>
-          <t>Upper back, Shoulders</t>
+          <t>Upper back, Low back, Hamstrings</t>
         </is>
       </c>
       <c r="D151" s="1" t="inlineStr">
@@ -4716,17 +4716,17 @@
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>Easy cardio (zone 1)</t>
+          <t>Mobility</t>
         </is>
       </c>
       <c r="B152" s="1" t="inlineStr">
         <is>
-          <t>Light Walk or Stationary Bike</t>
+          <t>Dumbbell Pullovers</t>
         </is>
       </c>
       <c r="C152" s="1" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Upper back, Shoulders</t>
         </is>
       </c>
       <c r="D152" s="1" t="inlineStr">
@@ -4749,7 +4749,7 @@
       </c>
       <c r="B153" s="1" t="inlineStr">
         <is>
-          <t>Incline Treadmill Walk</t>
+          <t>Light Walk or Stationary Bike</t>
         </is>
       </c>
       <c r="C153" s="1" t="inlineStr">
@@ -4777,7 +4777,7 @@
       </c>
       <c r="B154" s="1" t="inlineStr">
         <is>
-          <t>Outdoor Walk</t>
+          <t>Incline Treadmill Walk</t>
         </is>
       </c>
       <c r="C154" s="1" t="inlineStr">
@@ -4805,12 +4805,12 @@
       </c>
       <c r="B155" s="1" t="inlineStr">
         <is>
-          <t>Light Skipping</t>
+          <t>Outdoor Walk</t>
         </is>
       </c>
       <c r="C155" s="1" t="inlineStr">
         <is>
-          <t>Calves</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D155" s="1" t="inlineStr">
@@ -4828,17 +4828,17 @@
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>Breathing reset</t>
+          <t>Easy cardio (zone 1)</t>
         </is>
       </c>
       <c r="B156" s="1" t="inlineStr">
         <is>
-          <t>90/90 Breathing</t>
+          <t>Light Skipping</t>
         </is>
       </c>
       <c r="C156" s="1" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Calves</t>
         </is>
       </c>
       <c r="D156" s="1" t="inlineStr">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="B157" s="1" t="inlineStr">
         <is>
-          <t>Crocodile Breathing</t>
+          <t>90/90 Breathing</t>
         </is>
       </c>
       <c r="C157" s="1" t="inlineStr">
@@ -4889,7 +4889,7 @@
       </c>
       <c r="B158" s="1" t="inlineStr">
         <is>
-          <t>Box Breathing</t>
+          <t>Crocodile Breathing</t>
         </is>
       </c>
       <c r="C158" s="1" t="inlineStr">
@@ -4917,7 +4917,7 @@
       </c>
       <c r="B159" s="1" t="inlineStr">
         <is>
-          <t>Child's Pose with Breathing</t>
+          <t>Box Breathing</t>
         </is>
       </c>
       <c r="C159" s="1" t="inlineStr">
@@ -4940,12 +4940,12 @@
     <row r="160">
       <c r="A160" s="1" t="inlineStr">
         <is>
-          <t>Conditioning</t>
+          <t>Breathing reset</t>
         </is>
       </c>
       <c r="B160" s="1" t="inlineStr">
         <is>
-          <t>Sprint Intervals</t>
+          <t>Child's Pose with Breathing</t>
         </is>
       </c>
       <c r="C160" s="1" t="inlineStr">
@@ -4960,14 +4960,10 @@
       </c>
       <c r="E160" s="1" t="inlineStr">
         <is>
-          <t>1+ years</t>
-        </is>
-      </c>
-      <c r="F160" s="1" t="inlineStr">
-        <is>
-          <t>⚑ field sprint at top-end speed; hamstring/calf tagged 'avoid'. Gate here is conditioning base, not lifting experience, so this ladder may not be the right instrument at all.</t>
-        </is>
-      </c>
+          <t>everyone</t>
+        </is>
+      </c>
+      <c r="F160" s="1" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" s="1" t="inlineStr">
@@ -4977,7 +4973,7 @@
       </c>
       <c r="B161" s="1" t="inlineStr">
         <is>
-          <t>Hill Sprints</t>
+          <t>Sprint Intervals</t>
         </is>
       </c>
       <c r="C161" s="1" t="inlineStr">
@@ -5009,7 +5005,7 @@
       </c>
       <c r="B162" s="1" t="inlineStr">
         <is>
-          <t>Quality Sprints</t>
+          <t>Hill Sprints</t>
         </is>
       </c>
       <c r="C162" s="1" t="inlineStr">
@@ -5041,7 +5037,7 @@
       </c>
       <c r="B163" s="1" t="inlineStr">
         <is>
-          <t>MAS Training</t>
+          <t>Quality Sprints</t>
         </is>
       </c>
       <c r="C163" s="1" t="inlineStr">
@@ -5073,7 +5069,7 @@
       </c>
       <c r="B164" s="1" t="inlineStr">
         <is>
-          <t>Flying Sprints</t>
+          <t>MAS Training</t>
         </is>
       </c>
       <c r="C164" s="1" t="inlineStr">
@@ -5093,7 +5089,7 @@
       </c>
       <c r="F164" s="1" t="inlineStr">
         <is>
-          <t>⚑ field sprint at top-end speed. Gate here is conditioning base, not lifting experience, so this ladder may not be the right instrument at all.</t>
+          <t>⚑ field sprint at top-end speed; hamstring/calf tagged 'avoid'. Gate here is conditioning base, not lifting experience, so this ladder may not be the right instrument at all.</t>
         </is>
       </c>
     </row>
@@ -5105,7 +5101,7 @@
       </c>
       <c r="B165" s="1" t="inlineStr">
         <is>
-          <t>MAS 15:15 Blocks</t>
+          <t>Flying Sprints</t>
         </is>
       </c>
       <c r="C165" s="1" t="inlineStr">
@@ -5137,7 +5133,7 @@
       </c>
       <c r="B166" s="1" t="inlineStr">
         <is>
-          <t>Tabata Intervals</t>
+          <t>MAS 15:15 Blocks</t>
         </is>
       </c>
       <c r="C166" s="1" t="inlineStr">
@@ -5152,12 +5148,12 @@
       </c>
       <c r="E166" s="1" t="inlineStr">
         <is>
-          <t>everyone</t>
+          <t>1+ years</t>
         </is>
       </c>
       <c r="F166" s="1" t="inlineStr">
         <is>
-          <t>session format, not an individual movement — no meaningful muscle group.</t>
+          <t>⚑ field sprint at top-end speed. Gate here is conditioning base, not lifting experience, so this ladder may not be the right instrument at all.</t>
         </is>
       </c>
     </row>
@@ -5169,7 +5165,7 @@
       </c>
       <c r="B167" s="1" t="inlineStr">
         <is>
-          <t>Inverse Tabata</t>
+          <t>Tabata Intervals</t>
         </is>
       </c>
       <c r="C167" s="1" t="inlineStr">
@@ -5201,7 +5197,7 @@
       </c>
       <c r="B168" s="1" t="inlineStr">
         <is>
-          <t>Max Effort Sprint Accumulation</t>
+          <t>Inverse Tabata</t>
         </is>
       </c>
       <c r="C168" s="1" t="inlineStr">
@@ -5233,7 +5229,7 @@
       </c>
       <c r="B169" s="1" t="inlineStr">
         <is>
-          <t>Free Sprint Session</t>
+          <t>Max Effort Sprint Accumulation</t>
         </is>
       </c>
       <c r="C169" s="1" t="inlineStr">
@@ -5248,12 +5244,12 @@
       </c>
       <c r="E169" s="1" t="inlineStr">
         <is>
-          <t>1+ years</t>
+          <t>everyone</t>
         </is>
       </c>
       <c r="F169" s="1" t="inlineStr">
         <is>
-          <t>⚑ field sprint at top-end speed; hamstring/calf tagged 'avoid'. Gate here is conditioning base, not lifting experience, so this ladder may not be the right instrument at all.</t>
+          <t>session format, not an individual movement — no meaningful muscle group.</t>
         </is>
       </c>
     </row>
@@ -5265,7 +5261,7 @@
       </c>
       <c r="B170" s="1" t="inlineStr">
         <is>
-          <t>Long Run</t>
+          <t>Free Sprint Session</t>
         </is>
       </c>
       <c r="C170" s="1" t="inlineStr">
@@ -5280,12 +5276,12 @@
       </c>
       <c r="E170" s="1" t="inlineStr">
         <is>
-          <t>everyone</t>
+          <t>1+ years</t>
         </is>
       </c>
       <c r="F170" s="1" t="inlineStr">
         <is>
-          <t>session format, not an individual movement — no meaningful muscle group.</t>
+          <t>⚑ field sprint at top-end speed; hamstring/calf tagged 'avoid'. Gate here is conditioning base, not lifting experience, so this ladder may not be the right instrument at all.</t>
         </is>
       </c>
     </row>
@@ -5297,7 +5293,7 @@
       </c>
       <c r="B171" s="1" t="inlineStr">
         <is>
-          <t>6x1km</t>
+          <t>Long Run</t>
         </is>
       </c>
       <c r="C171" s="1" t="inlineStr">
@@ -5329,7 +5325,7 @@
       </c>
       <c r="B172" s="1" t="inlineStr">
         <is>
-          <t>1km Repeat Intervals</t>
+          <t>6x1km</t>
         </is>
       </c>
       <c r="C172" s="1" t="inlineStr">
@@ -5361,7 +5357,7 @@
       </c>
       <c r="B173" s="1" t="inlineStr">
         <is>
-          <t>4x4 VO2</t>
+          <t>1km Repeat Intervals</t>
         </is>
       </c>
       <c r="C173" s="1" t="inlineStr">
@@ -5393,7 +5389,7 @@
       </c>
       <c r="B174" s="1" t="inlineStr">
         <is>
-          <t>200m/400m Repeat Runs</t>
+          <t>4x4 VO2</t>
         </is>
       </c>
       <c r="C174" s="1" t="inlineStr">
@@ -5408,12 +5404,12 @@
       </c>
       <c r="E174" s="1" t="inlineStr">
         <is>
-          <t>1+ years</t>
+          <t>everyone</t>
         </is>
       </c>
       <c r="F174" s="1" t="inlineStr">
         <is>
-          <t>⚑ sprint-adjacent speed endurance at high impact — the training-age ladder is a rough fit for a session format.</t>
+          <t>session format, not an individual movement — no meaningful muscle group.</t>
         </is>
       </c>
     </row>
@@ -5425,7 +5421,7 @@
       </c>
       <c r="B175" s="1" t="inlineStr">
         <is>
-          <t>Footy Fartlek</t>
+          <t>200m/400m Repeat Runs</t>
         </is>
       </c>
       <c r="C175" s="1" t="inlineStr">
@@ -5440,12 +5436,12 @@
       </c>
       <c r="E175" s="1" t="inlineStr">
         <is>
-          <t>everyone</t>
+          <t>1+ years</t>
         </is>
       </c>
       <c r="F175" s="1" t="inlineStr">
         <is>
-          <t>session format, not an individual movement — no meaningful muscle group.</t>
+          <t>⚑ sprint-adjacent speed endurance at high impact — the training-age ladder is a rough fit for a session format.</t>
         </is>
       </c>
     </row>
@@ -5457,7 +5453,7 @@
       </c>
       <c r="B176" s="1" t="inlineStr">
         <is>
-          <t>Hard Row Intervals</t>
+          <t>Footy Fartlek</t>
         </is>
       </c>
       <c r="C176" s="1" t="inlineStr">
@@ -5489,7 +5485,7 @@
       </c>
       <c r="B177" s="1" t="inlineStr">
         <is>
-          <t>Hard SkiErg Intervals</t>
+          <t>Hard Row Intervals</t>
         </is>
       </c>
       <c r="C177" s="1" t="inlineStr">
@@ -5521,7 +5517,7 @@
       </c>
       <c r="B178" s="1" t="inlineStr">
         <is>
-          <t>Hard Assault Bike Intervals</t>
+          <t>Hard SkiErg Intervals</t>
         </is>
       </c>
       <c r="C178" s="1" t="inlineStr">
@@ -5553,7 +5549,7 @@
       </c>
       <c r="B179" s="1" t="inlineStr">
         <is>
-          <t>Erg EMOM</t>
+          <t>Hard Assault Bike Intervals</t>
         </is>
       </c>
       <c r="C179" s="1" t="inlineStr">
@@ -5585,7 +5581,7 @@
       </c>
       <c r="B180" s="1" t="inlineStr">
         <is>
-          <t>Tempo Run</t>
+          <t>Erg EMOM</t>
         </is>
       </c>
       <c r="C180" s="1" t="inlineStr">
@@ -5617,7 +5613,7 @@
       </c>
       <c r="B181" s="1" t="inlineStr">
         <is>
-          <t>Long Nasal Run</t>
+          <t>Tempo Run</t>
         </is>
       </c>
       <c r="C181" s="1" t="inlineStr">
@@ -5649,7 +5645,7 @@
       </c>
       <c r="B182" s="1" t="inlineStr">
         <is>
-          <t>30:30 Tempo Blocks</t>
+          <t>Long Nasal Run</t>
         </is>
       </c>
       <c r="C182" s="1" t="inlineStr">
@@ -5681,7 +5677,7 @@
       </c>
       <c r="B183" s="1" t="inlineStr">
         <is>
-          <t>Tempo Intervals (1min on / 1min easy)</t>
+          <t>30:30 Tempo Blocks</t>
         </is>
       </c>
       <c r="C183" s="1" t="inlineStr">
@@ -5713,7 +5709,7 @@
       </c>
       <c r="B184" s="1" t="inlineStr">
         <is>
-          <t>Cruise Intervals</t>
+          <t>Tempo Intervals (1min on / 1min easy)</t>
         </is>
       </c>
       <c r="C184" s="1" t="inlineStr">
@@ -5745,7 +5741,7 @@
       </c>
       <c r="B185" s="1" t="inlineStr">
         <is>
-          <t>Bike/Row/Ski Tempo Intervals</t>
+          <t>Cruise Intervals</t>
         </is>
       </c>
       <c r="C185" s="1" t="inlineStr">
@@ -5777,7 +5773,7 @@
       </c>
       <c r="B186" s="1" t="inlineStr">
         <is>
-          <t>Air Bike Sprints</t>
+          <t>Bike/Row/Ski Tempo Intervals</t>
         </is>
       </c>
       <c r="C186" s="1" t="inlineStr">
@@ -5809,7 +5805,7 @@
       </c>
       <c r="B187" s="1" t="inlineStr">
         <is>
-          <t>Row Intervals</t>
+          <t>Air Bike Sprints</t>
         </is>
       </c>
       <c r="C187" s="1" t="inlineStr">
@@ -5841,7 +5837,7 @@
       </c>
       <c r="B188" s="1" t="inlineStr">
         <is>
-          <t>SkiErg Intervals</t>
+          <t>Row Intervals</t>
         </is>
       </c>
       <c r="C188" s="1" t="inlineStr">
@@ -5873,7 +5869,7 @@
       </c>
       <c r="B189" s="1" t="inlineStr">
         <is>
-          <t>Assault Bike Intervals</t>
+          <t>SkiErg Intervals</t>
         </is>
       </c>
       <c r="C189" s="1" t="inlineStr">
@@ -5905,7 +5901,7 @@
       </c>
       <c r="B190" s="1" t="inlineStr">
         <is>
-          <t>Flush Run</t>
+          <t>Assault Bike Intervals</t>
         </is>
       </c>
       <c r="C190" s="1" t="inlineStr">
@@ -5937,7 +5933,7 @@
       </c>
       <c r="B191" s="1" t="inlineStr">
         <is>
-          <t>Easy Bike</t>
+          <t>Flush Run</t>
         </is>
       </c>
       <c r="C191" s="1" t="inlineStr">
@@ -5969,7 +5965,7 @@
       </c>
       <c r="B192" s="1" t="inlineStr">
         <is>
-          <t>Easy Row</t>
+          <t>Easy Bike</t>
         </is>
       </c>
       <c r="C192" s="1" t="inlineStr">
@@ -6001,7 +5997,7 @@
       </c>
       <c r="B193" s="1" t="inlineStr">
         <is>
-          <t>Easy Ski</t>
+          <t>Easy Row</t>
         </is>
       </c>
       <c r="C193" s="1" t="inlineStr">
@@ -6033,7 +6029,7 @@
       </c>
       <c r="B194" s="1" t="inlineStr">
         <is>
-          <t>Easy Swim</t>
+          <t>Easy Ski</t>
         </is>
       </c>
       <c r="C194" s="1" t="inlineStr">
@@ -6065,59 +6061,63 @@
       </c>
       <c r="B195" s="1" t="inlineStr">
         <is>
+          <t>Easy Swim</t>
+        </is>
+      </c>
+      <c r="C195" s="1" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D195" s="1" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E195" s="1" t="inlineStr">
+        <is>
+          <t>everyone</t>
+        </is>
+      </c>
+      <c r="F195" s="1" t="inlineStr">
+        <is>
+          <t>session format, not an individual movement — no meaningful muscle group.</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="1" t="inlineStr">
+        <is>
+          <t>Conditioning</t>
+        </is>
+      </c>
+      <c r="B196" s="1" t="inlineStr">
+        <is>
           <t>Light Circuits</t>
         </is>
       </c>
-      <c r="C195" s="1" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D195" s="1" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E195" s="1" t="inlineStr">
-        <is>
-          <t>everyone</t>
-        </is>
-      </c>
-      <c r="F195" s="1" t="inlineStr">
+      <c r="C196" s="1" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D196" s="1" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E196" s="1" t="inlineStr">
+        <is>
+          <t>everyone</t>
+        </is>
+      </c>
+      <c r="F196" s="1" t="inlineStr">
         <is>
           <t>session format, not an individual movement — no meaningful muscle group.</t>
         </is>
       </c>
     </row>
-    <row r="196"/>
-    <row r="197">
-      <c r="A197" s="1" t="inlineStr">
-        <is>
-          <t>Power</t>
-        </is>
-      </c>
-      <c r="B197" s="1" t="inlineStr">
-        <is>
-          <t>Vertical Jump</t>
-        </is>
-      </c>
-      <c r="C197" s="1" t="inlineStr">
-        <is>
-          <t>Glutes, Quads, Calves</t>
-        </is>
-      </c>
-      <c r="D197" s="1" t="inlineStr">
-        <is>
-          <t>Hamstrings, Midline</t>
-        </is>
-      </c>
-      <c r="E197" s="1" t="inlineStr">
-        <is>
-          <t>everyone</t>
-        </is>
-      </c>
-      <c r="F197" s="1" t="inlineStr"/>
-    </row>
+    <row r="197"/>
     <row r="198">
       <c r="A198" s="1" t="inlineStr">
         <is>
@@ -6126,17 +6126,17 @@
       </c>
       <c r="B198" s="1" t="inlineStr">
         <is>
-          <t>Pogo Hops</t>
+          <t>Vertical Jump</t>
         </is>
       </c>
       <c r="C198" s="1" t="inlineStr">
         <is>
-          <t>Calves</t>
+          <t>Glutes, Quads, Calves</t>
         </is>
       </c>
       <c r="D198" s="1" t="inlineStr">
         <is>
-          <t>Quads, Midline</t>
+          <t>Hamstrings, Midline</t>
         </is>
       </c>
       <c r="E198" s="1" t="inlineStr">
@@ -6144,11 +6144,7 @@
           <t>everyone</t>
         </is>
       </c>
-      <c r="F198" s="1" t="inlineStr">
-        <is>
-          <t>takes over when lower niggle (your spec)</t>
-        </is>
-      </c>
+      <c r="F198" s="1" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" s="1" t="inlineStr">
@@ -6158,17 +6154,17 @@
       </c>
       <c r="B199" s="1" t="inlineStr">
         <is>
-          <t>Lateral Jump</t>
+          <t>Pogo Hops</t>
         </is>
       </c>
       <c r="C199" s="1" t="inlineStr">
         <is>
-          <t>Glutes, Outer hip</t>
+          <t>Calves</t>
         </is>
       </c>
       <c r="D199" s="1" t="inlineStr">
         <is>
-          <t>Quads, Calves, Midline</t>
+          <t>Quads, Midline</t>
         </is>
       </c>
       <c r="E199" s="1" t="inlineStr">
@@ -6178,7 +6174,7 @@
       </c>
       <c r="F199" s="1" t="inlineStr">
         <is>
-          <t>your spec: beginner friendly</t>
+          <t>takes over when lower niggle (your spec)</t>
         </is>
       </c>
     </row>
@@ -6190,27 +6186,27 @@
       </c>
       <c r="B200" s="1" t="inlineStr">
         <is>
-          <t>Kneeling Jump</t>
+          <t>Lateral Jump</t>
         </is>
       </c>
       <c r="C200" s="1" t="inlineStr">
         <is>
-          <t>Glutes, Quads</t>
+          <t>Glutes, Outer hip</t>
         </is>
       </c>
       <c r="D200" s="1" t="inlineStr">
         <is>
-          <t>Hamstrings, Midline</t>
+          <t>Quads, Calves, Midline</t>
         </is>
       </c>
       <c r="E200" s="1" t="inlineStr">
         <is>
-          <t>2+ years</t>
+          <t>everyone</t>
         </is>
       </c>
       <c r="F200" s="1" t="inlineStr">
         <is>
-          <t>your spec: consistent+</t>
+          <t>your spec: beginner friendly</t>
         </is>
       </c>
     </row>
@@ -6222,17 +6218,17 @@
       </c>
       <c r="B201" s="1" t="inlineStr">
         <is>
-          <t>RFE Split Squat Jump</t>
+          <t>Kneeling Jump</t>
         </is>
       </c>
       <c r="C201" s="1" t="inlineStr">
         <is>
-          <t>Quads, Glutes</t>
+          <t>Glutes, Quads</t>
         </is>
       </c>
       <c r="D201" s="1" t="inlineStr">
         <is>
-          <t>Hamstrings, Calves, Midline</t>
+          <t>Hamstrings, Midline</t>
         </is>
       </c>
       <c r="E201" s="1" t="inlineStr">
@@ -6240,9 +6236,9 @@
           <t>2+ years</t>
         </is>
       </c>
-      <c r="F201" s="3" t="inlineStr">
-        <is>
-          <t>FLAG — gate proposed, confirm</t>
+      <c r="F201" s="1" t="inlineStr">
+        <is>
+          <t>your spec: consistent+</t>
         </is>
       </c>
     </row>
@@ -6254,25 +6250,29 @@
       </c>
       <c r="B202" s="1" t="inlineStr">
         <is>
-          <t>Explosive Push-up</t>
+          <t>RFE Split Squat Jump</t>
         </is>
       </c>
       <c r="C202" s="1" t="inlineStr">
         <is>
-          <t>Chest, Triceps</t>
+          <t>Quads, Glutes</t>
         </is>
       </c>
       <c r="D202" s="1" t="inlineStr">
         <is>
-          <t>Shoulders, Midline</t>
+          <t>Hamstrings, Calves, Midline</t>
         </is>
       </c>
       <c r="E202" s="1" t="inlineStr">
         <is>
-          <t>everyone</t>
-        </is>
-      </c>
-      <c r="F202" s="1" t="inlineStr"/>
+          <t>2+ years</t>
+        </is>
+      </c>
+      <c r="F202" s="3" t="inlineStr">
+        <is>
+          <t>FLAG — gate proposed, confirm</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="1" t="inlineStr">
@@ -6282,7 +6282,7 @@
       </c>
       <c r="B203" s="1" t="inlineStr">
         <is>
-          <t>Speed Bench</t>
+          <t>Explosive Push-up</t>
         </is>
       </c>
       <c r="C203" s="1" t="inlineStr">
@@ -6292,19 +6292,15 @@
       </c>
       <c r="D203" s="1" t="inlineStr">
         <is>
-          <t>Shoulders, Lats</t>
+          <t>Shoulders, Midline</t>
         </is>
       </c>
       <c r="E203" s="1" t="inlineStr">
         <is>
-          <t>2+ years</t>
-        </is>
-      </c>
-      <c r="F203" s="3" t="inlineStr">
-        <is>
-          <t>FLAG — gate proposed, confirm</t>
-        </is>
-      </c>
+          <t>everyone</t>
+        </is>
+      </c>
+      <c r="F203" s="1" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" s="1" t="inlineStr">
@@ -6314,25 +6310,57 @@
       </c>
       <c r="B204" s="1" t="inlineStr">
         <is>
+          <t>Speed Bench</t>
+        </is>
+      </c>
+      <c r="C204" s="1" t="inlineStr">
+        <is>
+          <t>Chest, Triceps</t>
+        </is>
+      </c>
+      <c r="D204" s="1" t="inlineStr">
+        <is>
+          <t>Shoulders, Lats</t>
+        </is>
+      </c>
+      <c r="E204" s="1" t="inlineStr">
+        <is>
+          <t>2+ years</t>
+        </is>
+      </c>
+      <c r="F204" s="3" t="inlineStr">
+        <is>
+          <t>FLAG — gate proposed, confirm</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="1" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="B205" s="1" t="inlineStr">
+        <is>
           <t>Speed Trap Bar Deadlift</t>
         </is>
       </c>
-      <c r="C204" s="1" t="inlineStr">
+      <c r="C205" s="1" t="inlineStr">
         <is>
           <t>Glutes, Hamstrings</t>
         </is>
       </c>
-      <c r="D204" s="1" t="inlineStr">
+      <c r="D205" s="1" t="inlineStr">
         <is>
           <t>Quads, Upper back, Grip</t>
         </is>
       </c>
-      <c r="E204" s="1" t="inlineStr">
+      <c r="E205" s="1" t="inlineStr">
         <is>
           <t>2+ years</t>
         </is>
       </c>
-      <c r="F204" s="3" t="inlineStr">
+      <c r="F205" s="3" t="inlineStr">
         <is>
           <t>FLAG — gate proposed, confirm</t>
         </is>
